--- a/RC_Lootcouncil.xlsx
+++ b/RC_Lootcouncil.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chris/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EE2FA6A-7BB5-F44A-874E-469EC2789572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5E8D79-0954-724B-9BB0-E20A7ED5524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10760" yWindow="1580" windowWidth="46560" windowHeight="26420" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4617" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="952">
   <si>
     <t>player</t>
   </si>
@@ -2135,6 +2135,837 @@
   </si>
   <si>
     <t>=HYPERLINK("https://tbc.wowhead.com/item=28734";"[Jewel of Infinite Possibilities]")</t>
+  </si>
+  <si>
+    <t>[Handschuhe des bezwungenen Helden]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des Waldläufergenerals]</t>
+  </si>
+  <si>
+    <t>[Leuchtende Brustplatte der Wahrheit]</t>
+  </si>
+  <si>
+    <t>[Ahnenring der Eroberung]</t>
+  </si>
+  <si>
+    <t>[Weltenbrecher]</t>
+  </si>
+  <si>
+    <t>[Ohrring der seelenvollen Meditation]</t>
+  </si>
+  <si>
+    <t>[Gürtel der hundert Tode]</t>
+  </si>
+  <si>
+    <t>[Nethervortex]</t>
+  </si>
+  <si>
+    <t>[Shuriken des Schlangenschreins]</t>
+  </si>
+  <si>
+    <t>[Muster: Stiefel des langen Weges]</t>
+  </si>
+  <si>
+    <t>[Anhänger der verlorenen Zeiten]</t>
+  </si>
+  <si>
+    <t>[Helm des bezwungenen Helden]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des bezwungenen Champions]</t>
+  </si>
+  <si>
+    <t>[Stachelige Korallenschulterpolster]</t>
+  </si>
+  <si>
+    <t>[Lebendige Wurzel des Wildherzens]</t>
+  </si>
+  <si>
+    <t>[Ring der Tödlichkeit]</t>
+  </si>
+  <si>
+    <t>[Handschuhe des bezwungenen Champions]</t>
+  </si>
+  <si>
+    <t>[Helm des bezwungenen Champions]</t>
+  </si>
+  <si>
+    <t>[Kriegsstiefel der Auslöschung]</t>
+  </si>
+  <si>
+    <t>[Totem des Mahlstroms]</t>
+  </si>
+  <si>
+    <t>[Flechte der Schlangenschlinge]</t>
+  </si>
+  <si>
+    <t>[Ring der Endlosschleife]</t>
+  </si>
+  <si>
+    <t>[Bark-Gloves of Ancient Wisdom]</t>
+  </si>
+  <si>
+    <t>[Arcanite Steam-Pistol]</t>
+  </si>
+  <si>
+    <t>[Fel-Steel Warhelm]</t>
+  </si>
+  <si>
+    <t>[Pauldrons of the Vanquished Defender]</t>
+  </si>
+  <si>
+    <t>[Mindstorm Wristbands]</t>
+  </si>
+  <si>
+    <t>[Boots of the Resilient]</t>
+  </si>
+  <si>
+    <t>[Seventh Ring of the Tirisfalen]</t>
+  </si>
+  <si>
+    <t>[Netherbane]</t>
+  </si>
+  <si>
+    <t>[Greaves of the Bloodwarder]</t>
+  </si>
+  <si>
+    <t>[Plans: Red Belt of Battle]</t>
+  </si>
+  <si>
+    <t>[Pauldrons of the Vanquished Hero]</t>
+  </si>
+  <si>
+    <t>[Void Star Talisman]</t>
+  </si>
+  <si>
+    <t>[Schulterpolster des Fremden]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des bezwungenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Handschuhe des bezwungenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Ausgefranster Strick des Ertrunkenen]</t>
+  </si>
+  <si>
+    <t>[Gurt des Unverwundbaren]</t>
+  </si>
+  <si>
+    <t>[Schulterpolster der Illidari]</t>
+  </si>
+  <si>
+    <t>[Das Siegel von Danzalar]</t>
+  </si>
+  <si>
+    <t>[Kralle von Azshara]</t>
+  </si>
+  <si>
+    <t>[Wickeltücher der Läuterung]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des bezwungenen Helden]</t>
+  </si>
+  <si>
+    <t>[Stiefel des mühelosen Kampfes]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke der Argentumschildwache]</t>
+  </si>
+  <si>
+    <t>[Royal Cloak of the Sunstriders]</t>
+  </si>
+  <si>
+    <t>[Girdle of Zaetar]</t>
+  </si>
+  <si>
+    <t>[Chestguard of the Vanquished Hero]</t>
+  </si>
+  <si>
+    <t>[Star-Strider Boots]</t>
+  </si>
+  <si>
+    <t>[Gloves of the Searing Grip]</t>
+  </si>
+  <si>
+    <t>[Trousers of the Astromancer]</t>
+  </si>
+  <si>
+    <t>[Chestguard of the Vanquished Defender]</t>
+  </si>
+  <si>
+    <t>[Phoenix-Ring of Rebirth]</t>
+  </si>
+  <si>
+    <t>[Bands of the Celestial Archer]</t>
+  </si>
+  <si>
+    <t>[Tome of Fiery Redemption]</t>
+  </si>
+  <si>
+    <t>[Verdant Sphere]</t>
+  </si>
+  <si>
+    <t>[Heartrazor]</t>
+  </si>
+  <si>
+    <t>[Rauer Brustharnisch der Uralten]</t>
+  </si>
+  <si>
+    <t>[Zahn von Gruul]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des gefallenen Helden]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des gefallenen Helden]</t>
+  </si>
+  <si>
+    <t>[Sextant der unsteten Strömung]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des gefallenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Magtheridons Kopf]</t>
+  </si>
+  <si>
+    <t>[Szepter der Lichtertiefe]</t>
+  </si>
+  <si>
+    <t>[Gürtel der göttlichen Eingebung]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des gefallenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Gleve der Grube]</t>
+  </si>
+  <si>
+    <t>[Skarabäus der Verdrängung]</t>
+  </si>
+  <si>
+    <t>[Stiefel des endlosen Mutes]</t>
+  </si>
+  <si>
+    <t>[Stiefel des sich wandelnden Alptraums]</t>
+  </si>
+  <si>
+    <t>[Drachenwirbeltrophäe]</t>
+  </si>
+  <si>
+    <t>[Buchband der absoluten Wahrheit]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des gefallenen Champions]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des gefallenen Champions]</t>
+  </si>
+  <si>
+    <t>[Schlaghammer der Gezeiten]</t>
+  </si>
+  <si>
+    <t>[Magtheridons Auge]</t>
+  </si>
+  <si>
+    <t>[Zwillingsklinge des Phönix]</t>
+  </si>
+  <si>
+    <t>[Gurt von Zaetar]</t>
+  </si>
+  <si>
+    <t>[Stulpen des Sonnenkönigs]</t>
+  </si>
+  <si>
+    <t>[Foliant der feurigen Erlösung]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des bezwungenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des bezwungenen Helden]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des bezwungenen Helden]</t>
+  </si>
+  <si>
+    <t>[Al'ars Band]</t>
+  </si>
+  <si>
+    <t>[Al'ars Kralle]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des bezwungenen Champions]</t>
+  </si>
+  <si>
+    <t>[Tiefgrüne Sphäre]</t>
+  </si>
+  <si>
+    <t>[Pattern: Boots of the Long Road]</t>
+  </si>
+  <si>
+    <t>[Soul-Strider Boots]</t>
+  </si>
+  <si>
+    <t>[Warboots of Obliteration]</t>
+  </si>
+  <si>
+    <t>[Libram of Absolute Truth]</t>
+  </si>
+  <si>
+    <t>[Bracers of Eradication]</t>
+  </si>
+  <si>
+    <t>[Pattern: Belt of Deep Shadow]</t>
+  </si>
+  <si>
+    <t>[Tempest-Strider Boots]</t>
+  </si>
+  <si>
+    <t>[Leggings of the Vanquished Champion]</t>
+  </si>
+  <si>
+    <t>[Pendant of the Perilous]</t>
+  </si>
+  <si>
+    <t>[Leggings of the Vanquished Defender]</t>
+  </si>
+  <si>
+    <t>[Leggings of the Vanquished Hero]</t>
+  </si>
+  <si>
+    <t>[Serpentshrine Shuriken]</t>
+  </si>
+  <si>
+    <t>[Plans: Red Havoc Boots]</t>
+  </si>
+  <si>
+    <t>[Pauldrons of the Wardancer]</t>
+  </si>
+  <si>
+    <t>[Belt of One-Hundred Deaths]</t>
+  </si>
+  <si>
+    <t>[Gnarled Chestpiece of the Ancients]</t>
+  </si>
+  <si>
+    <t>[Helm of the Vanquished Champion]</t>
+  </si>
+  <si>
+    <t>[Glorious Gauntlets of Crestfall]</t>
+  </si>
+  <si>
+    <t>[Band of the Vigilant]</t>
+  </si>
+  <si>
+    <t>[Helm of the Vanquished Hero]</t>
+  </si>
+  <si>
+    <t>[Pattern: Boots of Utter Darkness]</t>
+  </si>
+  <si>
+    <t>[Brighthelm of Justice]</t>
+  </si>
+  <si>
+    <t>[Fathomstone]</t>
+  </si>
+  <si>
+    <t>[Gugel des Großingenieurs]</t>
+  </si>
+  <si>
+    <t>[Axt der Gronnlords]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des gefallenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Zauberstab des vergessenen Sterns]</t>
+  </si>
+  <si>
+    <t>[Brustplatte des Feuerwappens]</t>
+  </si>
+  <si>
+    <t>[Auge von Gruul]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke des bezwungenen Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Lebensstab des Astraleums]</t>
+  </si>
+  <si>
+    <t>[Der Nexusschlüssel]</t>
+  </si>
+  <si>
+    <t>[Hammer der Naaru]</t>
+  </si>
+  <si>
+    <t>[Gurt des rechtschaffenen Pfads]</t>
+  </si>
+  <si>
+    <t>[Band des Waldläufergenerals]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des bezwungenen Champions]</t>
+  </si>
+  <si>
+    <t>[Handschützer des Wildtierfürsten]</t>
+  </si>
+  <si>
+    <t>[Brustschutz des Verschwörers]</t>
+  </si>
+  <si>
+    <t>[Siegel des Gestaltwandlers]</t>
+  </si>
+  <si>
+    <t>[Blutschrei]</t>
+  </si>
+  <si>
+    <t>[Essenz des Märtyrers]</t>
+  </si>
+  <si>
+    <t>[Gurt des Verrats]</t>
+  </si>
+  <si>
+    <t>[Phönixbogen des Sonnenzorns]</t>
+  </si>
+  <si>
+    <t>[Prophetenhalsring der Sethekk]</t>
+  </si>
+  <si>
+    <t>[Krone des Herzens der Leere]</t>
+  </si>
+  <si>
+    <t>[Gamaschen der Herzensflamme]</t>
+  </si>
+  <si>
+    <t>[Schulterpolster des Orkans]</t>
+  </si>
+  <si>
+    <t>[Alchimistenstein]</t>
+  </si>
+  <si>
+    <t>[Zauberfeuerhandschuhe]</t>
+  </si>
+  <si>
+    <t>[Violettes Siegel]</t>
+  </si>
+  <si>
+    <t>[Beinschützer des Rechtsprechers]</t>
+  </si>
+  <si>
+    <t>[Handschützer des Rechtsprechers]</t>
+  </si>
+  <si>
+    <t>[Panzatronikbrille]</t>
+  </si>
+  <si>
+    <t>[Eisenschreiter der Dringlichkeit]</t>
+  </si>
+  <si>
+    <t>[Hose des Zauberschlags]</t>
+  </si>
+  <si>
+    <t>[Ikone des Silberwappens]</t>
+  </si>
+  <si>
+    <t>[Band des purpurroten Furors]</t>
+  </si>
+  <si>
+    <t>[Hallowed Handwraps]</t>
+  </si>
+  <si>
+    <t>[Sunfury Bow of the Phoenix]</t>
+  </si>
+  <si>
+    <t>[Warbringer Greathelm]</t>
+  </si>
+  <si>
+    <t>[Warbringer Shoulderguards]</t>
+  </si>
+  <si>
+    <t>[Bracers of the White Stag]</t>
+  </si>
+  <si>
+    <t>[Boots of the Righteous Path]</t>
+  </si>
+  <si>
+    <t>[Violet Signet of the Great Protector]</t>
+  </si>
+  <si>
+    <t>[Dragonmaw]</t>
+  </si>
+  <si>
+    <t>[Warbringer Greaves]</t>
+  </si>
+  <si>
+    <t>[Pauldrons of the Aldor]</t>
+  </si>
+  <si>
+    <t>[Mitts of the Treemender]</t>
+  </si>
+  <si>
+    <t>[Shoulderguards of Malorne]</t>
+  </si>
+  <si>
+    <t>[Scryer's Bloodgem]</t>
+  </si>
+  <si>
+    <t>[Schulterplatten des Kriegshetzers]</t>
+  </si>
+  <si>
+    <t>[Schienbeinschützer des Kriegshetzers]</t>
+  </si>
+  <si>
+    <t>[Fürstliche Herrschaftgamaschen]</t>
+  </si>
+  <si>
+    <t>[Handschuhe der geschickten Manipulation]</t>
+  </si>
+  <si>
+    <t>[Anhänger des Gefahrvollen]</t>
+  </si>
+  <si>
+    <t>[Plattengürtel des Kriegsherren]</t>
+  </si>
+  <si>
+    <t>[Handlappen des Gedankenflusses]</t>
+  </si>
+  <si>
+    <t>[Malornes Schulterstücke]</t>
+  </si>
+  <si>
+    <t>[Siegel des Sehers]</t>
+  </si>
+  <si>
+    <t>[Drachenmal]</t>
+  </si>
+  <si>
+    <t>[Handschuhe der Aldor]</t>
+  </si>
+  <si>
+    <t>[Bänder des Innewohnens]</t>
+  </si>
+  <si>
+    <t>[Zierhuts verschwundene Treter]</t>
+  </si>
+  <si>
+    <t>[Geheiligte Schulterstücke]</t>
+  </si>
+  <si>
+    <t>[Farseer Cloak of Shadow Wrath]</t>
+  </si>
+  <si>
+    <t>[Cincture of Will]</t>
+  </si>
+  <si>
+    <t>[Beast Lord Cuirass]</t>
+  </si>
+  <si>
+    <t>[Edgewalker Longboots]</t>
+  </si>
+  <si>
+    <t>[Grips of Deftness]</t>
+  </si>
+  <si>
+    <t>[Light-Mantle of the Incarnate]</t>
+  </si>
+  <si>
+    <t>[Gladiator's Silk Amice]</t>
+  </si>
+  <si>
+    <t>[Vestments of the Aldor]</t>
+  </si>
+  <si>
+    <t>[Legwraps of the Aldor]</t>
+  </si>
+  <si>
+    <t>[Mantle of Malorne]</t>
+  </si>
+  <si>
+    <t>[Warbringer Breastplate]</t>
+  </si>
+  <si>
+    <t>[Ryngo's Band of Ingenuity]</t>
+  </si>
+  <si>
+    <t>[Stalker's War Bands]</t>
+  </si>
+  <si>
+    <t>[Icon of the Silver Crescent]</t>
+  </si>
+  <si>
+    <t>[Gladiator's Slicer]</t>
+  </si>
+  <si>
+    <t>[Wams des Steingeästs]</t>
+  </si>
+  <si>
+    <t>[Halskette der ewigen Hoffnung]</t>
+  </si>
+  <si>
+    <t>[Helm des Wildtierfürsten]</t>
+  </si>
+  <si>
+    <t>[Mantelung des Wildtierfürsten]</t>
+  </si>
+  <si>
+    <t>[Gamaschen des Wildtierfürsten]</t>
+  </si>
+  <si>
+    <t>[Gugel der Herausforderung]</t>
+  </si>
+  <si>
+    <t>[Stiefel der astralen Manipulation]</t>
+  </si>
+  <si>
+    <t>[Robe der Ahnenschriften]</t>
+  </si>
+  <si>
+    <t>[Gerechtigkeit des Lichts]</t>
+  </si>
+  <si>
+    <t>[Urmondstoffrobe]</t>
+  </si>
+  <si>
+    <t>[Gurt des Magiezorns]</t>
+  </si>
+  <si>
+    <t>[Zornstahlschultern]</t>
+  </si>
+  <si>
+    <t>[Glanz des Verteidigers]</t>
+  </si>
+  <si>
+    <t>[Lederstiefel des Veteranen]</t>
+  </si>
+  <si>
+    <t>[Malornes Schienbeinschützer]</t>
+  </si>
+  <si>
+    <t>[Malornes Brustplatte]</t>
+  </si>
+  <si>
+    <t>[Extravagante Stiefel der Bosheit]</t>
+  </si>
+  <si>
+    <t>[Handschutz des Geschicks]</t>
+  </si>
+  <si>
+    <t>[Stundenglas des Entwirrers]</t>
+  </si>
+  <si>
+    <t>[Stulpen der erneuten Hoffnung]</t>
+  </si>
+  <si>
+    <t>[Beinplatten des Unschuldigen]</t>
+  </si>
+  <si>
+    <t>[Schuppenbrustplatte des Blutbads]</t>
+  </si>
+  <si>
+    <t>[Kilt des Waldhüters]</t>
+  </si>
+  <si>
+    <t>[Stulpen der Kampfvollendung]</t>
+  </si>
+  <si>
+    <t>[Quagmirrans Auge]</t>
+  </si>
+  <si>
+    <t>[Ringpanzergurt des Veteranen]</t>
+  </si>
+  <si>
+    <t>[Schwere Grollhufweste]</t>
+  </si>
+  <si>
+    <t>[Gewänder der Aldor]</t>
+  </si>
+  <si>
+    <t>[Schulterstücke der Aldor]</t>
+  </si>
+  <si>
+    <t>[Kampfrauschbrosche]</t>
+  </si>
+  <si>
+    <t>[Klingenschulterpolster des Erbarmungslosen]</t>
+  </si>
+  <si>
+    <t>[Slippers of Serenity]</t>
+  </si>
+  <si>
+    <t>[Battlescar Boots]</t>
+  </si>
+  <si>
+    <t>[General's Plate Bracers]</t>
+  </si>
+  <si>
+    <t>[Silent Slippers of Meditation]</t>
+  </si>
+  <si>
+    <t>[Shattrath Leggings]</t>
+  </si>
+  <si>
+    <t>[Choker of Vile Intent]</t>
+  </si>
+  <si>
+    <t>[Spellstrike Pants]</t>
+  </si>
+  <si>
+    <t>[Warbringer Shoulderplates]</t>
+  </si>
+  <si>
+    <t>[Deathforge Girdle]</t>
+  </si>
+  <si>
+    <t>[Stonebough Jerkin]</t>
+  </si>
+  <si>
+    <t>[Justicar Diadem]</t>
+  </si>
+  <si>
+    <t>[Crystalforge Gloves]</t>
+  </si>
+  <si>
+    <t>[Spectral Band of Innervation]</t>
+  </si>
+  <si>
+    <t>[Beast Lord Helm]</t>
+  </si>
+  <si>
+    <t>[Hood of the Corruptor]</t>
+  </si>
+  <si>
+    <t>[The Black Stalk]</t>
+  </si>
+  <si>
+    <t>[Jewel of Infinite Possibilities]</t>
+  </si>
+  <si>
+    <t>[Band der Ewigkeit]</t>
+  </si>
+  <si>
+    <t>[Kopfputz des Gedankenbunds]</t>
+  </si>
+  <si>
+    <t>[Eisschattenzwirnschultern]</t>
+  </si>
+  <si>
+    <t>[Eisschattenzwirnrobe]</t>
+  </si>
+  <si>
+    <t>[Roben des Leibhaftigen]</t>
+  </si>
+  <si>
+    <t>[Teufelsledergamaschen]</t>
+  </si>
+  <si>
+    <t>[Abzeichen der Hartnäckigkeit]</t>
+  </si>
+  <si>
+    <t>[Vorherrschaftsstab von Tirisfal]</t>
+  </si>
+  <si>
+    <t>[Schleife der Opferung]</t>
+  </si>
+  <si>
+    <t>[Schulterplatten des Orkans]</t>
+  </si>
+  <si>
+    <t>[Getreuer Hammer des Lichts]</t>
+  </si>
+  <si>
+    <t>[Brustplatte des Kriegshetzers]</t>
+  </si>
+  <si>
+    <t>[Geisterklinge der Nathrezim]</t>
+  </si>
+  <si>
+    <t>[Schulterschutz des Rechtsprechers]</t>
+  </si>
+  <si>
+    <t>[Magusklinge des Blutmagens]</t>
+  </si>
+  <si>
+    <t>[Zieratgürtel des Veteranen]</t>
+  </si>
+  <si>
+    <t>[Schulterpolster der Netherklinge]</t>
+  </si>
+  <si>
+    <t>[Brustharnisch der Netherklinge]</t>
+  </si>
+  <si>
+    <t>[A'dals Gebot]</t>
+  </si>
+  <si>
+    <t>[Xi'ris Gabe]</t>
+  </si>
+  <si>
+    <t>[Ring des schattenhaften Schicksals]</t>
+  </si>
+  <si>
+    <t>[Der Blitzkondensator]</t>
+  </si>
+  <si>
+    <t>[Ring der Wiederkehr]</t>
+  </si>
+  <si>
+    <t>[Ring of Unyielding Force]</t>
+  </si>
+  <si>
+    <t>[Fel Edged Battleaxe]</t>
+  </si>
+  <si>
+    <t>[Quagmirran's Eye]</t>
+  </si>
+  <si>
+    <t>[Ashyens Gabe]</t>
+  </si>
+  <si>
+    <t>[Netherbann]</t>
+  </si>
+  <si>
+    <t>[Violet Signet of the Archmage]</t>
+  </si>
+  <si>
+    <t>[Figurine of the Colossus]</t>
+  </si>
+  <si>
+    <t>[Latro's Shifting Sword]</t>
+  </si>
+  <si>
+    <t>[Klinge des Unerwiderten]</t>
+  </si>
+  <si>
+    <t>[Figur des Kolosses]</t>
+  </si>
+  <si>
+    <t>[Ryngos Band des Scharfsinns]</t>
+  </si>
+  <si>
+    <t>[Abakus der Ungleichheit]</t>
+  </si>
+  <si>
+    <t>[Spektrales Band der Innervation]</t>
+  </si>
+  <si>
+    <t>[Zeitraffersplitter]</t>
+  </si>
+  <si>
+    <t>[Glaubensschild des Lichtjüngers]</t>
+  </si>
+  <si>
+    <t>[Tiefenstein]</t>
+  </si>
+  <si>
+    <t>[Verteidiger des Aldorivermächtnisses]</t>
+  </si>
+  <si>
+    <t>[Garonas Siegelring]</t>
   </si>
 </sst>
 </file>
@@ -6467,10 +7298,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="message" connectionId="1" xr16:uid="{28F6F41A-4054-D041-9870-344BB5B4A1B4}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
@@ -6920,9 +7747,8 @@
       <c r="C2" s="2">
         <v>0.91111111111111109</v>
       </c>
-      <c r="D2" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30241","[Handschuhe des bezwungenen Helden]")</f>
-        <v>[Handschuhe des bezwungenen Helden]</v>
+      <c r="D2" t="s">
+        <v>675</v>
       </c>
       <c r="E2">
         <v>30241</v>
@@ -6945,9 +7771,8 @@
       <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27474","[Handschützer des Wildtierfürsten]")</f>
-        <v>[Handschützer des Wildtierfürsten]</v>
+      <c r="L2" t="s">
+        <v>800</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -6979,9 +7804,8 @@
       <c r="C3" s="2">
         <v>0.86111111111111116</v>
       </c>
-      <c r="D3" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30054","[Brustschutz des Waldläufergenerals]")</f>
-        <v>[Brustschutz des Waldläufergenerals]</v>
+      <c r="D3" t="s">
+        <v>676</v>
       </c>
       <c r="E3">
         <v>30054</v>
@@ -7004,9 +7828,8 @@
       <c r="K3" t="s">
         <v>34</v>
       </c>
-      <c r="L3" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28601","[Brustschutz des Verschwörers]")</f>
-        <v>[Brustschutz des Verschwörers]</v>
+      <c r="L3" t="s">
+        <v>801</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -7041,9 +7864,8 @@
       <c r="C4" s="2">
         <v>0.87638888888888888</v>
       </c>
-      <c r="D4" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30065","[Leuchtende Brustplatte der Wahrheit]")</f>
-        <v>[Leuchtende Brustplatte der Wahrheit]</v>
+      <c r="D4" t="s">
+        <v>677</v>
       </c>
       <c r="E4">
         <v>30065</v>
@@ -7066,9 +7888,8 @@
       <c r="K4" t="s">
         <v>34</v>
       </c>
-      <c r="L4" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28601","[Brustschutz des Verschwörers]")</f>
-        <v>[Brustschutz des Verschwörers]</v>
+      <c r="L4" t="s">
+        <v>801</v>
       </c>
       <c r="N4">
         <v>4</v>
@@ -7103,9 +7924,8 @@
       <c r="C5" s="2">
         <v>0.87708333333333333</v>
       </c>
-      <c r="D5" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30061","[Ahnenring der Eroberung]")</f>
-        <v>[Ahnenring der Eroberung]</v>
+      <c r="D5" t="s">
+        <v>678</v>
       </c>
       <c r="E5">
         <v>30061</v>
@@ -7128,13 +7948,11 @@
       <c r="K5" t="s">
         <v>34</v>
       </c>
-      <c r="L5" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30834","[Siegel des Gestaltwandlers]")</f>
-        <v>[Siegel des Gestaltwandlers]</v>
-      </c>
-      <c r="M5" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29177","[A'dals Gebot]")</f>
-        <v>[A'dals Gebot]</v>
+      <c r="L5" t="s">
+        <v>802</v>
+      </c>
+      <c r="M5" t="s">
+        <v>929</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -7169,9 +7987,8 @@
       <c r="C6" s="2">
         <v>0.91041666666666665</v>
       </c>
-      <c r="D6" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30090","[Weltenbrecher]")</f>
-        <v>[Weltenbrecher]</v>
+      <c r="D6" t="s">
+        <v>679</v>
       </c>
       <c r="E6">
         <v>30090</v>
@@ -7194,9 +8011,8 @@
       <c r="K6" t="s">
         <v>26</v>
       </c>
-      <c r="L6" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28773","[Blutschrei]")</f>
-        <v>[Blutschrei]</v>
+      <c r="L6" t="s">
+        <v>803</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -7231,9 +8047,8 @@
       <c r="C7" s="2">
         <v>0.87708333333333333</v>
       </c>
-      <c r="D7" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30665","[Ohrring der seelenvollen Meditation]")</f>
-        <v>[Ohrring der seelenvollen Meditation]</v>
+      <c r="D7" t="s">
+        <v>680</v>
       </c>
       <c r="E7">
         <v>30665</v>
@@ -7256,13 +8071,11 @@
       <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="L7" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29376","[Essenz des Märtyrers]")</f>
-        <v>[Essenz des Märtyrers]</v>
-      </c>
-      <c r="M7" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28590","[Schleife der Opferung]")</f>
-        <v>[Schleife der Opferung]</v>
+      <c r="L7" t="s">
+        <v>804</v>
+      </c>
+      <c r="M7" t="s">
+        <v>919</v>
       </c>
       <c r="N7">
         <v>2</v>
@@ -7297,9 +8110,8 @@
       <c r="C8" s="2">
         <v>0.97916666666666663</v>
       </c>
-      <c r="D8" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30106","[Gürtel der hundert Tode]")</f>
-        <v>[Gürtel der hundert Tode]</v>
+      <c r="D8" t="s">
+        <v>681</v>
       </c>
       <c r="E8">
         <v>30106</v>
@@ -7322,9 +8134,8 @@
       <c r="K8" t="s">
         <v>53</v>
       </c>
-      <c r="L8" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28750","[Gurt des Verrats]")</f>
-        <v>[Gurt des Verrats]</v>
+      <c r="L8" t="s">
+        <v>805</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -7359,9 +8170,8 @@
       <c r="C9" s="2">
         <v>0.88749999999999996</v>
       </c>
-      <c r="D9" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30183","[Nethervortex]")</f>
-        <v>[Nethervortex]</v>
+      <c r="D9" t="s">
+        <v>682</v>
       </c>
       <c r="E9">
         <v>30183</v>
@@ -7414,9 +8224,8 @@
       <c r="C10" s="2">
         <v>0.90972222222222221</v>
       </c>
-      <c r="D10" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30025","[Shuriken des Schlangenschreins]")</f>
-        <v>[Shuriken des Schlangenschreins]</v>
+      <c r="D10" t="s">
+        <v>683</v>
       </c>
       <c r="E10">
         <v>30025</v>
@@ -7439,9 +8248,8 @@
       <c r="K10" t="s">
         <v>26</v>
       </c>
-      <c r="L10" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28772","[Phönixbogen des Sonnenzorns]")</f>
-        <v>[Phönixbogen des Sonnenzorns]</v>
+      <c r="L10" t="s">
+        <v>806</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -7476,9 +8284,8 @@
       <c r="C11" s="2">
         <v>0.91041666666666665</v>
       </c>
-      <c r="D11" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30283","[Muster: Stiefel des langen Weges]")</f>
-        <v>[Muster: Stiefel des langen Weges]</v>
+      <c r="D11" t="s">
+        <v>684</v>
       </c>
       <c r="E11">
         <v>30283</v>
@@ -7531,9 +8338,8 @@
       <c r="C12" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D12" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30008","[Anhänger der verlorenen Zeiten]")</f>
-        <v>[Anhänger der verlorenen Zeiten]</v>
+      <c r="D12" t="s">
+        <v>685</v>
       </c>
       <c r="E12">
         <v>30008</v>
@@ -7556,9 +8362,8 @@
       <c r="K12" t="s">
         <v>26</v>
       </c>
-      <c r="L12" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29333","[Prophetenhalsring der Sethekk]")</f>
-        <v>[Prophetenhalsring der Sethekk]</v>
+      <c r="L12" t="s">
+        <v>807</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -7593,9 +8398,8 @@
       <c r="C13" s="2">
         <v>0.97916666666666663</v>
       </c>
-      <c r="D13" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30244","[Helm des bezwungenen Helden]")</f>
-        <v>[Helm des bezwungenen Helden]</v>
+      <c r="D13" t="s">
+        <v>686</v>
       </c>
       <c r="E13">
         <v>30244</v>
@@ -7618,9 +8422,8 @@
       <c r="K13" t="s">
         <v>53</v>
       </c>
-      <c r="L13" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28963","[Krone des Herzens der Leere]")</f>
-        <v>[Krone des Herzens der Leere]</v>
+      <c r="L13" t="s">
+        <v>808</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -7652,9 +8455,8 @@
       <c r="C14" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D14" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30245","[Gamaschen des bezwungenen Champions]")</f>
-        <v>[Gamaschen des bezwungenen Champions]</v>
+      <c r="D14" t="s">
+        <v>687</v>
       </c>
       <c r="E14">
         <v>30245</v>
@@ -7677,9 +8479,8 @@
       <c r="K14" t="s">
         <v>26</v>
       </c>
-      <c r="L14" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28751","[Gamaschen der Herzensflamme]")</f>
-        <v>[Gamaschen der Herzensflamme]</v>
+      <c r="L14" t="s">
+        <v>809</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -7711,9 +8512,8 @@
       <c r="C15" s="2">
         <v>0.91041666666666665</v>
       </c>
-      <c r="D15" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30097","[Stachelige Korallenschulterpolster]")</f>
-        <v>[Stachelige Korallenschulterpolster]</v>
+      <c r="D15" t="s">
+        <v>688</v>
       </c>
       <c r="E15">
         <v>30097</v>
@@ -7736,9 +8536,8 @@
       <c r="K15" t="s">
         <v>26</v>
       </c>
-      <c r="L15" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29031","[Schulterpolster des Orkans]")</f>
-        <v>[Schulterpolster des Orkans]</v>
+      <c r="L15" t="s">
+        <v>810</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -7773,9 +8572,8 @@
       <c r="C16" s="2">
         <v>0.86250000000000004</v>
       </c>
-      <c r="D16" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30664","[Lebendige Wurzel des Wildherzens]")</f>
-        <v>[Lebendige Wurzel des Wildherzens]</v>
+      <c r="D16" t="s">
+        <v>689</v>
       </c>
       <c r="E16">
         <v>30664</v>
@@ -7798,13 +8596,11 @@
       <c r="K16" t="s">
         <v>34</v>
       </c>
-      <c r="L16" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=13503","[Alchimistenstein]")</f>
-        <v>[Alchimistenstein]</v>
-      </c>
-      <c r="M16" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29179","[Xi'ris Gabe]")</f>
-        <v>[Xi'ris Gabe]</v>
+      <c r="L16" t="s">
+        <v>811</v>
+      </c>
+      <c r="M16" t="s">
+        <v>930</v>
       </c>
       <c r="N16">
         <v>3</v>
@@ -7839,9 +8635,8 @@
       <c r="C17" s="2">
         <v>0.91180555555555554</v>
       </c>
-      <c r="D17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30241","[Handschuhe des bezwungenen Helden]")</f>
-        <v>[Handschuhe des bezwungenen Helden]</v>
+      <c r="D17" t="s">
+        <v>675</v>
       </c>
       <c r="E17">
         <v>30241</v>
@@ -7864,9 +8659,8 @@
       <c r="K17" t="s">
         <v>26</v>
       </c>
-      <c r="L17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=21847","[Zauberfeuerhandschuhe]")</f>
-        <v>[Zauberfeuerhandschuhe]</v>
+      <c r="L17" t="s">
+        <v>812</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -7898,9 +8692,8 @@
       <c r="C18" s="2">
         <v>0.8618055555555556</v>
       </c>
-      <c r="D18" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30052","[Ring der Tödlichkeit]")</f>
-        <v>[Ring der Tödlichkeit]</v>
+      <c r="D18" t="s">
+        <v>690</v>
       </c>
       <c r="E18">
         <v>30052</v>
@@ -7923,13 +8716,11 @@
       <c r="K18" t="s">
         <v>34</v>
       </c>
-      <c r="L18" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29282","[Violettes Siegel]")</f>
-        <v>[Violettes Siegel]</v>
-      </c>
-      <c r="M18" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28323","[Ring des schattenhaften Schicksals]")</f>
-        <v>[Ring des schattenhaften Schicksals]</v>
+      <c r="L18" t="s">
+        <v>813</v>
+      </c>
+      <c r="M18" t="s">
+        <v>931</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -7967,9 +8758,8 @@
       <c r="C19" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D19" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30245","[Gamaschen des bezwungenen Champions]")</f>
-        <v>[Gamaschen des bezwungenen Champions]</v>
+      <c r="D19" t="s">
+        <v>687</v>
       </c>
       <c r="E19">
         <v>30245</v>
@@ -7992,9 +8782,8 @@
       <c r="K19" t="s">
         <v>26</v>
       </c>
-      <c r="L19" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29069","[Beinschützer des Rechtsprechers]")</f>
-        <v>[Beinschützer des Rechtsprechers]</v>
+      <c r="L19" t="s">
+        <v>814</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -8026,9 +8815,8 @@
       <c r="C20" s="2">
         <v>0.91041666666666665</v>
       </c>
-      <c r="D20" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30239","[Handschuhe des bezwungenen Champions]")</f>
-        <v>[Handschuhe des bezwungenen Champions]</v>
+      <c r="D20" t="s">
+        <v>691</v>
       </c>
       <c r="E20">
         <v>30239</v>
@@ -8051,9 +8839,8 @@
       <c r="K20" t="s">
         <v>26</v>
       </c>
-      <c r="L20" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29067","[Handschützer des Rechtsprechers]")</f>
-        <v>[Handschützer des Rechtsprechers]</v>
+      <c r="L20" t="s">
+        <v>815</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -8085,9 +8872,8 @@
       <c r="C21" s="2">
         <v>0.97847222222222219</v>
       </c>
-      <c r="D21" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30242","[Helm des bezwungenen Champions]")</f>
-        <v>[Helm des bezwungenen Champions]</v>
+      <c r="D21" t="s">
+        <v>692</v>
       </c>
       <c r="E21">
         <v>30242</v>
@@ -8110,9 +8896,8 @@
       <c r="K21" t="s">
         <v>53</v>
       </c>
-      <c r="L21" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32473","[Panzatronikbrille]")</f>
-        <v>[Panzatronikbrille]</v>
+      <c r="L21" t="s">
+        <v>816</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -8144,9 +8929,8 @@
       <c r="C22" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D22" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30081","[Kriegsstiefel der Auslöschung]")</f>
-        <v>[Kriegsstiefel der Auslöschung]</v>
+      <c r="D22" t="s">
+        <v>693</v>
       </c>
       <c r="E22">
         <v>30081</v>
@@ -8169,9 +8953,8 @@
       <c r="K22" t="s">
         <v>26</v>
       </c>
-      <c r="L22" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28608","[Eisenschreiter der Dringlichkeit]")</f>
-        <v>[Eisenschreiter der Dringlichkeit]</v>
+      <c r="L22" t="s">
+        <v>817</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -8206,9 +8989,8 @@
       <c r="C23" s="2">
         <v>0.87777777777777777</v>
       </c>
-      <c r="D23" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30023","[Totem des Mahlstroms]")</f>
-        <v>[Totem des Mahlstroms]</v>
+      <c r="D23" t="s">
+        <v>694</v>
       </c>
       <c r="E23">
         <v>30023</v>
@@ -8264,9 +9046,8 @@
       <c r="C24" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D24" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30245","[Gamaschen des bezwungenen Champions]")</f>
-        <v>[Gamaschen des bezwungenen Champions]</v>
+      <c r="D24" t="s">
+        <v>687</v>
       </c>
       <c r="E24">
         <v>30245</v>
@@ -8289,9 +9070,8 @@
       <c r="K24" t="s">
         <v>26</v>
       </c>
-      <c r="L24" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=24262","[Hose des Zauberschlags]")</f>
-        <v>[Hose des Zauberschlags]</v>
+      <c r="L24" t="s">
+        <v>818</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -8323,9 +9103,8 @@
       <c r="C25" s="2">
         <v>0.90902777777777777</v>
       </c>
-      <c r="D25" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30720","[Flechte der Schlangenschlinge]")</f>
-        <v>[Flechte der Schlangenschlinge]</v>
+      <c r="D25" t="s">
+        <v>695</v>
       </c>
       <c r="E25">
         <v>30720</v>
@@ -8348,13 +9127,11 @@
       <c r="K25" t="s">
         <v>26</v>
       </c>
-      <c r="L25" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29370","[Ikone des Silberwappens]")</f>
-        <v>[Ikone des Silberwappens]</v>
-      </c>
-      <c r="M25" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28785","[Der Blitzkondensator]")</f>
-        <v>[Der Blitzkondensator]</v>
+      <c r="L25" t="s">
+        <v>819</v>
+      </c>
+      <c r="M25" t="s">
+        <v>932</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -8389,9 +9166,8 @@
       <c r="C26" s="2">
         <v>0.98055555555555551</v>
       </c>
-      <c r="D26" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30109","[Ring der Endlosschleife]")</f>
-        <v>[Ring der Endlosschleife]</v>
+      <c r="D26" t="s">
+        <v>696</v>
       </c>
       <c r="E26">
         <v>30109</v>
@@ -8414,13 +9190,11 @@
       <c r="K26" t="s">
         <v>53</v>
       </c>
-      <c r="L26" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28793","[Band des purpurroten Furors]")</f>
-        <v>[Band des purpurroten Furors]</v>
-      </c>
-      <c r="M26" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28753","[Ring der Wiederkehr]")</f>
-        <v>[Ring der Wiederkehr]</v>
+      <c r="L26" t="s">
+        <v>820</v>
+      </c>
+      <c r="M26" t="s">
+        <v>933</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -8455,9 +9229,8 @@
       <c r="C27" s="2">
         <v>0.97916666666666663</v>
       </c>
-      <c r="D27" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30244","[Helm des bezwungenen Helden]")</f>
-        <v>[Helm des bezwungenen Helden]</v>
+      <c r="D27" t="s">
+        <v>686</v>
       </c>
       <c r="E27">
         <v>30244</v>
@@ -8480,9 +9253,8 @@
       <c r="K27" t="s">
         <v>53</v>
       </c>
-      <c r="L27" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28963","[Krone des Herzens der Leere]")</f>
-        <v>[Krone des Herzens der Leere]</v>
+      <c r="L27" t="s">
+        <v>808</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -8514,9 +9286,8 @@
       <c r="C28" s="2">
         <v>0.90069444444444446</v>
       </c>
-      <c r="D28" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30029","[Bark-Gloves of Ancient Wisdom]")</f>
-        <v>[Bark-Gloves of Ancient Wisdom]</v>
+      <c r="D28" t="s">
+        <v>697</v>
       </c>
       <c r="E28">
         <v>30029</v>
@@ -8539,9 +9310,8 @@
       <c r="K28" t="s">
         <v>102</v>
       </c>
-      <c r="L28" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27536","[Hallowed Handwraps]")</f>
-        <v>[Hallowed Handwraps]</v>
+      <c r="L28" t="s">
+        <v>821</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -8579,9 +9349,8 @@
       <c r="C29" s="2">
         <v>0.90138888888888891</v>
       </c>
-      <c r="D29" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29949","[Arcanite Steam-Pistol]")</f>
-        <v>[Arcanite Steam-Pistol]</v>
+      <c r="D29" t="s">
+        <v>698</v>
       </c>
       <c r="E29">
         <v>29949</v>
@@ -8604,9 +9373,8 @@
       <c r="K29" t="s">
         <v>102</v>
       </c>
-      <c r="L29" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28772","[Sunfury Bow of the Phoenix]")</f>
-        <v>[Sunfury Bow of the Phoenix]</v>
+      <c r="L29" t="s">
+        <v>822</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -8641,9 +9409,8 @@
       <c r="C30" s="2">
         <v>0.91111111111111109</v>
       </c>
-      <c r="D30" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29983","[Fel-Steel Warhelm]")</f>
-        <v>[Fel-Steel Warhelm]</v>
+      <c r="D30" t="s">
+        <v>699</v>
       </c>
       <c r="E30">
         <v>29983</v>
@@ -8666,9 +9433,8 @@
       <c r="K30" t="s">
         <v>102</v>
       </c>
-      <c r="L30" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29011","[Warbringer Greathelm]")</f>
-        <v>[Warbringer Greathelm]</v>
+      <c r="L30" t="s">
+        <v>823</v>
       </c>
       <c r="N30">
         <v>3</v>
@@ -8703,9 +9469,8 @@
       <c r="C31" s="2">
         <v>0.92986111111111114</v>
       </c>
-      <c r="D31" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30249","[Pauldrons of the Vanquished Defender]")</f>
-        <v>[Pauldrons of the Vanquished Defender]</v>
+      <c r="D31" t="s">
+        <v>700</v>
       </c>
       <c r="E31">
         <v>30249</v>
@@ -8728,9 +9493,8 @@
       <c r="K31" t="s">
         <v>102</v>
       </c>
-      <c r="L31" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29016","[Warbringer Shoulderguards]")</f>
-        <v>[Warbringer Shoulderguards]</v>
+      <c r="L31" t="s">
+        <v>824</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -8762,9 +9526,8 @@
       <c r="C32" s="2">
         <v>0.90069444444444446</v>
       </c>
-      <c r="D32" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29918","[Mindstorm Wristbands]")</f>
-        <v>[Mindstorm Wristbands]</v>
+      <c r="D32" t="s">
+        <v>701</v>
       </c>
       <c r="E32">
         <v>29918</v>
@@ -8787,9 +9550,8 @@
       <c r="K32" t="s">
         <v>102</v>
       </c>
-      <c r="L32" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28453","[Bracers of the White Stag]")</f>
-        <v>[Bracers of the White Stag]</v>
+      <c r="L32" t="s">
+        <v>825</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -8824,9 +9586,8 @@
       <c r="C33" s="2">
         <v>0.93055555555555558</v>
       </c>
-      <c r="D33" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32267","[Boots of the Resilient]")</f>
-        <v>[Boots of the Resilient]</v>
+      <c r="D33" t="s">
+        <v>702</v>
       </c>
       <c r="E33">
         <v>32267</v>
@@ -8849,9 +9610,8 @@
       <c r="K33" t="s">
         <v>102</v>
       </c>
-      <c r="L33" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29254","[Boots of the Righteous Path]")</f>
-        <v>[Boots of the Righteous Path]</v>
+      <c r="L33" t="s">
+        <v>826</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -8886,9 +9646,8 @@
       <c r="C34" s="2">
         <v>0.93055555555555558</v>
       </c>
-      <c r="D34" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30028","[Seventh Ring of the Tirisfalen]")</f>
-        <v>[Seventh Ring of the Tirisfalen]</v>
+      <c r="D34" t="s">
+        <v>703</v>
       </c>
       <c r="E34">
         <v>30028</v>
@@ -8911,13 +9670,11 @@
       <c r="K34" t="s">
         <v>102</v>
       </c>
-      <c r="L34" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29279","[Violet Signet of the Great Protector]")</f>
-        <v>[Violet Signet of the Great Protector]</v>
-      </c>
-      <c r="M34" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29384","[Ring of Unyielding Force]")</f>
-        <v>[Ring of Unyielding Force]</v>
+      <c r="L34" t="s">
+        <v>827</v>
+      </c>
+      <c r="M34" t="s">
+        <v>934</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -8952,9 +9709,8 @@
       <c r="C35" s="2">
         <v>0.90208333333333335</v>
       </c>
-      <c r="D35" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29924","[Netherbane]")</f>
-        <v>[Netherbane]</v>
+      <c r="D35" t="s">
+        <v>704</v>
       </c>
       <c r="E35">
         <v>29924</v>
@@ -8977,13 +9733,11 @@
       <c r="K35" t="s">
         <v>102</v>
       </c>
-      <c r="L35" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28438","[Dragonmaw]")</f>
-        <v>[Dragonmaw]</v>
-      </c>
-      <c r="M35" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=23542","[Fel Edged Battleaxe]")</f>
-        <v>[Fel Edged Battleaxe]</v>
+      <c r="L35" t="s">
+        <v>828</v>
+      </c>
+      <c r="M35" t="s">
+        <v>935</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -9018,9 +9772,8 @@
       <c r="C36" s="2">
         <v>0.93055555555555558</v>
       </c>
-      <c r="D36" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29950","[Greaves of the Bloodwarder]")</f>
-        <v>[Greaves of the Bloodwarder]</v>
+      <c r="D36" t="s">
+        <v>705</v>
       </c>
       <c r="E36">
         <v>29950</v>
@@ -9043,9 +9796,8 @@
       <c r="K36" t="s">
         <v>102</v>
       </c>
-      <c r="L36" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29022","[Warbringer Greaves]")</f>
-        <v>[Warbringer Greaves]</v>
+      <c r="L36" t="s">
+        <v>829</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -9080,9 +9832,8 @@
       <c r="C37" s="2">
         <v>0.93125000000000002</v>
       </c>
-      <c r="D37" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30322","[Plans: Red Belt of Battle]")</f>
-        <v>[Plans: Red Belt of Battle]</v>
+      <c r="D37" t="s">
+        <v>706</v>
       </c>
       <c r="E37">
         <v>30322</v>
@@ -9135,9 +9886,8 @@
       <c r="C38" s="2">
         <v>0.92986111111111114</v>
       </c>
-      <c r="D38" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30250","[Pauldrons of the Vanquished Hero]")</f>
-        <v>[Pauldrons of the Vanquished Hero]</v>
+      <c r="D38" t="s">
+        <v>707</v>
       </c>
       <c r="E38">
         <v>30250</v>
@@ -9160,9 +9910,8 @@
       <c r="K38" t="s">
         <v>102</v>
       </c>
-      <c r="L38" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29079","[Pauldrons of the Aldor]")</f>
-        <v>[Pauldrons of the Aldor]</v>
+      <c r="L38" t="s">
+        <v>830</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -9194,9 +9943,8 @@
       <c r="C39" s="2">
         <v>0.90069444444444446</v>
       </c>
-      <c r="D39" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30029","[Bark-Gloves of Ancient Wisdom]")</f>
-        <v>[Bark-Gloves of Ancient Wisdom]</v>
+      <c r="D39" t="s">
+        <v>697</v>
       </c>
       <c r="E39">
         <v>30029</v>
@@ -9219,9 +9967,8 @@
       <c r="K39" t="s">
         <v>102</v>
       </c>
-      <c r="L39" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28521","[Mitts of the Treemender]")</f>
-        <v>[Mitts of the Treemender]</v>
+      <c r="L39" t="s">
+        <v>831</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -9256,9 +10003,8 @@
       <c r="C40" s="2">
         <v>0.92986111111111114</v>
       </c>
-      <c r="D40" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30249","[Pauldrons of the Vanquished Defender]")</f>
-        <v>[Pauldrons of the Vanquished Defender]</v>
+      <c r="D40" t="s">
+        <v>700</v>
       </c>
       <c r="E40">
         <v>30249</v>
@@ -9281,9 +10027,8 @@
       <c r="K40" t="s">
         <v>102</v>
       </c>
-      <c r="L40" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29089","[Shoulderguards of Malorne]")</f>
-        <v>[Shoulderguards of Malorne]</v>
+      <c r="L40" t="s">
+        <v>832</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -9315,9 +10060,8 @@
       <c r="C41" s="2">
         <v>0.93125000000000002</v>
       </c>
-      <c r="D41" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30449","[Void Star Talisman]")</f>
-        <v>[Void Star Talisman]</v>
+      <c r="D41" t="s">
+        <v>708</v>
       </c>
       <c r="E41">
         <v>30449</v>
@@ -9340,13 +10084,11 @@
       <c r="K41" t="s">
         <v>102</v>
       </c>
-      <c r="L41" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29132","[Scryer's Bloodgem]")</f>
-        <v>[Scryer's Bloodgem]</v>
-      </c>
-      <c r="M41" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27683","[Quagmirran's Eye]")</f>
-        <v>[Quagmirran's Eye]</v>
+      <c r="L41" t="s">
+        <v>833</v>
+      </c>
+      <c r="M41" t="s">
+        <v>936</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -9381,9 +10123,8 @@
       <c r="C42" s="2">
         <v>0.87638888888888888</v>
       </c>
-      <c r="D42" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30055","[Schulterpolster des Fremden]")</f>
-        <v>[Schulterpolster des Fremden]</v>
+      <c r="D42" t="s">
+        <v>709</v>
       </c>
       <c r="E42">
         <v>30055</v>
@@ -9406,9 +10147,8 @@
       <c r="K42" t="s">
         <v>129</v>
       </c>
-      <c r="L42" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29023","[Schulterplatten des Kriegshetzers]")</f>
-        <v>[Schulterplatten des Kriegshetzers]</v>
+      <c r="L42" t="s">
+        <v>834</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -9443,9 +10183,8 @@
       <c r="C43" s="2">
         <v>0.89236111111111116</v>
       </c>
-      <c r="D43" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30246","[Gamaschen des bezwungenen Verteidigers]")</f>
-        <v>[Gamaschen des bezwungenen Verteidigers]</v>
+      <c r="D43" t="s">
+        <v>710</v>
       </c>
       <c r="E43">
         <v>30246</v>
@@ -9468,9 +10207,8 @@
       <c r="K43" t="s">
         <v>129</v>
       </c>
-      <c r="L43" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29022","[Schienbeinschützer des Kriegshetzers]")</f>
-        <v>[Schienbeinschützer des Kriegshetzers]</v>
+      <c r="L43" t="s">
+        <v>835</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -9502,9 +10240,8 @@
       <c r="C44" s="2">
         <v>0.89236111111111116</v>
       </c>
-      <c r="D44" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30246","[Gamaschen des bezwungenen Verteidigers]")</f>
-        <v>[Gamaschen des bezwungenen Verteidigers]</v>
+      <c r="D44" t="s">
+        <v>710</v>
       </c>
       <c r="E44">
         <v>30246</v>
@@ -9527,9 +10264,8 @@
       <c r="K44" t="s">
         <v>129</v>
       </c>
-      <c r="L44" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=24359","[Fürstliche Herrschaftgamaschen]")</f>
-        <v>[Fürstliche Herrschaftgamaschen]</v>
+      <c r="L44" t="s">
+        <v>836</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -9561,9 +10297,8 @@
       <c r="C45" s="2">
         <v>0.88055555555555554</v>
       </c>
-      <c r="D45" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30240","[Handschuhe des bezwungenen Verteidigers]")</f>
-        <v>[Handschuhe des bezwungenen Verteidigers]</v>
+      <c r="D45" t="s">
+        <v>711</v>
       </c>
       <c r="E45">
         <v>30240</v>
@@ -9586,9 +10321,8 @@
       <c r="K45" t="s">
         <v>129</v>
       </c>
-      <c r="L45" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28506","[Handschuhe der geschickten Manipulation]")</f>
-        <v>[Handschuhe der geschickten Manipulation]</v>
+      <c r="L45" t="s">
+        <v>837</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -9620,9 +10354,8 @@
       <c r="C46" s="2">
         <v>0.87916666666666665</v>
       </c>
-      <c r="D46" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30099","[Ausgefranster Strick des Ertrunkenen]")</f>
-        <v>[Ausgefranster Strick des Ertrunkenen]</v>
+      <c r="D46" t="s">
+        <v>712</v>
       </c>
       <c r="E46">
         <v>30099</v>
@@ -9645,9 +10378,8 @@
       <c r="K46" t="s">
         <v>129</v>
       </c>
-      <c r="L46" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30022","[Anhänger des Gefahrvollen]")</f>
-        <v>[Anhänger des Gefahrvollen]</v>
+      <c r="L46" t="s">
+        <v>838</v>
       </c>
       <c r="N46">
         <v>4</v>
@@ -9682,9 +10414,8 @@
       <c r="C47" s="2">
         <v>0.88055555555555554</v>
       </c>
-      <c r="D47" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30096","[Gurt des Unverwundbaren]")</f>
-        <v>[Gurt des Unverwundbaren]</v>
+      <c r="D47" t="s">
+        <v>713</v>
       </c>
       <c r="E47">
         <v>30096</v>
@@ -9707,9 +10438,8 @@
       <c r="K47" t="s">
         <v>129</v>
       </c>
-      <c r="L47" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28385","[Plattengürtel des Kriegsherren]")</f>
-        <v>[Plattengürtel des Kriegsherren]</v>
+      <c r="L47" t="s">
+        <v>839</v>
       </c>
       <c r="N47">
         <v>4</v>
@@ -9744,9 +10474,8 @@
       <c r="C48" s="2">
         <v>0.87986111111111109</v>
       </c>
-      <c r="D48" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30239","[Handschuhe des bezwungenen Champions]")</f>
-        <v>[Handschuhe des bezwungenen Champions]</v>
+      <c r="D48" t="s">
+        <v>691</v>
       </c>
       <c r="E48">
         <v>30239</v>
@@ -9769,9 +10498,8 @@
       <c r="K48" t="s">
         <v>129</v>
       </c>
-      <c r="L48" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28507","[Handlappen des Gedankenflusses]")</f>
-        <v>[Handlappen des Gedankenflusses]</v>
+      <c r="L48" t="s">
+        <v>840</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -9803,9 +10531,8 @@
       <c r="C49" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D49" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30079","[Schulterpolster der Illidari]")</f>
-        <v>[Schulterpolster der Illidari]</v>
+      <c r="D49" t="s">
+        <v>714</v>
       </c>
       <c r="E49">
         <v>30079</v>
@@ -9828,9 +10555,8 @@
       <c r="K49" t="s">
         <v>129</v>
       </c>
-      <c r="L49" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29095","[Malornes Schulterstücke]")</f>
-        <v>[Malornes Schulterstücke]</v>
+      <c r="L49" t="s">
+        <v>841</v>
       </c>
       <c r="N49" t="s">
         <v>137</v>
@@ -9865,9 +10591,8 @@
       <c r="C50" s="2">
         <v>0.87708333333333333</v>
       </c>
-      <c r="D50" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=33054","[Das Siegel von Danzalar]")</f>
-        <v>[Das Siegel von Danzalar]</v>
+      <c r="D50" t="s">
+        <v>715</v>
       </c>
       <c r="E50">
         <v>33054</v>
@@ -9890,13 +10615,11 @@
       <c r="K50" t="s">
         <v>129</v>
       </c>
-      <c r="L50" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29126","[Siegel des Sehers]")</f>
-        <v>[Siegel des Sehers]</v>
-      </c>
-      <c r="M50" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29172","[Ashyens Gabe]")</f>
-        <v>[Ashyens Gabe]</v>
+      <c r="L50" t="s">
+        <v>842</v>
+      </c>
+      <c r="M50" t="s">
+        <v>937</v>
       </c>
       <c r="N50">
         <v>3</v>
@@ -9931,9 +10654,8 @@
       <c r="C51" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D51" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30082","[Kralle von Azshara]")</f>
-        <v>[Kralle von Azshara]</v>
+      <c r="D51" t="s">
+        <v>716</v>
       </c>
       <c r="E51">
         <v>30082</v>
@@ -9956,13 +10678,11 @@
       <c r="K51" t="s">
         <v>129</v>
       </c>
-      <c r="L51" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28438","[Drachenmal]")</f>
-        <v>[Drachenmal]</v>
-      </c>
-      <c r="M51" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29924","[Netherbann]")</f>
-        <v>[Netherbann]</v>
+      <c r="L51" t="s">
+        <v>843</v>
+      </c>
+      <c r="M51" t="s">
+        <v>938</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -9997,9 +10717,8 @@
       <c r="C52" s="2">
         <v>0.87986111111111109</v>
       </c>
-      <c r="D52" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30241","[Handschuhe des bezwungenen Helden]")</f>
-        <v>[Handschuhe des bezwungenen Helden]</v>
+      <c r="D52" t="s">
+        <v>675</v>
       </c>
       <c r="E52">
         <v>30241</v>
@@ -10022,9 +10741,8 @@
       <c r="K52" t="s">
         <v>129</v>
       </c>
-      <c r="L52" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29080","[Handschuhe der Aldor]")</f>
-        <v>[Handschuhe der Aldor]</v>
+      <c r="L52" t="s">
+        <v>844</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -10056,9 +10774,8 @@
       <c r="C53" s="2">
         <v>0.87708333333333333</v>
       </c>
-      <c r="D53" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32516","[Wickeltücher der Läuterung]")</f>
-        <v>[Wickeltücher der Läuterung]</v>
+      <c r="D53" t="s">
+        <v>717</v>
       </c>
       <c r="E53">
         <v>32516</v>
@@ -10081,9 +10798,8 @@
       <c r="K53" t="s">
         <v>129</v>
       </c>
-      <c r="L53" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28511","[Bänder des Innewohnens]")</f>
-        <v>[Bänder des Innewohnens]</v>
+      <c r="L53" t="s">
+        <v>845</v>
       </c>
       <c r="N53">
         <v>3</v>
@@ -10118,9 +10834,8 @@
       <c r="C54" s="2">
         <v>0.88194444444444442</v>
       </c>
-      <c r="D54" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30247","[Gamaschen des bezwungenen Helden]")</f>
-        <v>[Gamaschen des bezwungenen Helden]</v>
+      <c r="D54" t="s">
+        <v>718</v>
       </c>
       <c r="E54">
         <v>30247</v>
@@ -10143,9 +10858,8 @@
       <c r="K54" t="s">
         <v>129</v>
       </c>
-      <c r="L54" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=24262","[Hose des Zauberschlags]")</f>
-        <v>[Hose des Zauberschlags]</v>
+      <c r="L54" t="s">
+        <v>818</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -10177,9 +10891,8 @@
       <c r="C55" s="2">
         <v>0.87708333333333333</v>
       </c>
-      <c r="D55" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30060","[Stiefel des mühelosen Kampfes]")</f>
-        <v>[Stiefel des mühelosen Kampfes]</v>
+      <c r="D55" t="s">
+        <v>719</v>
       </c>
       <c r="E55">
         <v>30060</v>
@@ -10202,9 +10915,8 @@
       <c r="K55" t="s">
         <v>129</v>
       </c>
-      <c r="L55" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30674","[Zierhuts verschwundene Treter]")</f>
-        <v>[Zierhuts verschwundene Treter]</v>
+      <c r="L55" t="s">
+        <v>846</v>
       </c>
       <c r="N55">
         <v>3</v>
@@ -10239,9 +10951,8 @@
       <c r="C56" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D56" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30084","[Schulterstücke der Argentumschildwache]")</f>
-        <v>[Schulterstücke der Argentumschildwache]</v>
+      <c r="D56" t="s">
+        <v>720</v>
       </c>
       <c r="E56">
         <v>30084</v>
@@ -10264,9 +10975,8 @@
       <c r="K56" t="s">
         <v>129</v>
       </c>
-      <c r="L56" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27775","[Geheiligte Schulterstücke]")</f>
-        <v>[Geheiligte Schulterstücke]</v>
+      <c r="L56" t="s">
+        <v>847</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -10304,9 +11014,8 @@
       <c r="C57" s="2">
         <v>0.89236111111111116</v>
       </c>
-      <c r="D57" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29992","[Royal Cloak of the Sunstriders]")</f>
-        <v>[Royal Cloak of the Sunstriders]</v>
+      <c r="D57" t="s">
+        <v>721</v>
       </c>
       <c r="E57">
         <v>29992</v>
@@ -10329,9 +11038,8 @@
       <c r="K57" t="s">
         <v>102</v>
       </c>
-      <c r="L57" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=25039","[Farseer Cloak of Shadow Wrath]")</f>
-        <v>[Farseer Cloak of Shadow Wrath]</v>
+      <c r="L57" t="s">
+        <v>848</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -10366,9 +11074,8 @@
       <c r="C58" s="2">
         <v>0.89583333333333337</v>
       </c>
-      <c r="D58" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29984","[Girdle of Zaetar]")</f>
-        <v>[Girdle of Zaetar]</v>
+      <c r="D58" t="s">
+        <v>722</v>
       </c>
       <c r="E58">
         <v>29984</v>
@@ -10391,9 +11098,8 @@
       <c r="K58" t="s">
         <v>102</v>
       </c>
-      <c r="L58" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28652","[Cincture of Will]")</f>
-        <v>[Cincture of Will]</v>
+      <c r="L58" t="s">
+        <v>849</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -10431,9 +11137,8 @@
       <c r="C59" s="2">
         <v>0.89375000000000004</v>
       </c>
-      <c r="D59" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30238","[Chestguard of the Vanquished Hero]")</f>
-        <v>[Chestguard of the Vanquished Hero]</v>
+      <c r="D59" t="s">
+        <v>723</v>
       </c>
       <c r="E59">
         <v>30238</v>
@@ -10456,9 +11161,8 @@
       <c r="K59" t="s">
         <v>102</v>
       </c>
-      <c r="L59" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28228","[Beast Lord Cuirass]")</f>
-        <v>[Beast Lord Cuirass]</v>
+      <c r="L59" t="s">
+        <v>850</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -10490,9 +11194,8 @@
       <c r="C60" s="2">
         <v>0.90069444444444446</v>
       </c>
-      <c r="D60" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29951","[Star-Strider Boots]")</f>
-        <v>[Star-Strider Boots]</v>
+      <c r="D60" t="s">
+        <v>724</v>
       </c>
       <c r="E60">
         <v>29951</v>
@@ -10515,9 +11218,8 @@
       <c r="K60" t="s">
         <v>102</v>
       </c>
-      <c r="L60" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28545","[Edgewalker Longboots]")</f>
-        <v>[Edgewalker Longboots]</v>
+      <c r="L60" t="s">
+        <v>851</v>
       </c>
       <c r="N60">
         <v>2</v>
@@ -10552,9 +11254,8 @@
       <c r="C61" s="2">
         <v>0.89513888888888893</v>
       </c>
-      <c r="D61" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29947","[Gloves of the Searing Grip]")</f>
-        <v>[Gloves of the Searing Grip]</v>
+      <c r="D61" t="s">
+        <v>725</v>
       </c>
       <c r="E61">
         <v>29947</v>
@@ -10577,9 +11278,8 @@
       <c r="K61" t="s">
         <v>102</v>
       </c>
-      <c r="L61" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30644","[Grips of Deftness]")</f>
-        <v>[Grips of Deftness]</v>
+      <c r="L61" t="s">
+        <v>852</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -10614,9 +11314,8 @@
       <c r="C62" s="2">
         <v>0.89166666666666672</v>
       </c>
-      <c r="D62" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30249","[Pauldrons of the Vanquished Defender]")</f>
-        <v>[Pauldrons of the Vanquished Defender]</v>
+      <c r="D62" t="s">
+        <v>700</v>
       </c>
       <c r="E62">
         <v>30249</v>
@@ -10639,9 +11338,8 @@
       <c r="K62" t="s">
         <v>102</v>
       </c>
-      <c r="L62" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29054","[Light-Mantle of the Incarnate]")</f>
-        <v>[Light-Mantle of the Incarnate]</v>
+      <c r="L62" t="s">
+        <v>853</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -10673,9 +11371,8 @@
       <c r="C63" s="2">
         <v>0.89375000000000004</v>
       </c>
-      <c r="D63" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30250","[Pauldrons of the Vanquished Hero]")</f>
-        <v>[Pauldrons of the Vanquished Hero]</v>
+      <c r="D63" t="s">
+        <v>707</v>
       </c>
       <c r="E63">
         <v>30250</v>
@@ -10698,9 +11395,8 @@
       <c r="K63" t="s">
         <v>102</v>
       </c>
-      <c r="L63" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=25854","[Gladiator's Silk Amice]")</f>
-        <v>[Gladiator's Silk Amice]</v>
+      <c r="L63" t="s">
+        <v>854</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -10732,9 +11428,8 @@
       <c r="C64" s="2">
         <v>0.89375000000000004</v>
       </c>
-      <c r="D64" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30238","[Chestguard of the Vanquished Hero]")</f>
-        <v>[Chestguard of the Vanquished Hero]</v>
+      <c r="D64" t="s">
+        <v>723</v>
       </c>
       <c r="E64">
         <v>30238</v>
@@ -10757,9 +11452,8 @@
       <c r="K64" t="s">
         <v>102</v>
       </c>
-      <c r="L64" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29077","[Vestments of the Aldor]")</f>
-        <v>[Vestments of the Aldor]</v>
+      <c r="L64" t="s">
+        <v>855</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -10791,9 +11485,8 @@
       <c r="C65" s="2">
         <v>0.9</v>
       </c>
-      <c r="D65" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29972","[Trousers of the Astromancer]")</f>
-        <v>[Trousers of the Astromancer]</v>
+      <c r="D65" t="s">
+        <v>726</v>
       </c>
       <c r="E65">
         <v>29972</v>
@@ -10816,9 +11509,8 @@
       <c r="K65" t="s">
         <v>102</v>
       </c>
-      <c r="L65" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29078","[Legwraps of the Aldor]")</f>
-        <v>[Legwraps of the Aldor]</v>
+      <c r="L65" t="s">
+        <v>856</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -10853,9 +11545,8 @@
       <c r="C66" s="2">
         <v>0.89097222222222228</v>
       </c>
-      <c r="D66" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30249","[Pauldrons of the Vanquished Defender]")</f>
-        <v>[Pauldrons of the Vanquished Defender]</v>
+      <c r="D66" t="s">
+        <v>700</v>
       </c>
       <c r="E66">
         <v>30249</v>
@@ -10878,9 +11569,8 @@
       <c r="K66" t="s">
         <v>102</v>
       </c>
-      <c r="L66" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29100","[Mantle of Malorne]")</f>
-        <v>[Mantle of Malorne]</v>
+      <c r="L66" t="s">
+        <v>857</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -10912,9 +11602,8 @@
       <c r="C67" s="2">
         <v>0.8930555555555556</v>
       </c>
-      <c r="D67" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30237","[Chestguard of the Vanquished Defender]")</f>
-        <v>[Chestguard of the Vanquished Defender]</v>
+      <c r="D67" t="s">
+        <v>727</v>
       </c>
       <c r="E67">
         <v>30237</v>
@@ -10937,9 +11626,8 @@
       <c r="K67" t="s">
         <v>102</v>
       </c>
-      <c r="L67" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29019","[Warbringer Breastplate]")</f>
-        <v>[Warbringer Breastplate]</v>
+      <c r="L67" t="s">
+        <v>858</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -10971,9 +11659,8 @@
       <c r="C68" s="2">
         <v>0.89722222222222225</v>
       </c>
-      <c r="D68" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29920","[Phoenix-Ring of Rebirth]")</f>
-        <v>[Phoenix-Ring of Rebirth]</v>
+      <c r="D68" t="s">
+        <v>728</v>
       </c>
       <c r="E68">
         <v>29920</v>
@@ -10996,13 +11683,11 @@
       <c r="K68" t="s">
         <v>102</v>
       </c>
-      <c r="L68" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28394","[Ryngo's Band of Ingenuity]")</f>
-        <v>[Ryngo's Band of Ingenuity]</v>
-      </c>
-      <c r="M68" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29287","[Violet Signet of the Archmage]")</f>
-        <v>[Violet Signet of the Archmage]</v>
+      <c r="L68" t="s">
+        <v>859</v>
+      </c>
+      <c r="M68" t="s">
+        <v>939</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -11037,9 +11722,8 @@
       <c r="C69" s="2">
         <v>0.90208333333333335</v>
       </c>
-      <c r="D69" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30026","[Bands of the Celestial Archer]")</f>
-        <v>[Bands of the Celestial Archer]</v>
+      <c r="D69" t="s">
+        <v>729</v>
       </c>
       <c r="E69">
         <v>30026</v>
@@ -11062,9 +11746,8 @@
       <c r="K69" t="s">
         <v>102</v>
       </c>
-      <c r="L69" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28454","[Stalker's War Bands]")</f>
-        <v>[Stalker's War Bands]</v>
+      <c r="L69" t="s">
+        <v>860</v>
       </c>
       <c r="N69">
         <v>3</v>
@@ -11099,9 +11782,8 @@
       <c r="C70" s="2">
         <v>0.9</v>
       </c>
-      <c r="D70" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30447","[Tome of Fiery Redemption]")</f>
-        <v>[Tome of Fiery Redemption]</v>
+      <c r="D70" t="s">
+        <v>730</v>
       </c>
       <c r="E70">
         <v>30447</v>
@@ -11124,13 +11806,11 @@
       <c r="K70" t="s">
         <v>102</v>
       </c>
-      <c r="L70" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29370","[Icon of the Silver Crescent]")</f>
-        <v>[Icon of the Silver Crescent]</v>
-      </c>
-      <c r="M70" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27529","[Figurine of the Colossus]")</f>
-        <v>[Figurine of the Colossus]</v>
+      <c r="L70" t="s">
+        <v>861</v>
+      </c>
+      <c r="M70" t="s">
+        <v>940</v>
       </c>
       <c r="N70" t="s">
         <v>64</v>
@@ -11165,9 +11845,8 @@
       <c r="C71" s="2">
         <v>0.90069444444444446</v>
       </c>
-      <c r="D71" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32405","[Verdant Sphere]")</f>
-        <v>[Verdant Sphere]</v>
+      <c r="D71" t="s">
+        <v>731</v>
       </c>
       <c r="E71">
         <v>32405</v>
@@ -11220,9 +11899,8 @@
       <c r="C72" s="2">
         <v>0.89722222222222225</v>
       </c>
-      <c r="D72" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29962","[Heartrazor]")</f>
-        <v>[Heartrazor]</v>
+      <c r="D72" t="s">
+        <v>732</v>
       </c>
       <c r="E72">
         <v>29962</v>
@@ -11245,13 +11923,11 @@
       <c r="K72" t="s">
         <v>102</v>
       </c>
-      <c r="L72" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28295","[Gladiator's Slicer]")</f>
-        <v>[Gladiator's Slicer]</v>
-      </c>
-      <c r="M72" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28189","[Latro's Shifting Sword]")</f>
-        <v>[Latro's Shifting Sword]</v>
+      <c r="L72" t="s">
+        <v>862</v>
+      </c>
+      <c r="M72" t="s">
+        <v>941</v>
       </c>
       <c r="N72">
         <v>4</v>
@@ -11286,9 +11962,8 @@
       <c r="C73" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D73" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30029","[Bark-Gloves of Ancient Wisdom]")</f>
-        <v>[Bark-Gloves of Ancient Wisdom]</v>
+      <c r="D73" t="s">
+        <v>697</v>
       </c>
       <c r="E73">
         <v>30029</v>
@@ -11311,9 +11986,8 @@
       <c r="K73" t="s">
         <v>102</v>
       </c>
-      <c r="L73" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28521","[Mitts of the Treemender]")</f>
-        <v>[Mitts of the Treemender]</v>
+      <c r="L73" t="s">
+        <v>831</v>
       </c>
       <c r="N73">
         <v>3</v>
@@ -11348,9 +12022,8 @@
       <c r="C74" s="2">
         <v>0.84583333333333333</v>
       </c>
-      <c r="D74" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30247","[Gamaschen des bezwungenen Helden]")</f>
-        <v>[Gamaschen des bezwungenen Helden]</v>
+      <c r="D74" t="s">
+        <v>718</v>
       </c>
       <c r="E74">
         <v>30247</v>
@@ -11373,9 +12046,8 @@
       <c r="K74" t="s">
         <v>34</v>
       </c>
-      <c r="L74" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=24262","[Hose des Zauberschlags]")</f>
-        <v>[Hose des Zauberschlags]</v>
+      <c r="L74" t="s">
+        <v>818</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -11407,9 +12079,8 @@
       <c r="C75" s="2">
         <v>0.85833333333333328</v>
       </c>
-      <c r="D75" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30075","[Rauer Brustharnisch der Uralten]")</f>
-        <v>[Rauer Brustharnisch der Uralten]</v>
+      <c r="D75" t="s">
+        <v>733</v>
       </c>
       <c r="E75">
         <v>30075</v>
@@ -11432,9 +12103,8 @@
       <c r="K75" t="s">
         <v>129</v>
       </c>
-      <c r="L75" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28600","[Wams des Steingeästs]")</f>
-        <v>[Wams des Steingeästs]</v>
+      <c r="L75" t="s">
+        <v>863</v>
       </c>
       <c r="N75">
         <v>3</v>
@@ -11469,9 +12139,8 @@
       <c r="C76" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D76" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28822","[Zahn von Gruul]")</f>
-        <v>[Zahn von Gruul]</v>
+      <c r="D76" t="s">
+        <v>734</v>
       </c>
       <c r="E76">
         <v>28822</v>
@@ -11494,9 +12163,8 @@
       <c r="K76" t="s">
         <v>173</v>
       </c>
-      <c r="L76" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29374","[Halskette der ewigen Hoffnung]")</f>
-        <v>[Halskette der ewigen Hoffnung]</v>
+      <c r="L76" t="s">
+        <v>864</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -11531,9 +12199,8 @@
       <c r="C77" s="2">
         <v>0.87777777777777777</v>
       </c>
-      <c r="D77" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30244","[Helm des bezwungenen Helden]")</f>
-        <v>[Helm des bezwungenen Helden]</v>
+      <c r="D77" t="s">
+        <v>686</v>
       </c>
       <c r="E77">
         <v>30244</v>
@@ -11556,9 +12223,8 @@
       <c r="K77" t="s">
         <v>53</v>
       </c>
-      <c r="L77" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28275","[Helm des Wildtierfürsten]")</f>
-        <v>[Helm des Wildtierfürsten]</v>
+      <c r="L77" t="s">
+        <v>865</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -11590,9 +12256,8 @@
       <c r="C78" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D78" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29762","[Schulterstücke des gefallenen Helden]")</f>
-        <v>[Schulterstücke des gefallenen Helden]</v>
+      <c r="D78" t="s">
+        <v>735</v>
       </c>
       <c r="E78">
         <v>29762</v>
@@ -11615,9 +12280,8 @@
       <c r="K78" t="s">
         <v>173</v>
       </c>
-      <c r="L78" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27801","[Mantelung des Wildtierfürsten]")</f>
-        <v>[Mantelung des Wildtierfürsten]</v>
+      <c r="L78" t="s">
+        <v>866</v>
       </c>
       <c r="N78">
         <v>4</v>
@@ -11649,9 +12313,8 @@
       <c r="C79" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D79" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29765","[Gamaschen des gefallenen Helden]")</f>
-        <v>[Gamaschen des gefallenen Helden]</v>
+      <c r="D79" t="s">
+        <v>736</v>
       </c>
       <c r="E79">
         <v>29765</v>
@@ -11674,9 +12337,8 @@
       <c r="K79" t="s">
         <v>173</v>
       </c>
-      <c r="L79" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27874","[Gamaschen des Wildtierfürsten]")</f>
-        <v>[Gamaschen des Wildtierfürsten]</v>
+      <c r="L79" t="s">
+        <v>867</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -11708,9 +12370,8 @@
       <c r="C80" s="2">
         <v>0.90555555555555556</v>
       </c>
-      <c r="D80" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29765","[Gamaschen des gefallenen Helden]")</f>
-        <v>[Gamaschen des gefallenen Helden]</v>
+      <c r="D80" t="s">
+        <v>736</v>
       </c>
       <c r="E80">
         <v>29765</v>
@@ -11733,9 +12394,8 @@
       <c r="K80" t="s">
         <v>177</v>
       </c>
-      <c r="L80" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27874","[Gamaschen des Wildtierfürsten]")</f>
-        <v>[Gamaschen des Wildtierfürsten]</v>
+      <c r="L80" t="s">
+        <v>867</v>
       </c>
       <c r="N80">
         <v>4</v>
@@ -11767,9 +12427,8 @@
       <c r="C81" s="2">
         <v>0.87777777777777777</v>
       </c>
-      <c r="D81" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30244","[Helm des bezwungenen Helden]")</f>
-        <v>[Helm des bezwungenen Helden]</v>
+      <c r="D81" t="s">
+        <v>686</v>
       </c>
       <c r="E81">
         <v>30244</v>
@@ -11792,9 +12451,8 @@
       <c r="K81" t="s">
         <v>53</v>
       </c>
-      <c r="L81" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28275","[Helm des Wildtierfürsten]")</f>
-        <v>[Helm des Wildtierfürsten]</v>
+      <c r="L81" t="s">
+        <v>865</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -11826,9 +12484,8 @@
       <c r="C82" s="2">
         <v>0.87777777777777777</v>
       </c>
-      <c r="D82" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30242","[Helm des bezwungenen Champions]")</f>
-        <v>[Helm des bezwungenen Champions]</v>
+      <c r="D82" t="s">
+        <v>692</v>
       </c>
       <c r="E82">
         <v>30242</v>
@@ -11851,9 +12508,8 @@
       <c r="K82" t="s">
         <v>53</v>
       </c>
-      <c r="L82" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28732","[Gugel der Herausforderung]")</f>
-        <v>[Gugel der Herausforderung]</v>
+      <c r="L82" t="s">
+        <v>868</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -11885,9 +12541,8 @@
       <c r="C83" s="2">
         <v>0.81527777777777777</v>
       </c>
-      <c r="D83" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30060","[Stiefel des mühelosen Kampfes]")</f>
-        <v>[Stiefel des mühelosen Kampfes]</v>
+      <c r="D83" t="s">
+        <v>719</v>
       </c>
       <c r="E83">
         <v>30060</v>
@@ -11910,9 +12565,8 @@
       <c r="K83" t="s">
         <v>178</v>
       </c>
-      <c r="L83" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29258","[Stiefel der astralen Manipulation]")</f>
-        <v>[Stiefel der astralen Manipulation]</v>
+      <c r="L83" t="s">
+        <v>869</v>
       </c>
       <c r="N83">
         <v>4</v>
@@ -11947,9 +12601,8 @@
       <c r="C84" s="2">
         <v>0.84513888888888888</v>
       </c>
-      <c r="D84" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30626","[Sextant der unsteten Strömung]")</f>
-        <v>[Sextant der unsteten Strömung]</v>
+      <c r="D84" t="s">
+        <v>737</v>
       </c>
       <c r="E84">
         <v>30626</v>
@@ -11972,13 +12625,11 @@
       <c r="K84" t="s">
         <v>34</v>
       </c>
-      <c r="L84" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29370","[Ikone des Silberwappens]")</f>
-        <v>[Ikone des Silberwappens]</v>
-      </c>
-      <c r="M84" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=13503","[Alchimistenstein]")</f>
-        <v>[Alchimistenstein]</v>
+      <c r="L84" t="s">
+        <v>819</v>
+      </c>
+      <c r="M84" t="s">
+        <v>811</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -12013,9 +12664,8 @@
       <c r="C85" s="2">
         <v>0.90555555555555556</v>
       </c>
-      <c r="D85" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29753","[Brustschutz des gefallenen Verteidigers]")</f>
-        <v>[Brustschutz des gefallenen Verteidigers]</v>
+      <c r="D85" t="s">
+        <v>738</v>
       </c>
       <c r="E85">
         <v>29753</v>
@@ -12038,9 +12688,8 @@
       <c r="K85" t="s">
         <v>177</v>
       </c>
-      <c r="L85" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28602","[Robe der Ahnenschriften]")</f>
-        <v>[Robe der Ahnenschriften]</v>
+      <c r="L85" t="s">
+        <v>870</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -12072,9 +12721,8 @@
       <c r="C86" s="2">
         <v>0.90625</v>
       </c>
-      <c r="D86" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32386","[Magtheridons Kopf]")</f>
-        <v>[Magtheridons Kopf]</v>
+      <c r="D86" t="s">
+        <v>739</v>
       </c>
       <c r="E86">
         <v>32386</v>
@@ -12127,9 +12775,8 @@
       <c r="C87" s="2">
         <v>0.87986111111111109</v>
       </c>
-      <c r="D87" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30108","[Szepter der Lichtertiefe]")</f>
-        <v>[Szepter der Lichtertiefe]</v>
+      <c r="D87" t="s">
+        <v>740</v>
       </c>
       <c r="E87">
         <v>30108</v>
@@ -12152,9 +12799,8 @@
       <c r="K87" t="s">
         <v>53</v>
       </c>
-      <c r="L87" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28771","[Gerechtigkeit des Lichts]")</f>
-        <v>[Gerechtigkeit des Lichts]</v>
+      <c r="L87" t="s">
+        <v>871</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -12189,9 +12835,8 @@
       <c r="C88" s="2">
         <v>0.90555555555555556</v>
       </c>
-      <c r="D88" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29753","[Brustschutz des gefallenen Verteidigers]")</f>
-        <v>[Brustschutz des gefallenen Verteidigers]</v>
+      <c r="D88" t="s">
+        <v>738</v>
       </c>
       <c r="E88">
         <v>29753</v>
@@ -12214,9 +12859,8 @@
       <c r="K88" t="s">
         <v>177</v>
       </c>
-      <c r="L88" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=21875","[Urmondstoffrobe]")</f>
-        <v>[Urmondstoffrobe]</v>
+      <c r="L88" t="s">
+        <v>872</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -12248,9 +12892,8 @@
       <c r="C89" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D89" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28799","[Gürtel der göttlichen Eingebung]")</f>
-        <v>[Gürtel der göttlichen Eingebung]</v>
+      <c r="D89" t="s">
+        <v>741</v>
       </c>
       <c r="E89">
         <v>28799</v>
@@ -12273,9 +12916,8 @@
       <c r="K89" t="s">
         <v>173</v>
       </c>
-      <c r="L89" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27742","[Gurt des Magiezorns]")</f>
-        <v>[Gurt des Magiezorns]</v>
+      <c r="L89" t="s">
+        <v>873</v>
       </c>
       <c r="N89">
         <v>3</v>
@@ -12310,9 +12952,8 @@
       <c r="C90" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D90" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29764","[Schulterstücke des gefallenen Verteidigers]")</f>
-        <v>[Schulterstücke des gefallenen Verteidigers]</v>
+      <c r="D90" t="s">
+        <v>742</v>
       </c>
       <c r="E90">
         <v>29764</v>
@@ -12335,9 +12976,8 @@
       <c r="K90" t="s">
         <v>173</v>
       </c>
-      <c r="L90" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=33173","[Zornstahlschultern]")</f>
-        <v>[Zornstahlschultern]</v>
+      <c r="L90" t="s">
+        <v>874</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -12369,9 +13009,8 @@
       <c r="C91" s="2">
         <v>0.90625</v>
       </c>
-      <c r="D91" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28774","[Gleve der Grube]")</f>
-        <v>[Gleve der Grube]</v>
+      <c r="D91" t="s">
+        <v>743</v>
       </c>
       <c r="E91">
         <v>28774</v>
@@ -12394,13 +13033,11 @@
       <c r="K91" t="s">
         <v>177</v>
       </c>
-      <c r="L91" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29124","[Glanz des Verteidigers]")</f>
-        <v>[Glanz des Verteidigers]</v>
-      </c>
-      <c r="M91" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28572","[Klinge des Unerwiderten]")</f>
-        <v>[Klinge des Unerwiderten]</v>
+      <c r="L91" t="s">
+        <v>875</v>
+      </c>
+      <c r="M91" t="s">
+        <v>942</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -12435,9 +13072,8 @@
       <c r="C92" s="2">
         <v>0.80208333333333337</v>
       </c>
-      <c r="D92" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30629","[Skarabäus der Verdrängung]")</f>
-        <v>[Skarabäus der Verdrängung]</v>
+      <c r="D92" t="s">
+        <v>744</v>
       </c>
       <c r="E92">
         <v>30629</v>
@@ -12460,13 +13096,11 @@
       <c r="K92" t="s">
         <v>191</v>
       </c>
-      <c r="L92" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29370","[Ikone des Silberwappens]")</f>
-        <v>[Ikone des Silberwappens]</v>
-      </c>
-      <c r="M92" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27529","[Figur des Kolosses]")</f>
-        <v>[Figur des Kolosses]</v>
+      <c r="L92" t="s">
+        <v>819</v>
+      </c>
+      <c r="M92" t="s">
+        <v>943</v>
       </c>
       <c r="N92" t="s">
         <v>64</v>
@@ -12501,9 +13135,8 @@
       <c r="C93" s="2">
         <v>0.84444444444444444</v>
       </c>
-      <c r="D93" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30027","[Stiefel des endlosen Mutes]")</f>
-        <v>[Stiefel des endlosen Mutes]</v>
+      <c r="D93" t="s">
+        <v>745</v>
       </c>
       <c r="E93">
         <v>30027</v>
@@ -12526,9 +13159,8 @@
       <c r="K93" t="s">
         <v>26</v>
       </c>
-      <c r="L93" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32790","[Lederstiefel des Veteranen]")</f>
-        <v>[Lederstiefel des Veteranen]</v>
+      <c r="L93" t="s">
+        <v>876</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -12563,9 +13195,8 @@
       <c r="C94" s="2">
         <v>0.84444444444444444</v>
       </c>
-      <c r="D94" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30027","[Stiefel des endlosen Mutes]")</f>
-        <v>[Stiefel des endlosen Mutes]</v>
+      <c r="D94" t="s">
+        <v>745</v>
       </c>
       <c r="E94">
         <v>30027</v>
@@ -12588,9 +13219,8 @@
       <c r="K94" t="s">
         <v>26</v>
       </c>
-      <c r="L94" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32790","[Lederstiefel des Veteranen]")</f>
-        <v>[Lederstiefel des Veteranen]</v>
+      <c r="L94" t="s">
+        <v>876</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -12625,9 +13255,8 @@
       <c r="C95" s="2">
         <v>0.84583333333333333</v>
       </c>
-      <c r="D95" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30246","[Gamaschen des bezwungenen Verteidigers]")</f>
-        <v>[Gamaschen des bezwungenen Verteidigers]</v>
+      <c r="D95" t="s">
+        <v>710</v>
       </c>
       <c r="E95">
         <v>30246</v>
@@ -12650,9 +13279,8 @@
       <c r="K95" t="s">
         <v>34</v>
       </c>
-      <c r="L95" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29099","[Malornes Schienbeinschützer]")</f>
-        <v>[Malornes Schienbeinschützer]</v>
+      <c r="L95" t="s">
+        <v>877</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -12684,9 +13312,8 @@
       <c r="C96" s="2">
         <v>0.90486111111111112</v>
       </c>
-      <c r="D96" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29753","[Brustschutz des gefallenen Verteidigers]")</f>
-        <v>[Brustschutz des gefallenen Verteidigers]</v>
+      <c r="D96" t="s">
+        <v>738</v>
       </c>
       <c r="E96">
         <v>29753</v>
@@ -12709,9 +13336,8 @@
       <c r="K96" t="s">
         <v>177</v>
       </c>
-      <c r="L96" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29096","[Malornes Brustplatte]")</f>
-        <v>[Malornes Brustplatte]</v>
+      <c r="L96" t="s">
+        <v>878</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -12743,9 +13369,8 @@
       <c r="C97" s="2">
         <v>0.80208333333333337</v>
       </c>
-      <c r="D97" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30050","[Stiefel des sich wandelnden Alptraums]")</f>
-        <v>[Stiefel des sich wandelnden Alptraums]</v>
+      <c r="D97" t="s">
+        <v>746</v>
       </c>
       <c r="E97">
         <v>30050</v>
@@ -12768,9 +13393,8 @@
       <c r="K97" t="s">
         <v>191</v>
       </c>
-      <c r="L97" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27821","[Extravagante Stiefel der Bosheit]")</f>
-        <v>[Extravagante Stiefel der Bosheit]</v>
+      <c r="L97" t="s">
+        <v>879</v>
       </c>
       <c r="N97">
         <v>2</v>
@@ -12808,9 +13432,8 @@
       <c r="C98" s="2">
         <v>0.83680555555555558</v>
       </c>
-      <c r="D98" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30240","[Handschuhe des bezwungenen Verteidigers]")</f>
-        <v>[Handschuhe des bezwungenen Verteidigers]</v>
+      <c r="D98" t="s">
+        <v>711</v>
       </c>
       <c r="E98">
         <v>30240</v>
@@ -12833,9 +13456,8 @@
       <c r="K98" t="s">
         <v>26</v>
       </c>
-      <c r="L98" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30644","[Handschutz des Geschicks]")</f>
-        <v>[Handschutz des Geschicks]</v>
+      <c r="L98" t="s">
+        <v>880</v>
       </c>
       <c r="N98">
         <v>3</v>
@@ -12867,9 +13489,8 @@
       <c r="C99" s="2">
         <v>0.87916666666666665</v>
       </c>
-      <c r="D99" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30106","[Gürtel der hundert Tode]")</f>
-        <v>[Gürtel der hundert Tode]</v>
+      <c r="D99" t="s">
+        <v>681</v>
       </c>
       <c r="E99">
         <v>30106</v>
@@ -12892,9 +13513,8 @@
       <c r="K99" t="s">
         <v>53</v>
       </c>
-      <c r="L99" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28385","[Plattengürtel des Kriegsherren]")</f>
-        <v>[Plattengürtel des Kriegsherren]</v>
+      <c r="L99" t="s">
+        <v>839</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -12929,9 +13549,8 @@
       <c r="C100" s="2">
         <v>0.89097222222222228</v>
       </c>
-      <c r="D100" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28830","[Drachenwirbeltrophäe]")</f>
-        <v>[Drachenwirbeltrophäe]</v>
+      <c r="D100" t="s">
+        <v>747</v>
       </c>
       <c r="E100">
         <v>28830</v>
@@ -12954,13 +13573,11 @@
       <c r="K100" t="s">
         <v>173</v>
       </c>
-      <c r="L100" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28034","[Stundenglas des Entwirrers]")</f>
-        <v>[Stundenglas des Entwirrers]</v>
-      </c>
-      <c r="M100" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29383","[Kampfrauschbrosche]")</f>
-        <v>[Kampfrauschbrosche]</v>
+      <c r="L100" t="s">
+        <v>881</v>
+      </c>
+      <c r="M100" t="s">
+        <v>892</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -12995,9 +13612,8 @@
       <c r="C101" s="2">
         <v>0.81527777777777777</v>
       </c>
-      <c r="D101" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30063","[Buchband der absoluten Wahrheit]")</f>
-        <v>[Buchband der absoluten Wahrheit]</v>
+      <c r="D101" t="s">
+        <v>748</v>
       </c>
       <c r="E101">
         <v>30063</v>
@@ -13053,9 +13669,8 @@
       <c r="C102" s="2">
         <v>0.83680555555555558</v>
       </c>
-      <c r="D102" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30239","[Handschuhe des bezwungenen Champions]")</f>
-        <v>[Handschuhe des bezwungenen Champions]</v>
+      <c r="D102" t="s">
+        <v>691</v>
       </c>
       <c r="E102">
         <v>30239</v>
@@ -13078,9 +13693,8 @@
       <c r="K102" t="s">
         <v>26</v>
       </c>
-      <c r="L102" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28505","[Stulpen der erneuten Hoffnung]")</f>
-        <v>[Stulpen der erneuten Hoffnung]</v>
+      <c r="L102" t="s">
+        <v>882</v>
       </c>
       <c r="N102">
         <v>2</v>
@@ -13112,9 +13726,8 @@
       <c r="C103" s="2">
         <v>0.83680555555555558</v>
       </c>
-      <c r="D103" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30097","[Stachelige Korallenschulterpolster]")</f>
-        <v>[Stachelige Korallenschulterpolster]</v>
+      <c r="D103" t="s">
+        <v>688</v>
       </c>
       <c r="E103">
         <v>30097</v>
@@ -13137,9 +13750,8 @@
       <c r="K103" t="s">
         <v>26</v>
       </c>
-      <c r="L103" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30084","[Schulterstücke der Argentumschildwache]")</f>
-        <v>[Schulterstücke der Argentumschildwache]</v>
+      <c r="L103" t="s">
+        <v>720</v>
       </c>
       <c r="N103">
         <v>3</v>
@@ -13174,9 +13786,8 @@
       <c r="C104" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D104" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29763","[Schulterstücke des gefallenen Champions]")</f>
-        <v>[Schulterstücke des gefallenen Champions]</v>
+      <c r="D104" t="s">
+        <v>749</v>
       </c>
       <c r="E104">
         <v>29763</v>
@@ -13199,9 +13810,8 @@
       <c r="K104" t="s">
         <v>173</v>
       </c>
-      <c r="L104" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30084","[Schulterstücke der Argentumschildwache]")</f>
-        <v>[Schulterstücke der Argentumschildwache]</v>
+      <c r="L104" t="s">
+        <v>720</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -13233,9 +13843,8 @@
       <c r="C105" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D105" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29766","[Gamaschen des gefallenen Champions]")</f>
-        <v>[Gamaschen des gefallenen Champions]</v>
+      <c r="D105" t="s">
+        <v>750</v>
       </c>
       <c r="E105">
         <v>29766</v>
@@ -13258,9 +13867,8 @@
       <c r="K105" t="s">
         <v>173</v>
       </c>
-      <c r="L105" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28748","[Beinplatten des Unschuldigen]")</f>
-        <v>[Beinplatten des Unschuldigen]</v>
+      <c r="L105" t="s">
+        <v>883</v>
       </c>
       <c r="N105">
         <v>2</v>
@@ -13292,9 +13900,8 @@
       <c r="C106" s="2">
         <v>0.84513888888888888</v>
       </c>
-      <c r="D106" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30247","[Gamaschen des bezwungenen Helden]")</f>
-        <v>[Gamaschen des bezwungenen Helden]</v>
+      <c r="D106" t="s">
+        <v>718</v>
       </c>
       <c r="E106">
         <v>30247</v>
@@ -13317,9 +13924,8 @@
       <c r="K106" t="s">
         <v>34</v>
       </c>
-      <c r="L106" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=24262","[Hose des Zauberschlags]")</f>
-        <v>[Hose des Zauberschlags]</v>
+      <c r="L106" t="s">
+        <v>818</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -13351,9 +13957,8 @@
       <c r="C107" s="2">
         <v>0.85833333333333328</v>
       </c>
-      <c r="D107" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30720","[Flechte der Schlangenschlinge]")</f>
-        <v>[Flechte der Schlangenschlinge]</v>
+      <c r="D107" t="s">
+        <v>695</v>
       </c>
       <c r="E107">
         <v>30720</v>
@@ -13409,9 +14014,8 @@
       <c r="C108" s="2">
         <v>0.85833333333333328</v>
       </c>
-      <c r="D108" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30081","[Kriegsstiefel der Auslöschung]")</f>
-        <v>[Kriegsstiefel der Auslöschung]</v>
+      <c r="D108" t="s">
+        <v>693</v>
       </c>
       <c r="E108">
         <v>30081</v>
@@ -13434,9 +14038,8 @@
       <c r="K108" t="s">
         <v>129</v>
       </c>
-      <c r="L108" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28608","[Eisenschreiter der Dringlichkeit]")</f>
-        <v>[Eisenschreiter der Dringlichkeit]</v>
+      <c r="L108" t="s">
+        <v>817</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -13471,9 +14074,8 @@
       <c r="C109" s="2">
         <v>0.90555555555555556</v>
       </c>
-      <c r="D109" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29753","[Brustschutz des gefallenen Verteidigers]")</f>
-        <v>[Brustschutz des gefallenen Verteidigers]</v>
+      <c r="D109" t="s">
+        <v>738</v>
       </c>
       <c r="E109">
         <v>29753</v>
@@ -13496,9 +14098,8 @@
       <c r="K109" t="s">
         <v>177</v>
       </c>
-      <c r="L109" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28601","[Brustschutz des Verschwörers]")</f>
-        <v>[Brustschutz des Verschwörers]</v>
+      <c r="L109" t="s">
+        <v>801</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -13530,9 +14131,8 @@
       <c r="C110" s="2">
         <v>0.80138888888888893</v>
       </c>
-      <c r="D110" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30054","[Brustschutz des Waldläufergenerals]")</f>
-        <v>[Brustschutz des Waldläufergenerals]</v>
+      <c r="D110" t="s">
+        <v>676</v>
       </c>
       <c r="E110">
         <v>30054</v>
@@ -13555,9 +14155,8 @@
       <c r="K110" t="s">
         <v>191</v>
       </c>
-      <c r="L110" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28599","[Schuppenbrustplatte des Blutbads]")</f>
-        <v>[Schuppenbrustplatte des Blutbads]</v>
+      <c r="L110" t="s">
+        <v>884</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -13592,9 +14191,8 @@
       <c r="C111" s="2">
         <v>0.89444444444444449</v>
       </c>
-      <c r="D111" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29766","[Gamaschen des gefallenen Champions]")</f>
-        <v>[Gamaschen des gefallenen Champions]</v>
+      <c r="D111" t="s">
+        <v>750</v>
       </c>
       <c r="E111">
         <v>29766</v>
@@ -13617,9 +14215,8 @@
       <c r="K111" t="s">
         <v>173</v>
       </c>
-      <c r="L111" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30535","[Kilt des Waldhüters]")</f>
-        <v>[Kilt des Waldhüters]</v>
+      <c r="L111" t="s">
+        <v>885</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -13651,9 +14248,8 @@
       <c r="C112" s="2">
         <v>0.81527777777777777</v>
       </c>
-      <c r="D112" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30058","[Schlaghammer der Gezeiten]")</f>
-        <v>[Schlaghammer der Gezeiten]</v>
+      <c r="D112" t="s">
+        <v>751</v>
       </c>
       <c r="E112">
         <v>30058</v>
@@ -13676,9 +14272,8 @@
       <c r="K112" t="s">
         <v>178</v>
       </c>
-      <c r="L112" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28438","[Drachenmal]")</f>
-        <v>[Drachenmal]</v>
+      <c r="L112" t="s">
+        <v>843</v>
       </c>
       <c r="N112">
         <v>4</v>
@@ -13713,9 +14308,8 @@
       <c r="C113" s="2">
         <v>0.83680555555555558</v>
       </c>
-      <c r="D113" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30240","[Handschuhe des bezwungenen Verteidigers]")</f>
-        <v>[Handschuhe des bezwungenen Verteidigers]</v>
+      <c r="D113" t="s">
+        <v>711</v>
       </c>
       <c r="E113">
         <v>30240</v>
@@ -13738,9 +14332,8 @@
       <c r="K113" t="s">
         <v>26</v>
       </c>
-      <c r="L113" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28824","[Stulpen der Kampfvollendung]")</f>
-        <v>[Stulpen der Kampfvollendung]</v>
+      <c r="L113" t="s">
+        <v>886</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -13772,9 +14365,8 @@
       <c r="C114" s="2">
         <v>0.90625</v>
       </c>
-      <c r="D114" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28789","[Magtheridons Auge]")</f>
-        <v>[Magtheridons Auge]</v>
+      <c r="D114" t="s">
+        <v>752</v>
       </c>
       <c r="E114">
         <v>28789</v>
@@ -13797,13 +14389,11 @@
       <c r="K114" t="s">
         <v>177</v>
       </c>
-      <c r="L114" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27683","[Quagmirrans Auge]")</f>
-        <v>[Quagmirrans Auge]</v>
-      </c>
-      <c r="M114" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29370","[Ikone des Silberwappens]")</f>
-        <v>[Ikone des Silberwappens]</v>
+      <c r="L114" t="s">
+        <v>887</v>
+      </c>
+      <c r="M114" t="s">
+        <v>819</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -13838,9 +14428,8 @@
       <c r="C115" s="2">
         <v>0.84930555555555554</v>
       </c>
-      <c r="D115" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29993","[Zwillingsklinge des Phönix]")</f>
-        <v>[Zwillingsklinge des Phönix]</v>
+      <c r="D115" s="17" t="s">
+        <v>753</v>
       </c>
       <c r="E115">
         <v>29993</v>
@@ -13896,9 +14485,8 @@
       <c r="C116" s="2">
         <v>0.81805555555555554</v>
       </c>
-      <c r="D116" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29984","[Gurt von Zaetar]")</f>
-        <v>[Gurt von Zaetar]</v>
+      <c r="D116" s="17" t="s">
+        <v>754</v>
       </c>
       <c r="E116">
         <v>29984</v>
@@ -13921,9 +14509,8 @@
       <c r="K116" t="s">
         <v>210</v>
       </c>
-      <c r="L116" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32998","[Ringpanzergurt des Veteranen]")</f>
-        <v>[Ringpanzergurt des Veteranen]</v>
+      <c r="L116" t="s">
+        <v>888</v>
       </c>
       <c r="N116">
         <v>2</v>
@@ -13958,9 +14545,8 @@
       <c r="C117" s="2">
         <v>0.85</v>
       </c>
-      <c r="D117" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29987","[Stulpen des Sonnenkönigs]")</f>
-        <v>[Stulpen des Sonnenkönigs]</v>
+      <c r="D117" s="17" t="s">
+        <v>755</v>
       </c>
       <c r="E117">
         <v>29987</v>
@@ -13983,9 +14569,8 @@
       <c r="K117" t="s">
         <v>207</v>
       </c>
-      <c r="L117" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29080","[Handschuhe der Aldor]")</f>
-        <v>[Handschuhe der Aldor]</v>
+      <c r="L117" t="s">
+        <v>844</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -14020,9 +14605,8 @@
       <c r="C118" s="2">
         <v>0.80972222222222223</v>
       </c>
-      <c r="D118" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30447","[Foliant der feurigen Erlösung]")</f>
-        <v>[Foliant der feurigen Erlösung]</v>
+      <c r="D118" s="17" t="s">
+        <v>756</v>
       </c>
       <c r="E118">
         <v>30447</v>
@@ -14045,13 +14629,11 @@
       <c r="K118" t="s">
         <v>212</v>
       </c>
-      <c r="L118" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29376","[Essenz des Märtyrers]")</f>
-        <v>[Essenz des Märtyrers]</v>
-      </c>
-      <c r="M118" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28590","[Schleife der Opferung]")</f>
-        <v>[Schleife der Opferung]</v>
+      <c r="L118" t="s">
+        <v>804</v>
+      </c>
+      <c r="M118" t="s">
+        <v>919</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -14086,9 +14668,8 @@
       <c r="C119" s="2">
         <v>0.84861111111111109</v>
       </c>
-      <c r="D119" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30237","[Brustschutz des bezwungenen Verteidigers]")</f>
-        <v>[Brustschutz des bezwungenen Verteidigers]</v>
+      <c r="D119" s="17" t="s">
+        <v>757</v>
       </c>
       <c r="E119">
         <v>30237</v>
@@ -14111,9 +14692,8 @@
       <c r="K119" t="s">
         <v>207</v>
       </c>
-      <c r="L119" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=25689","[Schwere Grollhufweste]")</f>
-        <v>[Schwere Grollhufweste]</v>
+      <c r="L119" t="s">
+        <v>889</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -14145,9 +14725,8 @@
       <c r="C120" s="2">
         <v>0.84930555555555554</v>
       </c>
-      <c r="D120" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30238","[Brustschutz des bezwungenen Helden]")</f>
-        <v>[Brustschutz des bezwungenen Helden]</v>
+      <c r="D120" s="17" t="s">
+        <v>758</v>
       </c>
       <c r="E120">
         <v>30238</v>
@@ -14170,9 +14749,8 @@
       <c r="K120" t="s">
         <v>207</v>
       </c>
-      <c r="L120" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29077","[Gewänder der Aldor]")</f>
-        <v>[Gewänder der Aldor]</v>
+      <c r="L120" t="s">
+        <v>890</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -14207,9 +14785,8 @@
       <c r="C121" s="2">
         <v>0.81805555555555554</v>
       </c>
-      <c r="D121" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30250","[Schulterstücke des bezwungenen Helden]")</f>
-        <v>[Schulterstücke des bezwungenen Helden]</v>
+      <c r="D121" s="17" t="s">
+        <v>759</v>
       </c>
       <c r="E121">
         <v>30250</v>
@@ -14232,9 +14809,8 @@
       <c r="K121" t="s">
         <v>210</v>
       </c>
-      <c r="L121" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=27801","[Mantelung des Wildtierfürsten]")</f>
-        <v>[Mantelung des Wildtierfürsten]</v>
+      <c r="L121" t="s">
+        <v>866</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -14269,9 +14845,8 @@
       <c r="C122" s="2">
         <v>0.80694444444444446</v>
       </c>
-      <c r="D122" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29922","[Al'ars Band]")</f>
-        <v>[Al'ars Band]</v>
+      <c r="D122" s="17" t="s">
+        <v>760</v>
       </c>
       <c r="E122">
         <v>29922</v>
@@ -14294,13 +14869,11 @@
       <c r="K122" t="s">
         <v>212</v>
       </c>
-      <c r="L122" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29285","[Violettes Siegel]")</f>
-        <v>[Violettes Siegel]</v>
-      </c>
-      <c r="M122" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28394","[Ryngos Band des Scharfsinns]")</f>
-        <v>[Ryngos Band des Scharfsinns]</v>
+      <c r="L122" t="s">
+        <v>813</v>
+      </c>
+      <c r="M122" t="s">
+        <v>944</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -14335,9 +14908,8 @@
       <c r="C123" s="2">
         <v>0.81874999999999998</v>
       </c>
-      <c r="D123" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30250","[Schulterstücke des bezwungenen Helden]")</f>
-        <v>[Schulterstücke des bezwungenen Helden]</v>
+      <c r="D123" s="17" t="s">
+        <v>759</v>
       </c>
       <c r="E123">
         <v>30250</v>
@@ -14360,9 +14932,8 @@
       <c r="K123" t="s">
         <v>210</v>
       </c>
-      <c r="L123" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29079","[Schulterstücke der Aldor]")</f>
-        <v>[Schulterstücke der Aldor]</v>
+      <c r="L123" t="s">
+        <v>891</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -14394,9 +14965,8 @@
       <c r="C124" s="2">
         <v>0.81736111111111109</v>
       </c>
-      <c r="D124" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30448","[Al'ars Kralle]")</f>
-        <v>[Al'ars Kralle]</v>
+      <c r="D124" s="17" t="s">
+        <v>761</v>
       </c>
       <c r="E124">
         <v>30448</v>
@@ -14419,13 +14989,11 @@
       <c r="K124" t="s">
         <v>212</v>
       </c>
-      <c r="L124" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=29383","[Kampfrauschbrosche]")</f>
-        <v>[Kampfrauschbrosche]</v>
-      </c>
-      <c r="M124" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28288","[Abakus der Ungleichheit]")</f>
-        <v>[Abakus der Ungleichheit]</v>
+      <c r="L124" t="s">
+        <v>892</v>
+      </c>
+      <c r="M124" t="s">
+        <v>945</v>
       </c>
       <c r="N124" t="s">
         <v>64</v>
@@ -14460,9 +15028,8 @@
       <c r="C125" s="2">
         <v>0.81874999999999998</v>
       </c>
-      <c r="D125" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30248","[Schulterstücke des bezwungenen Champions]")</f>
-        <v>[Schulterstücke des bezwungenen Champions]</v>
+      <c r="D125" s="17" t="s">
+        <v>762</v>
       </c>
       <c r="E125">
         <v>30248</v>
@@ -14485,9 +15052,8 @@
       <c r="K125" t="s">
         <v>210</v>
       </c>
-      <c r="L125" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28755","[Klingenschulterpolster des Erbarmungslosen]")</f>
-        <v>[Klingenschulterpolster des Erbarmungslosen]</v>
+      <c r="L125" t="s">
+        <v>893</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -14519,9 +15085,8 @@
       <c r="C126" s="2">
         <v>0.85138888888888886</v>
       </c>
-      <c r="D126" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=32405","[Tiefgrüne Sphäre]")</f>
-        <v>[Tiefgrüne Sphäre]</v>
+      <c r="D126" s="17" t="s">
+        <v>763</v>
       </c>
       <c r="E126">
         <v>32405</v>
@@ -14574,9 +15139,8 @@
       <c r="C127" s="2">
         <v>0.84930555555555554</v>
       </c>
-      <c r="D127" s="17" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=30237","[Brustschutz des bezwungenen Verteidigers]")</f>
-        <v>[Brustschutz des bezwungenen Verteidigers]</v>
+      <c r="D127" s="17" t="s">
+        <v>757</v>
       </c>
       <c r="E127">
         <v>30237</v>
@@ -14599,9 +15163,8 @@
       <c r="K127" t="s">
         <v>207</v>
       </c>
-      <c r="L127" t="str">
-        <f>HYPERLINK("https://tbc.wowhead.com/item=28602","[Robe der Ahnenschriften]")</f>
-        <v>[Robe der Ahnenschriften]</v>
+      <c r="L127" t="s">
+        <v>870</v>
       </c>
       <c r="N127">
         <v>1</v>
@@ -14634,7 +15197,7 @@
         <v>0.80347222222222225</v>
       </c>
       <c r="D128" t="s">
-        <v>263</v>
+        <v>764</v>
       </c>
       <c r="E128">
         <v>30283</v>
@@ -14688,7 +15251,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D129" t="s">
-        <v>277</v>
+        <v>765</v>
       </c>
       <c r="E129">
         <v>30100</v>
@@ -14712,7 +15275,7 @@
         <v>279</v>
       </c>
       <c r="L129" t="s">
-        <v>280</v>
+        <v>894</v>
       </c>
       <c r="N129">
         <v>1</v>
@@ -14748,7 +15311,7 @@
         <v>0.86388888888888893</v>
       </c>
       <c r="D130" t="s">
-        <v>334</v>
+        <v>766</v>
       </c>
       <c r="E130">
         <v>30081</v>
@@ -14772,7 +15335,7 @@
         <v>335</v>
       </c>
       <c r="L130" t="s">
-        <v>336</v>
+        <v>895</v>
       </c>
       <c r="N130">
         <v>1</v>
@@ -14808,7 +15371,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D131" t="s">
-        <v>337</v>
+        <v>767</v>
       </c>
       <c r="E131">
         <v>30063</v>
@@ -14865,7 +15428,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D132" t="s">
-        <v>412</v>
+        <v>768</v>
       </c>
       <c r="E132">
         <v>30057</v>
@@ -14889,7 +15452,7 @@
         <v>53</v>
       </c>
       <c r="L132" t="s">
-        <v>414</v>
+        <v>896</v>
       </c>
       <c r="N132">
         <v>1</v>
@@ -14925,7 +15488,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="D133" t="s">
-        <v>450</v>
+        <v>769</v>
       </c>
       <c r="E133">
         <v>30302</v>
@@ -14979,7 +15542,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D134" t="s">
-        <v>454</v>
+        <v>770</v>
       </c>
       <c r="E134">
         <v>30066</v>
@@ -15003,7 +15566,7 @@
         <v>53</v>
       </c>
       <c r="L134" t="s">
-        <v>456</v>
+        <v>897</v>
       </c>
       <c r="N134">
         <v>3</v>
@@ -15039,7 +15602,7 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="D135" t="s">
-        <v>483</v>
+        <v>771</v>
       </c>
       <c r="E135">
         <v>30245</v>
@@ -15063,7 +15626,7 @@
         <v>279</v>
       </c>
       <c r="L135" t="s">
-        <v>484</v>
+        <v>898</v>
       </c>
       <c r="N135">
         <v>1</v>
@@ -15099,7 +15662,7 @@
         <v>0.86805555555555558</v>
       </c>
       <c r="D136" t="s">
-        <v>486</v>
+        <v>772</v>
       </c>
       <c r="E136">
         <v>30022</v>
@@ -15123,7 +15686,7 @@
         <v>335</v>
       </c>
       <c r="L136" t="s">
-        <v>488</v>
+        <v>899</v>
       </c>
       <c r="N136">
         <v>1</v>
@@ -15159,7 +15722,7 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="D137" t="s">
-        <v>507</v>
+        <v>773</v>
       </c>
       <c r="E137">
         <v>30246</v>
@@ -15183,7 +15746,7 @@
         <v>279</v>
       </c>
       <c r="L137" t="s">
-        <v>508</v>
+        <v>900</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -15216,7 +15779,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D138" t="s">
-        <v>515</v>
+        <v>774</v>
       </c>
       <c r="E138">
         <v>30247</v>
@@ -15240,7 +15803,7 @@
         <v>279</v>
       </c>
       <c r="L138" t="s">
-        <v>508</v>
+        <v>900</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -15273,7 +15836,7 @@
         <v>0.8305555555555556</v>
       </c>
       <c r="D139" t="s">
-        <v>538</v>
+        <v>775</v>
       </c>
       <c r="E139">
         <v>30025</v>
@@ -15297,7 +15860,7 @@
         <v>539</v>
       </c>
       <c r="L139" t="s">
-        <v>526</v>
+        <v>822</v>
       </c>
       <c r="N139">
         <v>4</v>
@@ -15333,7 +15896,7 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="D140" t="s">
-        <v>540</v>
+        <v>776</v>
       </c>
       <c r="E140">
         <v>30324</v>
@@ -15387,7 +15950,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D141" t="s">
-        <v>542</v>
+        <v>777</v>
       </c>
       <c r="E141">
         <v>30053</v>
@@ -15411,7 +15974,7 @@
         <v>53</v>
       </c>
       <c r="L141" t="s">
-        <v>544</v>
+        <v>901</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -15447,7 +16010,7 @@
         <v>0.88680555555555551</v>
       </c>
       <c r="D142" t="s">
-        <v>545</v>
+        <v>778</v>
       </c>
       <c r="E142">
         <v>30106</v>
@@ -15471,7 +16034,7 @@
         <v>53</v>
       </c>
       <c r="L142" t="s">
-        <v>546</v>
+        <v>902</v>
       </c>
       <c r="N142">
         <v>1</v>
@@ -15507,7 +16070,7 @@
         <v>0.86319444444444449</v>
       </c>
       <c r="D143" t="s">
-        <v>594</v>
+        <v>779</v>
       </c>
       <c r="E143">
         <v>30075</v>
@@ -15531,7 +16094,7 @@
         <v>335</v>
       </c>
       <c r="L143" t="s">
-        <v>595</v>
+        <v>903</v>
       </c>
       <c r="N143">
         <v>3</v>
@@ -15567,7 +16130,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D144" t="s">
-        <v>596</v>
+        <v>780</v>
       </c>
       <c r="E144">
         <v>30242</v>
@@ -15591,7 +16154,7 @@
         <v>53</v>
       </c>
       <c r="L144" t="s">
-        <v>597</v>
+        <v>904</v>
       </c>
       <c r="N144">
         <v>1</v>
@@ -15624,7 +16187,7 @@
         <v>0.88472222222222219</v>
       </c>
       <c r="D145" t="s">
-        <v>598</v>
+        <v>781</v>
       </c>
       <c r="E145">
         <v>30112</v>
@@ -15648,7 +16211,7 @@
         <v>53</v>
       </c>
       <c r="L145" t="s">
-        <v>600</v>
+        <v>905</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -15684,7 +16247,7 @@
         <v>0.86388888888888893</v>
       </c>
       <c r="D146" t="s">
-        <v>605</v>
+        <v>782</v>
       </c>
       <c r="E146">
         <v>33058</v>
@@ -15708,10 +16271,10 @@
         <v>335</v>
       </c>
       <c r="L146" t="s">
-        <v>607</v>
+        <v>906</v>
       </c>
       <c r="M146" t="s">
-        <v>472</v>
+        <v>859</v>
       </c>
       <c r="N146">
         <v>4</v>
@@ -15747,7 +16310,7 @@
         <v>0.88472222222222219</v>
       </c>
       <c r="D147" t="s">
-        <v>614</v>
+        <v>783</v>
       </c>
       <c r="E147">
         <v>30244</v>
@@ -15771,7 +16334,7 @@
         <v>53</v>
       </c>
       <c r="L147" t="s">
-        <v>615</v>
+        <v>907</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -15804,7 +16367,7 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="D148" t="s">
-        <v>659</v>
+        <v>784</v>
       </c>
       <c r="E148">
         <v>30306</v>
@@ -15858,7 +16421,7 @@
         <v>0.87986111111111109</v>
       </c>
       <c r="D149" t="s">
-        <v>668</v>
+        <v>785</v>
       </c>
       <c r="E149">
         <v>30048</v>
@@ -15882,7 +16445,7 @@
         <v>53</v>
       </c>
       <c r="L149" t="s">
-        <v>670</v>
+        <v>908</v>
       </c>
       <c r="N149">
         <v>1</v>
@@ -15918,7 +16481,7 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="D150" t="s">
-        <v>538</v>
+        <v>775</v>
       </c>
       <c r="E150">
         <v>30025</v>
@@ -15942,7 +16505,7 @@
         <v>53</v>
       </c>
       <c r="L150" t="s">
-        <v>671</v>
+        <v>909</v>
       </c>
       <c r="N150">
         <v>1</v>
@@ -15978,7 +16541,7 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="D151" t="s">
-        <v>672</v>
+        <v>786</v>
       </c>
       <c r="E151">
         <v>30049</v>
@@ -16002,7 +16565,7 @@
         <v>53</v>
       </c>
       <c r="L151" t="s">
-        <v>674</v>
+        <v>910</v>
       </c>
       <c r="N151">
         <v>1</v>
@@ -16038,7 +16601,7 @@
         <v>0.81180555555555556</v>
       </c>
       <c r="D152" t="s">
-        <v>267</v>
+        <v>760</v>
       </c>
       <c r="E152">
         <v>29922</v>
@@ -16062,10 +16625,10 @@
         <v>212</v>
       </c>
       <c r="L152" t="s">
-        <v>268</v>
+        <v>911</v>
       </c>
       <c r="M152" t="s">
-        <v>269</v>
+        <v>946</v>
       </c>
       <c r="N152">
         <v>1</v>
@@ -16101,7 +16664,7 @@
         <v>0.8256944444444444</v>
       </c>
       <c r="D153" t="s">
-        <v>270</v>
+        <v>787</v>
       </c>
       <c r="E153">
         <v>29986</v>
@@ -16125,7 +16688,7 @@
         <v>210</v>
       </c>
       <c r="L153" t="s">
-        <v>272</v>
+        <v>912</v>
       </c>
       <c r="N153">
         <v>1</v>
@@ -16161,7 +16724,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D154" t="s">
-        <v>273</v>
+        <v>742</v>
       </c>
       <c r="E154">
         <v>29764</v>
@@ -16185,7 +16748,7 @@
         <v>173</v>
       </c>
       <c r="L154" t="s">
-        <v>274</v>
+        <v>913</v>
       </c>
       <c r="N154">
         <v>4</v>
@@ -16218,7 +16781,7 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="D155" t="s">
-        <v>254</v>
+        <v>738</v>
       </c>
       <c r="E155">
         <v>29753</v>
@@ -16242,7 +16805,7 @@
         <v>177</v>
       </c>
       <c r="L155" t="s">
-        <v>275</v>
+        <v>914</v>
       </c>
       <c r="N155">
         <v>4</v>
@@ -16275,7 +16838,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D156" t="s">
-        <v>281</v>
+        <v>757</v>
       </c>
       <c r="E156">
         <v>30237</v>
@@ -16299,7 +16862,7 @@
         <v>282</v>
       </c>
       <c r="L156" t="s">
-        <v>283</v>
+        <v>915</v>
       </c>
       <c r="N156">
         <v>1</v>
@@ -16332,7 +16895,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D157" t="s">
-        <v>317</v>
+        <v>763</v>
       </c>
       <c r="E157">
         <v>32405</v>
@@ -16386,7 +16949,7 @@
         <v>0.87222222222222223</v>
       </c>
       <c r="D158" t="s">
-        <v>360</v>
+        <v>788</v>
       </c>
       <c r="E158">
         <v>28794</v>
@@ -16410,10 +16973,10 @@
         <v>173</v>
       </c>
       <c r="L158" t="s">
-        <v>358</v>
+        <v>875</v>
       </c>
       <c r="M158" t="s">
-        <v>359</v>
+        <v>942</v>
       </c>
       <c r="N158">
         <v>3</v>
@@ -16449,7 +17012,7 @@
         <v>0.875</v>
       </c>
       <c r="D159" t="s">
-        <v>363</v>
+        <v>789</v>
       </c>
       <c r="E159">
         <v>29767</v>
@@ -16473,7 +17036,7 @@
         <v>173</v>
       </c>
       <c r="L159" t="s">
-        <v>365</v>
+        <v>916</v>
       </c>
       <c r="N159">
         <v>1</v>
@@ -16506,7 +17069,7 @@
         <v>0.85624999999999996</v>
       </c>
       <c r="D160" t="s">
-        <v>382</v>
+        <v>761</v>
       </c>
       <c r="E160">
         <v>30448</v>
@@ -16530,10 +17093,10 @@
         <v>212</v>
       </c>
       <c r="L160" t="s">
-        <v>383</v>
+        <v>917</v>
       </c>
       <c r="M160" t="s">
-        <v>384</v>
+        <v>947</v>
       </c>
       <c r="N160">
         <v>1</v>
@@ -16569,7 +17132,7 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="D161" t="s">
-        <v>436</v>
+        <v>790</v>
       </c>
       <c r="E161">
         <v>29982</v>
@@ -16593,7 +17156,7 @@
         <v>438</v>
       </c>
       <c r="L161" t="s">
-        <v>439</v>
+        <v>918</v>
       </c>
       <c r="N161">
         <v>1</v>
@@ -16632,7 +17195,7 @@
         <v>0.81180555555555556</v>
       </c>
       <c r="D162" t="s">
-        <v>457</v>
+        <v>791</v>
       </c>
       <c r="E162">
         <v>29921</v>
@@ -16656,7 +17219,7 @@
         <v>212</v>
       </c>
       <c r="L162" t="s">
-        <v>447</v>
+        <v>733</v>
       </c>
       <c r="N162">
         <v>2</v>
@@ -16692,7 +17255,7 @@
         <v>0.87152777777777779</v>
       </c>
       <c r="D163" t="s">
-        <v>474</v>
+        <v>792</v>
       </c>
       <c r="E163">
         <v>28823</v>
@@ -16716,10 +17279,10 @@
         <v>173</v>
       </c>
       <c r="L163" t="s">
-        <v>343</v>
+        <v>919</v>
       </c>
       <c r="M163" t="s">
-        <v>342</v>
+        <v>804</v>
       </c>
       <c r="N163">
         <v>3</v>
@@ -16755,7 +17318,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D164" t="s">
-        <v>476</v>
+        <v>749</v>
       </c>
       <c r="E164">
         <v>29763</v>
@@ -16779,7 +17342,7 @@
         <v>173</v>
       </c>
       <c r="L164" t="s">
-        <v>489</v>
+        <v>920</v>
       </c>
       <c r="N164">
         <v>4</v>
@@ -16815,7 +17378,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D165" t="s">
-        <v>509</v>
+        <v>793</v>
       </c>
       <c r="E165">
         <v>30249</v>
@@ -16839,7 +17402,7 @@
         <v>210</v>
       </c>
       <c r="L165" t="s">
-        <v>501</v>
+        <v>714</v>
       </c>
       <c r="N165">
         <v>1</v>
@@ -16872,7 +17435,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D166" t="s">
-        <v>513</v>
+        <v>735</v>
       </c>
       <c r="E166">
         <v>29762</v>
@@ -16896,7 +17459,7 @@
         <v>173</v>
       </c>
       <c r="L166" t="s">
-        <v>429</v>
+        <v>891</v>
       </c>
       <c r="N166">
         <v>2</v>
@@ -16929,7 +17492,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D167" t="s">
-        <v>422</v>
+        <v>736</v>
       </c>
       <c r="E167">
         <v>29765</v>
@@ -16953,7 +17516,7 @@
         <v>173</v>
       </c>
       <c r="L167" t="s">
-        <v>316</v>
+        <v>818</v>
       </c>
       <c r="N167">
         <v>2</v>
@@ -16986,7 +17549,7 @@
         <v>0.875</v>
       </c>
       <c r="D168" t="s">
-        <v>422</v>
+        <v>736</v>
       </c>
       <c r="E168">
         <v>29765</v>
@@ -17010,7 +17573,7 @@
         <v>173</v>
       </c>
       <c r="L168" t="s">
-        <v>316</v>
+        <v>818</v>
       </c>
       <c r="N168">
         <v>2</v>
@@ -17043,7 +17606,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D169" t="s">
-        <v>518</v>
+        <v>794</v>
       </c>
       <c r="E169">
         <v>29981</v>
@@ -17067,10 +17630,10 @@
         <v>438</v>
       </c>
       <c r="L169" t="s">
-        <v>520</v>
+        <v>921</v>
       </c>
       <c r="M169" t="s">
-        <v>521</v>
+        <v>948</v>
       </c>
       <c r="N169">
         <v>3</v>
@@ -17106,7 +17669,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D170" t="s">
-        <v>281</v>
+        <v>757</v>
       </c>
       <c r="E170">
         <v>30237</v>
@@ -17130,7 +17693,7 @@
         <v>282</v>
       </c>
       <c r="L170" t="s">
-        <v>547</v>
+        <v>922</v>
       </c>
       <c r="N170">
         <v>1</v>
@@ -17163,7 +17726,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D171" t="s">
-        <v>559</v>
+        <v>795</v>
       </c>
       <c r="E171">
         <v>29988</v>
@@ -17187,10 +17750,10 @@
         <v>282</v>
       </c>
       <c r="L171" t="s">
-        <v>561</v>
+        <v>923</v>
       </c>
       <c r="M171" t="s">
-        <v>562</v>
+        <v>949</v>
       </c>
       <c r="N171">
         <v>1</v>
@@ -17226,7 +17789,7 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="D172" t="s">
-        <v>581</v>
+        <v>762</v>
       </c>
       <c r="E172">
         <v>30248</v>
@@ -17250,7 +17813,7 @@
         <v>210</v>
       </c>
       <c r="L172" t="s">
-        <v>582</v>
+        <v>924</v>
       </c>
       <c r="N172">
         <v>1</v>
@@ -17283,7 +17846,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D173" t="s">
-        <v>583</v>
+        <v>796</v>
       </c>
       <c r="E173">
         <v>28800</v>
@@ -17307,10 +17870,10 @@
         <v>173</v>
       </c>
       <c r="L173" t="s">
-        <v>585</v>
+        <v>925</v>
       </c>
       <c r="M173" t="s">
-        <v>394</v>
+        <v>950</v>
       </c>
       <c r="N173" t="s">
         <v>64</v>
@@ -17346,7 +17909,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D174" t="s">
-        <v>601</v>
+        <v>797</v>
       </c>
       <c r="E174">
         <v>29965</v>
@@ -17370,7 +17933,7 @@
         <v>438</v>
       </c>
       <c r="L174" t="s">
-        <v>603</v>
+        <v>926</v>
       </c>
       <c r="N174">
         <v>2</v>
@@ -17406,7 +17969,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D175" t="s">
-        <v>307</v>
+        <v>739</v>
       </c>
       <c r="E175">
         <v>32386</v>
@@ -17460,7 +18023,7 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="D176" t="s">
-        <v>254</v>
+        <v>738</v>
       </c>
       <c r="E176">
         <v>29753</v>
@@ -17484,7 +18047,7 @@
         <v>177</v>
       </c>
       <c r="L176" t="s">
-        <v>275</v>
+        <v>914</v>
       </c>
       <c r="N176" t="s">
         <v>64</v>
@@ -17517,7 +18080,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D177" t="s">
-        <v>254</v>
+        <v>738</v>
       </c>
       <c r="E177">
         <v>29753</v>
@@ -17541,7 +18104,7 @@
         <v>177</v>
       </c>
       <c r="L177" t="s">
-        <v>275</v>
+        <v>914</v>
       </c>
       <c r="N177" t="s">
         <v>64</v>
@@ -17574,7 +18137,7 @@
         <v>0.8256944444444444</v>
       </c>
       <c r="D178" t="s">
-        <v>581</v>
+        <v>762</v>
       </c>
       <c r="E178">
         <v>30248</v>
@@ -17598,7 +18161,7 @@
         <v>210</v>
       </c>
       <c r="L178" t="s">
-        <v>620</v>
+        <v>927</v>
       </c>
       <c r="N178">
         <v>1</v>
@@ -17631,7 +18194,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D179" t="s">
-        <v>621</v>
+        <v>798</v>
       </c>
       <c r="E179">
         <v>29997</v>
@@ -17655,10 +18218,10 @@
         <v>282</v>
       </c>
       <c r="L179" t="s">
-        <v>623</v>
+        <v>911</v>
       </c>
       <c r="M179" t="s">
-        <v>624</v>
+        <v>951</v>
       </c>
       <c r="N179">
         <v>1</v>
@@ -17694,7 +18257,7 @@
         <v>0.85555555555555551</v>
       </c>
       <c r="D180" t="s">
-        <v>625</v>
+        <v>799</v>
       </c>
       <c r="E180">
         <v>30236</v>
@@ -17718,7 +18281,7 @@
         <v>282</v>
       </c>
       <c r="L180" t="s">
-        <v>627</v>
+        <v>928</v>
       </c>
       <c r="N180">
         <v>1</v>

--- a/RC_Lootcouncil.xlsx
+++ b/RC_Lootcouncil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6460C6A1-0B54-4481-A3D9-5F7FA852DEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537786AA-9D76-41D2-A481-DE1EE55EFF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
+    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loot History" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="926">
   <si>
     <t>player</t>
   </si>
@@ -2143,9 +2143,6 @@
     <t>Magtheridons' Lair-25 Spieler</t>
   </si>
   <si>
-    <t>Gruul the Dragonslayer</t>
-  </si>
-  <si>
     <t>Void Reaver</t>
   </si>
   <si>
@@ -2870,6 +2867,27 @@
   </si>
   <si>
     <t>Garona's Signet Ring</t>
+  </si>
+  <si>
+    <t>Trash Mobs (Serpentshrine Cavern)</t>
+  </si>
+  <si>
+    <t>Raid Bosses (T5/T6) / Vendor</t>
+  </si>
+  <si>
+    <t>Trash Mobs (SSC / TK)</t>
+  </si>
+  <si>
+    <t>Trash Mobs (Tempest Keep)</t>
+  </si>
+  <si>
+    <t>Gruul the Dragonkiller</t>
+  </si>
+  <si>
+    <t>High King Maulgar</t>
+  </si>
+  <si>
+    <t>Fathom-Lord Karathress / Morogrim</t>
   </si>
 </sst>
 </file>
@@ -4160,7 +4178,7 @@
             <c:strRef>
               <c:f>[0]!chartBossNames</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>Al'ar</c:v>
                 </c:pt>
@@ -4168,33 +4186,48 @@
                   <c:v>Fathom-Lord Karathress</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Gruul the Dragonslayer</c:v>
+                  <c:v>Fathom-Lord Karathress / Morogrim</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Gruul the Dragonkiller</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>High Astromancer Solarian</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>High King Maulgar</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Hydross the Unstable</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>Kael'thas Sunstrider</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="8">
                   <c:v>Lady Vashj</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="9">
                   <c:v>Leotheras the Blind</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>Magtheridon</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>Morogrim Tidewalker</c:v>
                 </c:pt>
-                <c:pt idx="10">
-                  <c:v>The Lurker Below</c:v>
+                <c:pt idx="12">
+                  <c:v>Raid Bosses (T5/T6) / Vendor</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="13">
+                  <c:v>Trash Mobs (Serpentshrine Cavern)</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Trash Mobs (SSC / TK)</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Trash Mobs (Tempest Keep)</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Void Reaver</c:v>
                 </c:pt>
               </c:strCache>
@@ -4205,42 +4238,57 @@
               <c:f>[0]!chartBossCounts</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>17</c:v>
+                <c:pt idx="15">
+                  <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>21</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>12</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>23</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>8</c:v>
+                <c:pt idx="16">
+                  <c:v>14</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7611,7 +7659,7 @@
         <v>0.91111111111111109</v>
       </c>
       <c r="D2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E2">
         <v>30241</v>
@@ -7635,7 +7683,7 @@
         <v>539</v>
       </c>
       <c r="L2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -7668,7 +7716,7 @@
         <v>0.86111111111111116</v>
       </c>
       <c r="D3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E3">
         <v>30054</v>
@@ -7689,10 +7737,10 @@
         <v>265</v>
       </c>
       <c r="K3" t="s">
-        <v>279</v>
+        <v>102</v>
       </c>
       <c r="L3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -7728,7 +7776,7 @@
         <v>0.87638888888888888</v>
       </c>
       <c r="D4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E4">
         <v>30065</v>
@@ -7749,10 +7797,10 @@
         <v>265</v>
       </c>
       <c r="K4" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="L4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N4">
         <v>4</v>
@@ -7788,7 +7836,7 @@
         <v>0.87708333333333333</v>
       </c>
       <c r="D5" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E5">
         <v>30061</v>
@@ -7809,13 +7857,13 @@
         <v>265</v>
       </c>
       <c r="K5" t="s">
-        <v>279</v>
+        <v>919</v>
       </c>
       <c r="L5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="M5" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="N5">
         <v>2</v>
@@ -7851,7 +7899,7 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="D6" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="E6">
         <v>30090</v>
@@ -7872,10 +7920,10 @@
         <v>265</v>
       </c>
       <c r="K6" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L6" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -7911,7 +7959,7 @@
         <v>0.87708333333333333</v>
       </c>
       <c r="D7" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E7">
         <v>30665</v>
@@ -7932,13 +7980,13 @@
         <v>265</v>
       </c>
       <c r="K7" t="s">
-        <v>279</v>
+        <v>678</v>
       </c>
       <c r="L7" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M7" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N7">
         <v>2</v>
@@ -7974,7 +8022,7 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="D8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E8">
         <v>30106</v>
@@ -7998,7 +8046,7 @@
         <v>53</v>
       </c>
       <c r="L8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="N8">
         <v>1</v>
@@ -8034,7 +8082,7 @@
         <v>0.88749999999999996</v>
       </c>
       <c r="D9" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E9">
         <v>30183</v>
@@ -8055,7 +8103,7 @@
         <v>265</v>
       </c>
       <c r="K9" t="s">
-        <v>279</v>
+        <v>920</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -8088,7 +8136,7 @@
         <v>0.90972222222222221</v>
       </c>
       <c r="D10" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E10">
         <v>30025</v>
@@ -8109,10 +8157,10 @@
         <v>265</v>
       </c>
       <c r="K10" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L10" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -8148,7 +8196,7 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="D11" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E11">
         <v>30283</v>
@@ -8169,7 +8217,7 @@
         <v>265</v>
       </c>
       <c r="K11" t="s">
-        <v>539</v>
+        <v>921</v>
       </c>
       <c r="N11" t="s">
         <v>64</v>
@@ -8202,7 +8250,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D12" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E12">
         <v>30008</v>
@@ -8223,10 +8271,10 @@
         <v>265</v>
       </c>
       <c r="K12" t="s">
-        <v>539</v>
+        <v>922</v>
       </c>
       <c r="L12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -8262,7 +8310,7 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="D13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E13">
         <v>30244</v>
@@ -8286,7 +8334,7 @@
         <v>53</v>
       </c>
       <c r="L13" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="N13">
         <v>1</v>
@@ -8319,7 +8367,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D14" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E14">
         <v>30245</v>
@@ -8340,10 +8388,10 @@
         <v>265</v>
       </c>
       <c r="K14" t="s">
-        <v>539</v>
+        <v>279</v>
       </c>
       <c r="L14" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -8376,7 +8424,7 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="D15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E15">
         <v>30097</v>
@@ -8397,10 +8445,10 @@
         <v>265</v>
       </c>
       <c r="K15" t="s">
-        <v>539</v>
+        <v>266</v>
       </c>
       <c r="L15" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -8436,7 +8484,7 @@
         <v>0.86250000000000004</v>
       </c>
       <c r="D16" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E16">
         <v>30664</v>
@@ -8460,10 +8508,10 @@
         <v>279</v>
       </c>
       <c r="L16" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="M16" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="N16">
         <v>3</v>
@@ -8499,7 +8547,7 @@
         <v>0.91180555555555554</v>
       </c>
       <c r="D17" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E17">
         <v>30241</v>
@@ -8523,7 +8571,7 @@
         <v>539</v>
       </c>
       <c r="L17" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -8556,7 +8604,7 @@
         <v>0.8618055555555556</v>
       </c>
       <c r="D18" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E18">
         <v>30052</v>
@@ -8577,13 +8625,13 @@
         <v>265</v>
       </c>
       <c r="K18" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="L18" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M18" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="N18">
         <v>1</v>
@@ -8622,7 +8670,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D19" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E19">
         <v>30245</v>
@@ -8643,10 +8691,10 @@
         <v>265</v>
       </c>
       <c r="K19" t="s">
-        <v>539</v>
+        <v>279</v>
       </c>
       <c r="L19" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="N19">
         <v>1</v>
@@ -8679,7 +8727,7 @@
         <v>0.91041666666666665</v>
       </c>
       <c r="D20" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E20">
         <v>30239</v>
@@ -8703,7 +8751,7 @@
         <v>539</v>
       </c>
       <c r="L20" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N20">
         <v>1</v>
@@ -8736,7 +8784,7 @@
         <v>0.97847222222222219</v>
       </c>
       <c r="D21" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E21">
         <v>30242</v>
@@ -8760,7 +8808,7 @@
         <v>53</v>
       </c>
       <c r="L21" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N21">
         <v>1</v>
@@ -8793,7 +8841,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D22" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E22">
         <v>30081</v>
@@ -8814,10 +8862,10 @@
         <v>265</v>
       </c>
       <c r="K22" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L22" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N22">
         <v>1</v>
@@ -8853,7 +8901,7 @@
         <v>0.87777777777777777</v>
       </c>
       <c r="D23" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E23">
         <v>30023</v>
@@ -8874,7 +8922,7 @@
         <v>265</v>
       </c>
       <c r="K23" t="s">
-        <v>279</v>
+        <v>678</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -8910,7 +8958,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D24" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E24">
         <v>30245</v>
@@ -8931,10 +8979,10 @@
         <v>265</v>
       </c>
       <c r="K24" t="s">
-        <v>539</v>
+        <v>279</v>
       </c>
       <c r="L24" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -8967,7 +9015,7 @@
         <v>0.90902777777777777</v>
       </c>
       <c r="D25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E25">
         <v>30720</v>
@@ -8988,13 +9036,13 @@
         <v>265</v>
       </c>
       <c r="K25" t="s">
-        <v>539</v>
+        <v>335</v>
       </c>
       <c r="L25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M25" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -9030,7 +9078,7 @@
         <v>0.98055555555555551</v>
       </c>
       <c r="D26" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="E26">
         <v>30109</v>
@@ -9054,10 +9102,10 @@
         <v>53</v>
       </c>
       <c r="L26" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M26" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -9093,7 +9141,7 @@
         <v>0.97916666666666663</v>
       </c>
       <c r="D27" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E27">
         <v>30244</v>
@@ -9117,7 +9165,7 @@
         <v>53</v>
       </c>
       <c r="L27" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="N27">
         <v>1</v>
@@ -9150,7 +9198,7 @@
         <v>0.90069444444444446</v>
       </c>
       <c r="D28" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E28">
         <v>30029</v>
@@ -9171,10 +9219,10 @@
         <v>101</v>
       </c>
       <c r="K28" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L28" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="N28">
         <v>3</v>
@@ -9213,7 +9261,7 @@
         <v>0.90138888888888891</v>
       </c>
       <c r="D29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E29">
         <v>29949</v>
@@ -9234,10 +9282,10 @@
         <v>101</v>
       </c>
       <c r="K29" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L29" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N29">
         <v>2</v>
@@ -9273,7 +9321,7 @@
         <v>0.91111111111111109</v>
       </c>
       <c r="D30" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="E30">
         <v>29983</v>
@@ -9294,10 +9342,10 @@
         <v>101</v>
       </c>
       <c r="K30" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L30" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="N30">
         <v>3</v>
@@ -9333,7 +9381,7 @@
         <v>0.92986111111111114</v>
       </c>
       <c r="D31" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E31">
         <v>30249</v>
@@ -9354,10 +9402,10 @@
         <v>101</v>
       </c>
       <c r="K31" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L31" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -9390,7 +9438,7 @@
         <v>0.90069444444444446</v>
       </c>
       <c r="D32" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E32">
         <v>29918</v>
@@ -9411,10 +9459,10 @@
         <v>101</v>
       </c>
       <c r="K32" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L32" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="N32">
         <v>1</v>
@@ -9450,7 +9498,7 @@
         <v>0.93055555555555558</v>
       </c>
       <c r="D33" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E33">
         <v>32267</v>
@@ -9471,10 +9519,10 @@
         <v>101</v>
       </c>
       <c r="K33" t="s">
-        <v>102</v>
+        <v>678</v>
       </c>
       <c r="L33" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="N33">
         <v>1</v>
@@ -9510,7 +9558,7 @@
         <v>0.93055555555555558</v>
       </c>
       <c r="D34" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E34">
         <v>30028</v>
@@ -9531,13 +9579,13 @@
         <v>101</v>
       </c>
       <c r="K34" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L34" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M34" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="N34">
         <v>1</v>
@@ -9573,7 +9621,7 @@
         <v>0.90208333333333335</v>
       </c>
       <c r="D35" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E35">
         <v>29924</v>
@@ -9594,13 +9642,13 @@
         <v>101</v>
       </c>
       <c r="K35" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L35" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M35" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="N35">
         <v>2</v>
@@ -9636,7 +9684,7 @@
         <v>0.93055555555555558</v>
       </c>
       <c r="D36" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E36">
         <v>29950</v>
@@ -9657,10 +9705,10 @@
         <v>101</v>
       </c>
       <c r="K36" t="s">
-        <v>102</v>
+        <v>678</v>
       </c>
       <c r="L36" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N36">
         <v>2</v>
@@ -9696,7 +9744,7 @@
         <v>0.93125000000000002</v>
       </c>
       <c r="D37" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E37">
         <v>30322</v>
@@ -9717,7 +9765,7 @@
         <v>101</v>
       </c>
       <c r="K37" t="s">
-        <v>102</v>
+        <v>921</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -9750,7 +9798,7 @@
         <v>0.92986111111111114</v>
       </c>
       <c r="D38" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E38">
         <v>30250</v>
@@ -9771,10 +9819,10 @@
         <v>101</v>
       </c>
       <c r="K38" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L38" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N38">
         <v>1</v>
@@ -9807,7 +9855,7 @@
         <v>0.90069444444444446</v>
       </c>
       <c r="D39" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E39">
         <v>30029</v>
@@ -9828,10 +9876,10 @@
         <v>101</v>
       </c>
       <c r="K39" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L39" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N39">
         <v>4</v>
@@ -9867,7 +9915,7 @@
         <v>0.92986111111111114</v>
       </c>
       <c r="D40" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E40">
         <v>30249</v>
@@ -9888,10 +9936,10 @@
         <v>101</v>
       </c>
       <c r="K40" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L40" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="N40">
         <v>1</v>
@@ -9924,7 +9972,7 @@
         <v>0.93125000000000002</v>
       </c>
       <c r="D41" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E41">
         <v>30449</v>
@@ -9945,13 +9993,13 @@
         <v>101</v>
       </c>
       <c r="K41" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L41" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="M41" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="N41">
         <v>4</v>
@@ -9987,7 +10035,7 @@
         <v>0.87638888888888888</v>
       </c>
       <c r="D42" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E42">
         <v>30055</v>
@@ -10008,10 +10056,10 @@
         <v>265</v>
       </c>
       <c r="K42" t="s">
-        <v>335</v>
+        <v>266</v>
       </c>
       <c r="L42" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N42">
         <v>1</v>
@@ -10047,7 +10095,7 @@
         <v>0.89236111111111116</v>
       </c>
       <c r="D43" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E43">
         <v>30246</v>
@@ -10068,10 +10116,10 @@
         <v>265</v>
       </c>
       <c r="K43" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="L43" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N43">
         <v>1</v>
@@ -10104,7 +10152,7 @@
         <v>0.89236111111111116</v>
       </c>
       <c r="D44" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E44">
         <v>30246</v>
@@ -10125,10 +10173,10 @@
         <v>265</v>
       </c>
       <c r="K44" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="L44" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="N44">
         <v>1</v>
@@ -10161,7 +10209,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D45" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E45">
         <v>30240</v>
@@ -10182,10 +10230,10 @@
         <v>265</v>
       </c>
       <c r="K45" t="s">
-        <v>335</v>
+        <v>539</v>
       </c>
       <c r="L45" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="N45">
         <v>1</v>
@@ -10218,7 +10266,7 @@
         <v>0.87916666666666665</v>
       </c>
       <c r="D46" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E46">
         <v>30099</v>
@@ -10239,10 +10287,10 @@
         <v>265</v>
       </c>
       <c r="K46" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="L46" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N46">
         <v>4</v>
@@ -10278,7 +10326,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D47" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E47">
         <v>30096</v>
@@ -10299,10 +10347,10 @@
         <v>265</v>
       </c>
       <c r="K47" t="s">
-        <v>335</v>
+        <v>539</v>
       </c>
       <c r="L47" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="N47">
         <v>4</v>
@@ -10338,7 +10386,7 @@
         <v>0.87986111111111109</v>
       </c>
       <c r="D48" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E48">
         <v>30239</v>
@@ -10359,10 +10407,10 @@
         <v>265</v>
       </c>
       <c r="K48" t="s">
-        <v>335</v>
+        <v>539</v>
       </c>
       <c r="L48" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="N48">
         <v>1</v>
@@ -10395,7 +10443,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D49" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E49">
         <v>30079</v>
@@ -10416,10 +10464,10 @@
         <v>265</v>
       </c>
       <c r="K49" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L49" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="N49" t="s">
         <v>137</v>
@@ -10455,7 +10503,7 @@
         <v>0.87708333333333333</v>
       </c>
       <c r="D50" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E50">
         <v>33054</v>
@@ -10476,13 +10524,13 @@
         <v>265</v>
       </c>
       <c r="K50" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L50" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M50" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="N50">
         <v>3</v>
@@ -10518,7 +10566,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D51" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E51">
         <v>30082</v>
@@ -10542,10 +10590,10 @@
         <v>335</v>
       </c>
       <c r="L51" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M51" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="N51">
         <v>1</v>
@@ -10581,7 +10629,7 @@
         <v>0.87986111111111109</v>
       </c>
       <c r="D52" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E52">
         <v>30241</v>
@@ -10602,10 +10650,10 @@
         <v>265</v>
       </c>
       <c r="K52" t="s">
-        <v>335</v>
+        <v>539</v>
       </c>
       <c r="L52" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="N52">
         <v>1</v>
@@ -10638,7 +10686,7 @@
         <v>0.87708333333333333</v>
       </c>
       <c r="D53" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E53">
         <v>32516</v>
@@ -10659,10 +10707,10 @@
         <v>265</v>
       </c>
       <c r="K53" t="s">
-        <v>335</v>
+        <v>678</v>
       </c>
       <c r="L53" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="N53">
         <v>3</v>
@@ -10698,7 +10746,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D54" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E54">
         <v>30247</v>
@@ -10719,10 +10767,10 @@
         <v>265</v>
       </c>
       <c r="K54" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="L54" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N54">
         <v>1</v>
@@ -10755,7 +10803,7 @@
         <v>0.87708333333333333</v>
       </c>
       <c r="D55" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E55">
         <v>30060</v>
@@ -10776,10 +10824,10 @@
         <v>265</v>
       </c>
       <c r="K55" t="s">
-        <v>335</v>
+        <v>53</v>
       </c>
       <c r="L55" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="N55">
         <v>3</v>
@@ -10815,7 +10863,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D56" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E56">
         <v>30084</v>
@@ -10839,7 +10887,7 @@
         <v>335</v>
       </c>
       <c r="L56" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="N56">
         <v>1</v>
@@ -10878,7 +10926,7 @@
         <v>0.89236111111111116</v>
       </c>
       <c r="D57" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E57">
         <v>29992</v>
@@ -10902,7 +10950,7 @@
         <v>102</v>
       </c>
       <c r="L57" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="N57">
         <v>1</v>
@@ -10938,7 +10986,7 @@
         <v>0.89583333333333337</v>
       </c>
       <c r="D58" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E58">
         <v>29984</v>
@@ -10959,10 +11007,10 @@
         <v>101</v>
       </c>
       <c r="K58" t="s">
-        <v>102</v>
+        <v>919</v>
       </c>
       <c r="L58" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="N58">
         <v>2</v>
@@ -11001,7 +11049,7 @@
         <v>0.89375000000000004</v>
       </c>
       <c r="D59" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E59">
         <v>30238</v>
@@ -11025,7 +11073,7 @@
         <v>102</v>
       </c>
       <c r="L59" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="N59">
         <v>1</v>
@@ -11058,7 +11106,7 @@
         <v>0.90069444444444446</v>
       </c>
       <c r="D60" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="E60">
         <v>29951</v>
@@ -11079,10 +11127,10 @@
         <v>101</v>
       </c>
       <c r="K60" t="s">
-        <v>102</v>
+        <v>678</v>
       </c>
       <c r="L60" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="N60">
         <v>2</v>
@@ -11118,7 +11166,7 @@
         <v>0.89513888888888893</v>
       </c>
       <c r="D61" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="E61">
         <v>29947</v>
@@ -11139,10 +11187,10 @@
         <v>101</v>
       </c>
       <c r="K61" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L61" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="N61">
         <v>1</v>
@@ -11178,7 +11226,7 @@
         <v>0.89166666666666672</v>
       </c>
       <c r="D62" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E62">
         <v>30249</v>
@@ -11199,10 +11247,10 @@
         <v>101</v>
       </c>
       <c r="K62" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L62" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="N62">
         <v>1</v>
@@ -11235,7 +11283,7 @@
         <v>0.89375000000000004</v>
       </c>
       <c r="D63" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E63">
         <v>30250</v>
@@ -11256,10 +11304,10 @@
         <v>101</v>
       </c>
       <c r="K63" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L63" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="N63">
         <v>1</v>
@@ -11292,7 +11340,7 @@
         <v>0.89375000000000004</v>
       </c>
       <c r="D64" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E64">
         <v>30238</v>
@@ -11316,7 +11364,7 @@
         <v>102</v>
       </c>
       <c r="L64" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="N64">
         <v>1</v>
@@ -11349,7 +11397,7 @@
         <v>0.9</v>
       </c>
       <c r="D65" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E65">
         <v>29972</v>
@@ -11370,10 +11418,10 @@
         <v>101</v>
       </c>
       <c r="K65" t="s">
-        <v>102</v>
+        <v>678</v>
       </c>
       <c r="L65" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="N65">
         <v>3</v>
@@ -11409,7 +11457,7 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="D66" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E66">
         <v>30249</v>
@@ -11430,10 +11478,10 @@
         <v>101</v>
       </c>
       <c r="K66" t="s">
-        <v>102</v>
+        <v>677</v>
       </c>
       <c r="L66" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="N66">
         <v>1</v>
@@ -11466,7 +11514,7 @@
         <v>0.8930555555555556</v>
       </c>
       <c r="D67" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E67">
         <v>30237</v>
@@ -11490,7 +11538,7 @@
         <v>102</v>
       </c>
       <c r="L67" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="N67">
         <v>1</v>
@@ -11523,7 +11571,7 @@
         <v>0.89722222222222225</v>
       </c>
       <c r="D68" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E68">
         <v>29920</v>
@@ -11544,13 +11592,13 @@
         <v>101</v>
       </c>
       <c r="K68" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="L68" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="M68" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="N68">
         <v>1</v>
@@ -11586,7 +11634,7 @@
         <v>0.90208333333333335</v>
       </c>
       <c r="D69" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E69">
         <v>30026</v>
@@ -11607,10 +11655,10 @@
         <v>101</v>
       </c>
       <c r="K69" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L69" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="N69">
         <v>3</v>
@@ -11646,7 +11694,7 @@
         <v>0.9</v>
       </c>
       <c r="D70" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E70">
         <v>30447</v>
@@ -11667,13 +11715,13 @@
         <v>101</v>
       </c>
       <c r="K70" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L70" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M70" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N70" t="s">
         <v>64</v>
@@ -11709,7 +11757,7 @@
         <v>0.90069444444444446</v>
       </c>
       <c r="D71" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E71">
         <v>32405</v>
@@ -11763,7 +11811,7 @@
         <v>0.89722222222222225</v>
       </c>
       <c r="D72" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E72">
         <v>29962</v>
@@ -11784,13 +11832,13 @@
         <v>101</v>
       </c>
       <c r="K72" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L72" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="M72" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="N72">
         <v>4</v>
@@ -11826,7 +11874,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D73" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E73">
         <v>30029</v>
@@ -11847,10 +11895,10 @@
         <v>101</v>
       </c>
       <c r="K73" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L73" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="N73">
         <v>3</v>
@@ -11886,7 +11934,7 @@
         <v>0.84583333333333333</v>
       </c>
       <c r="D74" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E74">
         <v>30247</v>
@@ -11910,7 +11958,7 @@
         <v>279</v>
       </c>
       <c r="L74" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N74">
         <v>1</v>
@@ -11943,7 +11991,7 @@
         <v>0.85833333333333328</v>
       </c>
       <c r="D75" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E75">
         <v>30075</v>
@@ -11964,10 +12012,10 @@
         <v>265</v>
       </c>
       <c r="K75" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L75" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="N75">
         <v>3</v>
@@ -12003,7 +12051,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D76" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E76">
         <v>28822</v>
@@ -12024,10 +12072,10 @@
         <v>675</v>
       </c>
       <c r="K76" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L76" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="N76">
         <v>3</v>
@@ -12063,7 +12111,7 @@
         <v>0.87777777777777777</v>
       </c>
       <c r="D77" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E77">
         <v>30244</v>
@@ -12087,7 +12135,7 @@
         <v>53</v>
       </c>
       <c r="L77" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N77">
         <v>1</v>
@@ -12120,7 +12168,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D78" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E78">
         <v>29762</v>
@@ -12141,10 +12189,10 @@
         <v>675</v>
       </c>
       <c r="K78" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L78" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="N78">
         <v>4</v>
@@ -12177,7 +12225,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D79" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E79">
         <v>29765</v>
@@ -12198,10 +12246,10 @@
         <v>675</v>
       </c>
       <c r="K79" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L79" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -12234,7 +12282,7 @@
         <v>0.90555555555555556</v>
       </c>
       <c r="D80" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E80">
         <v>29765</v>
@@ -12255,10 +12303,10 @@
         <v>676</v>
       </c>
       <c r="K80" t="s">
-        <v>177</v>
+        <v>923</v>
       </c>
       <c r="L80" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="N80">
         <v>4</v>
@@ -12291,7 +12339,7 @@
         <v>0.87777777777777777</v>
       </c>
       <c r="D81" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E81">
         <v>30244</v>
@@ -12315,7 +12363,7 @@
         <v>53</v>
       </c>
       <c r="L81" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N81">
         <v>1</v>
@@ -12348,7 +12396,7 @@
         <v>0.87777777777777777</v>
       </c>
       <c r="D82" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E82">
         <v>30242</v>
@@ -12372,7 +12420,7 @@
         <v>53</v>
       </c>
       <c r="L82" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="N82">
         <v>1</v>
@@ -12405,7 +12453,7 @@
         <v>0.81527777777777777</v>
       </c>
       <c r="D83" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E83">
         <v>30060</v>
@@ -12426,10 +12474,10 @@
         <v>265</v>
       </c>
       <c r="K83" t="s">
-        <v>452</v>
+        <v>53</v>
       </c>
       <c r="L83" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="N83">
         <v>4</v>
@@ -12465,7 +12513,7 @@
         <v>0.84513888888888888</v>
       </c>
       <c r="D84" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E84">
         <v>30626</v>
@@ -12489,10 +12537,10 @@
         <v>279</v>
       </c>
       <c r="L84" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M84" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="N84">
         <v>2</v>
@@ -12528,7 +12576,7 @@
         <v>0.90555555555555556</v>
       </c>
       <c r="D85" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E85">
         <v>29753</v>
@@ -12552,7 +12600,7 @@
         <v>177</v>
       </c>
       <c r="L85" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="N85">
         <v>1</v>
@@ -12585,7 +12633,7 @@
         <v>0.90625</v>
       </c>
       <c r="D86" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E86">
         <v>32386</v>
@@ -12639,7 +12687,7 @@
         <v>0.87986111111111109</v>
       </c>
       <c r="D87" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E87">
         <v>30108</v>
@@ -12660,10 +12708,10 @@
         <v>265</v>
       </c>
       <c r="K87" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="L87" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="N87">
         <v>1</v>
@@ -12699,7 +12747,7 @@
         <v>0.90555555555555556</v>
       </c>
       <c r="D88" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E88">
         <v>29753</v>
@@ -12723,7 +12771,7 @@
         <v>177</v>
       </c>
       <c r="L88" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="N88">
         <v>2</v>
@@ -12756,7 +12804,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D89" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E89">
         <v>28799</v>
@@ -12777,10 +12825,10 @@
         <v>675</v>
       </c>
       <c r="K89" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L89" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="N89">
         <v>3</v>
@@ -12816,7 +12864,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D90" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E90">
         <v>29764</v>
@@ -12837,10 +12885,10 @@
         <v>675</v>
       </c>
       <c r="K90" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L90" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="N90">
         <v>1</v>
@@ -12873,7 +12921,7 @@
         <v>0.90625</v>
       </c>
       <c r="D91" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E91">
         <v>28774</v>
@@ -12897,10 +12945,10 @@
         <v>177</v>
       </c>
       <c r="L91" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M91" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N91">
         <v>4</v>
@@ -12936,7 +12984,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="D92" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E92">
         <v>30629</v>
@@ -12957,13 +13005,13 @@
         <v>265</v>
       </c>
       <c r="K92" t="s">
-        <v>266</v>
+        <v>919</v>
       </c>
       <c r="L92" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M92" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="N92" t="s">
         <v>64</v>
@@ -12999,7 +13047,7 @@
         <v>0.84444444444444444</v>
       </c>
       <c r="D93" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E93">
         <v>30027</v>
@@ -13020,10 +13068,10 @@
         <v>265</v>
       </c>
       <c r="K93" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L93" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N93">
         <v>1</v>
@@ -13059,7 +13107,7 @@
         <v>0.84444444444444444</v>
       </c>
       <c r="D94" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E94">
         <v>30027</v>
@@ -13080,10 +13128,10 @@
         <v>265</v>
       </c>
       <c r="K94" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L94" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="N94">
         <v>1</v>
@@ -13119,7 +13167,7 @@
         <v>0.84583333333333333</v>
       </c>
       <c r="D95" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E95">
         <v>30246</v>
@@ -13143,7 +13191,7 @@
         <v>279</v>
       </c>
       <c r="L95" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="N95">
         <v>1</v>
@@ -13176,7 +13224,7 @@
         <v>0.90486111111111112</v>
       </c>
       <c r="D96" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E96">
         <v>29753</v>
@@ -13200,7 +13248,7 @@
         <v>177</v>
       </c>
       <c r="L96" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="N96">
         <v>1</v>
@@ -13233,7 +13281,7 @@
         <v>0.80208333333333337</v>
       </c>
       <c r="D97" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E97">
         <v>30050</v>
@@ -13257,7 +13305,7 @@
         <v>266</v>
       </c>
       <c r="L97" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="N97">
         <v>2</v>
@@ -13296,7 +13344,7 @@
         <v>0.83680555555555558</v>
       </c>
       <c r="D98" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E98">
         <v>30240</v>
@@ -13320,7 +13368,7 @@
         <v>539</v>
       </c>
       <c r="L98" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="N98">
         <v>3</v>
@@ -13353,7 +13401,7 @@
         <v>0.87916666666666665</v>
       </c>
       <c r="D99" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E99">
         <v>30106</v>
@@ -13377,7 +13425,7 @@
         <v>53</v>
       </c>
       <c r="L99" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="N99">
         <v>1</v>
@@ -13413,7 +13461,7 @@
         <v>0.89097222222222228</v>
       </c>
       <c r="D100" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E100">
         <v>28830</v>
@@ -13434,13 +13482,13 @@
         <v>675</v>
       </c>
       <c r="K100" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L100" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="M100" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="N100">
         <v>1</v>
@@ -13476,7 +13524,7 @@
         <v>0.81527777777777777</v>
       </c>
       <c r="D101" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E101">
         <v>30063</v>
@@ -13497,7 +13545,7 @@
         <v>265</v>
       </c>
       <c r="K101" t="s">
-        <v>452</v>
+        <v>919</v>
       </c>
       <c r="N101">
         <v>3</v>
@@ -13533,7 +13581,7 @@
         <v>0.83680555555555558</v>
       </c>
       <c r="D102" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E102">
         <v>30239</v>
@@ -13557,7 +13605,7 @@
         <v>539</v>
       </c>
       <c r="L102" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="N102">
         <v>2</v>
@@ -13590,7 +13638,7 @@
         <v>0.83680555555555558</v>
       </c>
       <c r="D103" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E103">
         <v>30097</v>
@@ -13611,10 +13659,10 @@
         <v>265</v>
       </c>
       <c r="K103" t="s">
-        <v>539</v>
+        <v>266</v>
       </c>
       <c r="L103" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="N103">
         <v>3</v>
@@ -13650,7 +13698,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D104" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E104">
         <v>29763</v>
@@ -13671,10 +13719,10 @@
         <v>675</v>
       </c>
       <c r="K104" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L104" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="N104">
         <v>1</v>
@@ -13707,7 +13755,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D105" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E105">
         <v>29766</v>
@@ -13728,10 +13776,10 @@
         <v>675</v>
       </c>
       <c r="K105" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L105" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="N105">
         <v>2</v>
@@ -13764,7 +13812,7 @@
         <v>0.84513888888888888</v>
       </c>
       <c r="D106" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E106">
         <v>30247</v>
@@ -13788,7 +13836,7 @@
         <v>279</v>
       </c>
       <c r="L106" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N106">
         <v>1</v>
@@ -13821,7 +13869,7 @@
         <v>0.85833333333333328</v>
       </c>
       <c r="D107" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E107">
         <v>30720</v>
@@ -13878,7 +13926,7 @@
         <v>0.85833333333333328</v>
       </c>
       <c r="D108" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E108">
         <v>30081</v>
@@ -13899,10 +13947,10 @@
         <v>265</v>
       </c>
       <c r="K108" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L108" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N108">
         <v>1</v>
@@ -13938,7 +13986,7 @@
         <v>0.90555555555555556</v>
       </c>
       <c r="D109" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E109">
         <v>29753</v>
@@ -13962,7 +14010,7 @@
         <v>177</v>
       </c>
       <c r="L109" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N109">
         <v>1</v>
@@ -13995,7 +14043,7 @@
         <v>0.80138888888888893</v>
       </c>
       <c r="D110" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="E110">
         <v>30054</v>
@@ -14016,10 +14064,10 @@
         <v>265</v>
       </c>
       <c r="K110" t="s">
-        <v>266</v>
+        <v>102</v>
       </c>
       <c r="L110" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="N110">
         <v>3</v>
@@ -14055,7 +14103,7 @@
         <v>0.89444444444444449</v>
       </c>
       <c r="D111" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E111">
         <v>29766</v>
@@ -14076,10 +14124,10 @@
         <v>675</v>
       </c>
       <c r="K111" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L111" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="N111">
         <v>1</v>
@@ -14112,7 +14160,7 @@
         <v>0.81527777777777777</v>
       </c>
       <c r="D112" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E112">
         <v>30058</v>
@@ -14133,10 +14181,10 @@
         <v>265</v>
       </c>
       <c r="K112" t="s">
-        <v>452</v>
+        <v>925</v>
       </c>
       <c r="L112" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="N112">
         <v>4</v>
@@ -14172,7 +14220,7 @@
         <v>0.83680555555555558</v>
       </c>
       <c r="D113" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E113">
         <v>30240</v>
@@ -14196,7 +14244,7 @@
         <v>539</v>
       </c>
       <c r="L113" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="N113">
         <v>1</v>
@@ -14229,7 +14277,7 @@
         <v>0.90625</v>
       </c>
       <c r="D114" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E114">
         <v>28789</v>
@@ -14253,10 +14301,10 @@
         <v>177</v>
       </c>
       <c r="L114" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="M114" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N114">
         <v>1</v>
@@ -14292,7 +14340,7 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="D115" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E115">
         <v>29993</v>
@@ -14349,7 +14397,7 @@
         <v>0.81805555555555554</v>
       </c>
       <c r="D116" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="E116">
         <v>29984</v>
@@ -14370,10 +14418,10 @@
         <v>101</v>
       </c>
       <c r="K116" t="s">
-        <v>678</v>
+        <v>919</v>
       </c>
       <c r="L116" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="N116">
         <v>2</v>
@@ -14409,7 +14457,7 @@
         <v>0.85</v>
       </c>
       <c r="D117" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E117">
         <v>29987</v>
@@ -14433,7 +14481,7 @@
         <v>102</v>
       </c>
       <c r="L117" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="N117">
         <v>1</v>
@@ -14469,7 +14517,7 @@
         <v>0.80972222222222223</v>
       </c>
       <c r="D118" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E118">
         <v>30447</v>
@@ -14490,13 +14538,13 @@
         <v>101</v>
       </c>
       <c r="K118" t="s">
-        <v>212</v>
+        <v>922</v>
       </c>
       <c r="L118" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="M118" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="N118">
         <v>4</v>
@@ -14532,7 +14580,7 @@
         <v>0.84861111111111109</v>
       </c>
       <c r="D119" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E119">
         <v>30237</v>
@@ -14556,7 +14604,7 @@
         <v>102</v>
       </c>
       <c r="L119" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="N119">
         <v>1</v>
@@ -14589,7 +14637,7 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="D120" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="E120">
         <v>30238</v>
@@ -14613,7 +14661,7 @@
         <v>102</v>
       </c>
       <c r="L120" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="N120">
         <v>1</v>
@@ -14649,7 +14697,7 @@
         <v>0.81805555555555554</v>
       </c>
       <c r="D121" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E121">
         <v>30250</v>
@@ -14670,10 +14718,10 @@
         <v>101</v>
       </c>
       <c r="K121" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L121" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="N121">
         <v>1</v>
@@ -14709,7 +14757,7 @@
         <v>0.80694444444444446</v>
       </c>
       <c r="D122" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E122">
         <v>29922</v>
@@ -14733,10 +14781,10 @@
         <v>212</v>
       </c>
       <c r="L122" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M122" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N122">
         <v>1</v>
@@ -14772,7 +14820,7 @@
         <v>0.81874999999999998</v>
       </c>
       <c r="D123" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E123">
         <v>30250</v>
@@ -14793,10 +14841,10 @@
         <v>101</v>
       </c>
       <c r="K123" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L123" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N123">
         <v>1</v>
@@ -14829,7 +14877,7 @@
         <v>0.81736111111111109</v>
       </c>
       <c r="D124" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E124">
         <v>30448</v>
@@ -14853,10 +14901,10 @@
         <v>212</v>
       </c>
       <c r="L124" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="M124" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="N124" t="s">
         <v>64</v>
@@ -14892,7 +14940,7 @@
         <v>0.81874999999999998</v>
       </c>
       <c r="D125" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E125">
         <v>30248</v>
@@ -14913,10 +14961,10 @@
         <v>101</v>
       </c>
       <c r="K125" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L125" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="N125">
         <v>1</v>
@@ -14949,7 +14997,7 @@
         <v>0.85138888888888886</v>
       </c>
       <c r="D126" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E126">
         <v>32405</v>
@@ -15003,7 +15051,7 @@
         <v>0.84930555555555554</v>
       </c>
       <c r="D127" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E127">
         <v>30237</v>
@@ -15027,7 +15075,7 @@
         <v>102</v>
       </c>
       <c r="L127" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="N127">
         <v>1</v>
@@ -15060,7 +15108,7 @@
         <v>0.80347222222222225</v>
       </c>
       <c r="D128" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="E128">
         <v>30283</v>
@@ -15081,7 +15129,7 @@
         <v>265</v>
       </c>
       <c r="K128" t="s">
-        <v>266</v>
+        <v>921</v>
       </c>
       <c r="N128">
         <v>4</v>
@@ -15114,7 +15162,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D129" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E129">
         <v>30100</v>
@@ -15135,10 +15183,10 @@
         <v>265</v>
       </c>
       <c r="K129" t="s">
-        <v>279</v>
+        <v>539</v>
       </c>
       <c r="L129" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="N129">
         <v>1</v>
@@ -15174,7 +15222,7 @@
         <v>0.86388888888888893</v>
       </c>
       <c r="D130" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="E130">
         <v>30081</v>
@@ -15195,10 +15243,10 @@
         <v>265</v>
       </c>
       <c r="K130" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L130" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="N130">
         <v>1</v>
@@ -15234,7 +15282,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D131" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E131">
         <v>30063</v>
@@ -15255,7 +15303,7 @@
         <v>265</v>
       </c>
       <c r="K131" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="N131">
         <v>4</v>
@@ -15291,7 +15339,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D132" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E132">
         <v>30057</v>
@@ -15312,10 +15360,10 @@
         <v>265</v>
       </c>
       <c r="K132" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="L132" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="N132">
         <v>1</v>
@@ -15351,7 +15399,7 @@
         <v>0.82291666666666663</v>
       </c>
       <c r="D133" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E133">
         <v>30302</v>
@@ -15372,7 +15420,7 @@
         <v>265</v>
       </c>
       <c r="K133" t="s">
-        <v>452</v>
+        <v>921</v>
       </c>
       <c r="N133">
         <v>1</v>
@@ -15405,7 +15453,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D134" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E134">
         <v>30066</v>
@@ -15426,10 +15474,10 @@
         <v>265</v>
       </c>
       <c r="K134" t="s">
-        <v>53</v>
+        <v>678</v>
       </c>
       <c r="L134" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="N134">
         <v>3</v>
@@ -15465,7 +15513,7 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="D135" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E135">
         <v>30245</v>
@@ -15489,7 +15537,7 @@
         <v>279</v>
       </c>
       <c r="L135" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="N135">
         <v>1</v>
@@ -15525,7 +15573,7 @@
         <v>0.86805555555555558</v>
       </c>
       <c r="D136" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="E136">
         <v>30022</v>
@@ -15546,10 +15594,10 @@
         <v>265</v>
       </c>
       <c r="K136" t="s">
-        <v>335</v>
+        <v>922</v>
       </c>
       <c r="L136" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="N136">
         <v>1</v>
@@ -15585,7 +15633,7 @@
         <v>0.85277777777777775</v>
       </c>
       <c r="D137" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E137">
         <v>30246</v>
@@ -15609,7 +15657,7 @@
         <v>279</v>
       </c>
       <c r="L137" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N137">
         <v>1</v>
@@ -15642,7 +15690,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D138" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E138">
         <v>30247</v>
@@ -15666,7 +15714,7 @@
         <v>279</v>
       </c>
       <c r="L138" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N138">
         <v>1</v>
@@ -15699,7 +15747,7 @@
         <v>0.8305555555555556</v>
       </c>
       <c r="D139" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E139">
         <v>30025</v>
@@ -15720,10 +15768,10 @@
         <v>265</v>
       </c>
       <c r="K139" t="s">
-        <v>539</v>
+        <v>919</v>
       </c>
       <c r="L139" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N139">
         <v>4</v>
@@ -15759,7 +15807,7 @@
         <v>0.86597222222222225</v>
       </c>
       <c r="D140" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E140">
         <v>30324</v>
@@ -15780,7 +15828,7 @@
         <v>265</v>
       </c>
       <c r="K140" t="s">
-        <v>335</v>
+        <v>921</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -15813,7 +15861,7 @@
         <v>0.88055555555555554</v>
       </c>
       <c r="D141" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E141">
         <v>30053</v>
@@ -15834,10 +15882,10 @@
         <v>265</v>
       </c>
       <c r="K141" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="L141" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="N141">
         <v>3</v>
@@ -15873,7 +15921,7 @@
         <v>0.88680555555555551</v>
       </c>
       <c r="D142" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="E142">
         <v>30106</v>
@@ -15897,7 +15945,7 @@
         <v>53</v>
       </c>
       <c r="L142" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="N142">
         <v>1</v>
@@ -15933,7 +15981,7 @@
         <v>0.86319444444444449</v>
       </c>
       <c r="D143" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E143">
         <v>30075</v>
@@ -15954,10 +16002,10 @@
         <v>265</v>
       </c>
       <c r="K143" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L143" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="N143">
         <v>3</v>
@@ -15993,7 +16041,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D144" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E144">
         <v>30242</v>
@@ -16017,7 +16065,7 @@
         <v>53</v>
       </c>
       <c r="L144" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="N144">
         <v>1</v>
@@ -16050,7 +16098,7 @@
         <v>0.88472222222222219</v>
       </c>
       <c r="D145" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E145">
         <v>30112</v>
@@ -16071,10 +16119,10 @@
         <v>265</v>
       </c>
       <c r="K145" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="L145" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="N145">
         <v>1</v>
@@ -16110,7 +16158,7 @@
         <v>0.86388888888888893</v>
       </c>
       <c r="D146" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E146">
         <v>33058</v>
@@ -16131,13 +16179,13 @@
         <v>265</v>
       </c>
       <c r="K146" t="s">
-        <v>335</v>
+        <v>919</v>
       </c>
       <c r="L146" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="M146" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="N146">
         <v>4</v>
@@ -16173,7 +16221,7 @@
         <v>0.88472222222222219</v>
       </c>
       <c r="D147" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E147">
         <v>30244</v>
@@ -16197,7 +16245,7 @@
         <v>53</v>
       </c>
       <c r="L147" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="N147">
         <v>1</v>
@@ -16230,7 +16278,7 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="D148" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E148">
         <v>30306</v>
@@ -16251,7 +16299,7 @@
         <v>265</v>
       </c>
       <c r="K148" t="s">
-        <v>279</v>
+        <v>921</v>
       </c>
       <c r="N148">
         <v>1</v>
@@ -16284,7 +16332,7 @@
         <v>0.87986111111111109</v>
       </c>
       <c r="D149" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E149">
         <v>30048</v>
@@ -16305,10 +16353,10 @@
         <v>265</v>
       </c>
       <c r="K149" t="s">
-        <v>53</v>
+        <v>266</v>
       </c>
       <c r="L149" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="N149">
         <v>1</v>
@@ -16344,7 +16392,7 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="D150" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E150">
         <v>30025</v>
@@ -16365,10 +16413,10 @@
         <v>265</v>
       </c>
       <c r="K150" t="s">
-        <v>53</v>
+        <v>919</v>
       </c>
       <c r="L150" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="N150">
         <v>1</v>
@@ -16404,7 +16452,7 @@
         <v>0.88124999999999998</v>
       </c>
       <c r="D151" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E151">
         <v>30049</v>
@@ -16425,10 +16473,10 @@
         <v>265</v>
       </c>
       <c r="K151" t="s">
-        <v>53</v>
+        <v>335</v>
       </c>
       <c r="L151" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="N151">
         <v>1</v>
@@ -16464,7 +16512,7 @@
         <v>0.81180555555555556</v>
       </c>
       <c r="D152" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E152">
         <v>29922</v>
@@ -16488,10 +16536,10 @@
         <v>212</v>
       </c>
       <c r="L152" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M152" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="N152">
         <v>1</v>
@@ -16527,7 +16575,7 @@
         <v>0.8256944444444444</v>
       </c>
       <c r="D153" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E153">
         <v>29986</v>
@@ -16548,10 +16596,10 @@
         <v>101</v>
       </c>
       <c r="K153" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L153" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="N153">
         <v>1</v>
@@ -16587,7 +16635,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D154" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E154">
         <v>29764</v>
@@ -16608,10 +16656,10 @@
         <v>675</v>
       </c>
       <c r="K154" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L154" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="N154">
         <v>4</v>
@@ -16644,7 +16692,7 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="D155" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E155">
         <v>29753</v>
@@ -16668,7 +16716,7 @@
         <v>177</v>
       </c>
       <c r="L155" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N155">
         <v>4</v>
@@ -16701,7 +16749,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D156" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E156">
         <v>30237</v>
@@ -16725,7 +16773,7 @@
         <v>102</v>
       </c>
       <c r="L156" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="N156">
         <v>1</v>
@@ -16758,7 +16806,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D157" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E157">
         <v>32405</v>
@@ -16812,7 +16860,7 @@
         <v>0.87222222222222223</v>
       </c>
       <c r="D158" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E158">
         <v>28794</v>
@@ -16833,13 +16881,13 @@
         <v>675</v>
       </c>
       <c r="K158" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L158" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="M158" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="N158">
         <v>3</v>
@@ -16875,7 +16923,7 @@
         <v>0.875</v>
       </c>
       <c r="D159" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E159">
         <v>29767</v>
@@ -16896,10 +16944,10 @@
         <v>675</v>
       </c>
       <c r="K159" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L159" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="N159">
         <v>1</v>
@@ -16932,7 +16980,7 @@
         <v>0.85624999999999996</v>
       </c>
       <c r="D160" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E160">
         <v>30448</v>
@@ -16956,10 +17004,10 @@
         <v>212</v>
       </c>
       <c r="L160" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="M160" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="N160">
         <v>1</v>
@@ -16995,7 +17043,7 @@
         <v>0.85486111111111107</v>
       </c>
       <c r="D161" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E161">
         <v>29982</v>
@@ -17016,10 +17064,10 @@
         <v>101</v>
       </c>
       <c r="K161" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L161" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="N161">
         <v>1</v>
@@ -17058,7 +17106,7 @@
         <v>0.81180555555555556</v>
       </c>
       <c r="D162" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="E162">
         <v>29921</v>
@@ -17079,10 +17127,10 @@
         <v>101</v>
       </c>
       <c r="K162" t="s">
-        <v>212</v>
+        <v>922</v>
       </c>
       <c r="L162" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="N162">
         <v>2</v>
@@ -17118,7 +17166,7 @@
         <v>0.87152777777777779</v>
       </c>
       <c r="D163" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E163">
         <v>28823</v>
@@ -17139,13 +17187,13 @@
         <v>675</v>
       </c>
       <c r="K163" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L163" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="M163" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="N163">
         <v>3</v>
@@ -17181,7 +17229,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D164" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E164">
         <v>29763</v>
@@ -17202,10 +17250,10 @@
         <v>675</v>
       </c>
       <c r="K164" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L164" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="N164">
         <v>4</v>
@@ -17241,7 +17289,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D165" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E165">
         <v>30249</v>
@@ -17262,10 +17310,10 @@
         <v>101</v>
       </c>
       <c r="K165" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L165" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="N165">
         <v>1</v>
@@ -17298,7 +17346,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D166" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E166">
         <v>29762</v>
@@ -17319,10 +17367,10 @@
         <v>675</v>
       </c>
       <c r="K166" t="s">
-        <v>677</v>
+        <v>924</v>
       </c>
       <c r="L166" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="N166">
         <v>2</v>
@@ -17355,7 +17403,7 @@
         <v>0.87083333333333335</v>
       </c>
       <c r="D167" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E167">
         <v>29765</v>
@@ -17376,10 +17424,10 @@
         <v>675</v>
       </c>
       <c r="K167" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L167" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N167">
         <v>2</v>
@@ -17412,7 +17460,7 @@
         <v>0.875</v>
       </c>
       <c r="D168" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E168">
         <v>29765</v>
@@ -17433,10 +17481,10 @@
         <v>675</v>
       </c>
       <c r="K168" t="s">
-        <v>677</v>
+        <v>923</v>
       </c>
       <c r="L168" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N168">
         <v>2</v>
@@ -17469,7 +17517,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D169" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E169">
         <v>29981</v>
@@ -17490,13 +17538,13 @@
         <v>101</v>
       </c>
       <c r="K169" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="L169" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="M169" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="N169">
         <v>3</v>
@@ -17532,7 +17580,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D170" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E170">
         <v>30237</v>
@@ -17556,7 +17604,7 @@
         <v>102</v>
       </c>
       <c r="L170" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="N170">
         <v>1</v>
@@ -17589,7 +17637,7 @@
         <v>0.85347222222222219</v>
       </c>
       <c r="D171" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E171">
         <v>29988</v>
@@ -17613,10 +17661,10 @@
         <v>102</v>
       </c>
       <c r="L171" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="M171" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="N171">
         <v>1</v>
@@ -17652,7 +17700,7 @@
         <v>0.82499999999999996</v>
       </c>
       <c r="D172" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E172">
         <v>30248</v>
@@ -17673,10 +17721,10 @@
         <v>101</v>
       </c>
       <c r="K172" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L172" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="N172">
         <v>1</v>
@@ -17709,7 +17757,7 @@
         <v>0.88194444444444442</v>
       </c>
       <c r="D173" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E173">
         <v>28800</v>
@@ -17730,13 +17778,13 @@
         <v>675</v>
       </c>
       <c r="K173" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L173" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="M173" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="N173" t="s">
         <v>64</v>
@@ -17772,7 +17820,7 @@
         <v>0.83402777777777781</v>
       </c>
       <c r="D174" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E174">
         <v>29965</v>
@@ -17793,10 +17841,10 @@
         <v>101</v>
       </c>
       <c r="K174" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="L174" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N174">
         <v>2</v>
@@ -17832,7 +17880,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D175" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E175">
         <v>32386</v>
@@ -17886,7 +17934,7 @@
         <v>0.88263888888888886</v>
       </c>
       <c r="D176" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E176">
         <v>29753</v>
@@ -17910,7 +17958,7 @@
         <v>177</v>
       </c>
       <c r="L176" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N176" t="s">
         <v>64</v>
@@ -17943,7 +17991,7 @@
         <v>0.8833333333333333</v>
       </c>
       <c r="D177" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E177">
         <v>29753</v>
@@ -17967,7 +18015,7 @@
         <v>177</v>
       </c>
       <c r="L177" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="N177" t="s">
         <v>64</v>
@@ -18000,7 +18048,7 @@
         <v>0.8256944444444444</v>
       </c>
       <c r="D178" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E178">
         <v>30248</v>
@@ -18021,10 +18069,10 @@
         <v>101</v>
       </c>
       <c r="K178" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="L178" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N178">
         <v>1</v>
@@ -18057,7 +18105,7 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="D179" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E179">
         <v>29997</v>
@@ -18078,13 +18126,13 @@
         <v>101</v>
       </c>
       <c r="K179" t="s">
-        <v>102</v>
+        <v>922</v>
       </c>
       <c r="L179" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="M179" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="N179">
         <v>1</v>
@@ -18120,7 +18168,7 @@
         <v>0.85555555555555551</v>
       </c>
       <c r="D180" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="E180">
         <v>30236</v>
@@ -18144,7 +18192,7 @@
         <v>102</v>
       </c>
       <c r="L180" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N180">
         <v>1</v>
@@ -32225,12 +32273,12 @@
         <v>MAGE</v>
       </c>
       <c r="W4" t="str" cm="1">
-        <f t="array" ref="W4:W15">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
+        <f t="array" ref="W4:W20">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
         <v>Al'ar</v>
       </c>
       <c r="X4" s="11">
         <f>IF(W4="","",COUNTIF('Loot History'!$K:$K,W4))</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Z4" s="4" cm="1">
         <f t="array" ref="Z4:Z11">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!B2:B1000,'Loot History'!B2:B1000&lt;&gt;""))),"")</f>
@@ -32293,7 +32341,7 @@
       </c>
       <c r="X5" s="11">
         <f>IF(W5="","",COUNTIF('Loot History'!$K:$K,W5))</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Z5" s="4">
         <v>46161</v>
@@ -32351,11 +32399,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W6" t="str">
-        <v>Gruul the Dragonslayer</v>
+        <v>Fathom-Lord Karathress / Morogrim</v>
       </c>
       <c r="X6" s="11">
         <f>IF(W6="","",COUNTIF('Loot History'!$K:$K,W6))</f>
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Z6" s="4">
         <v>46163</v>
@@ -32413,11 +32461,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W7" t="str">
-        <v>High Astromancer Solarian</v>
+        <v>Gruul the Dragonkiller</v>
       </c>
       <c r="X7" s="11">
         <f>IF(W7="","",COUNTIF('Loot History'!$K:$K,W7))</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Z7" s="4">
         <v>46167</v>
@@ -32437,7 +32485,7 @@
       </c>
       <c r="B8" s="7" cm="1">
         <f t="array" ref="B8">SUMPRODUCT(('Loot History'!K2:K1000&lt;&gt;"")/COUNTIF('Loot History'!K2:K1000,'Loot History'!K2:K1000&amp;""))</f>
-        <v>11.999999999999996</v>
+        <v>16.999999999999989</v>
       </c>
       <c r="D8" t="str">
         <v>Fetzine-Thunderstrike</v>
@@ -32475,11 +32523,11 @@
         <v>HUNTER</v>
       </c>
       <c r="W8" t="str">
-        <v>Hydross the Unstable</v>
+        <v>High Astromancer Solarian</v>
       </c>
       <c r="X8" s="11">
         <f>IF(W8="","",COUNTIF('Loot History'!$K:$K,W8))</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Z8" s="4">
         <v>46170</v>
@@ -32530,11 +32578,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W9" t="str">
-        <v>Kael'thas Sunstrider</v>
+        <v>High King Maulgar</v>
       </c>
       <c r="X9" s="11">
         <f>IF(W9="","",COUNTIF('Loot History'!$K:$K,W9))</f>
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Z9" s="4">
         <v>46174</v>
@@ -32585,11 +32633,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W10" t="str">
-        <v>Lady Vashj</v>
+        <v>Hydross the Unstable</v>
       </c>
       <c r="X10" s="11">
         <f>IF(W10="","",COUNTIF('Loot History'!$K:$K,W10))</f>
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="4">
         <v>46177</v>
@@ -32640,11 +32688,11 @@
         <v>SHAMAN</v>
       </c>
       <c r="W11" t="str">
-        <v>Leotheras the Blind</v>
+        <v>Kael'thas Sunstrider</v>
       </c>
       <c r="X11" s="11">
         <f>IF(W11="","",COUNTIF('Loot History'!$K:$K,W11))</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Z11" s="4">
         <v>46181</v>
@@ -32695,11 +32743,11 @@
         <v>DRUID</v>
       </c>
       <c r="W12" t="str">
-        <v>Magtheridon</v>
+        <v>Lady Vashj</v>
       </c>
       <c r="X12" s="11">
         <f>IF(W12="","",COUNTIF('Loot History'!$K:$K,W12))</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="11" t="str">
@@ -32748,11 +32796,11 @@
         <v>ROGUE</v>
       </c>
       <c r="W13" t="str">
-        <v>Morogrim Tidewalker</v>
+        <v>Leotheras the Blind</v>
       </c>
       <c r="X13" s="11">
         <f>IF(W13="","",COUNTIF('Loot History'!$K:$K,W13))</f>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="11" t="str">
@@ -32801,11 +32849,11 @@
         <v>DRUID</v>
       </c>
       <c r="W14" t="str">
-        <v>The Lurker Below</v>
+        <v>Magtheridon</v>
       </c>
       <c r="X14" s="11">
         <f>IF(W14="","",COUNTIF('Loot History'!$K:$K,W14))</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="11" t="str">
@@ -32854,11 +32902,11 @@
         <v>HUNTER</v>
       </c>
       <c r="W15" t="str">
-        <v>Void Reaver</v>
+        <v>Morogrim Tidewalker</v>
       </c>
       <c r="X15" s="11">
         <f>IF(W15="","",COUNTIF('Loot History'!$K:$K,W15))</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="11" t="str">
@@ -32906,9 +32954,12 @@
         <f>IF(D16="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D16,'Loot History'!$A:$A,0)),""))</f>
         <v>DRUID</v>
       </c>
-      <c r="X16" s="11" t="str">
+      <c r="W16" t="str">
+        <v>Raid Bosses (T5/T6) / Vendor</v>
+      </c>
+      <c r="X16" s="11">
         <f>IF(W16="","",COUNTIF('Loot History'!$K:$K,W16))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="11" t="str">
@@ -32956,9 +33007,12 @@
         <f>IF(D17="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D17,'Loot History'!$A:$A,0)),""))</f>
         <v>SHAMAN</v>
       </c>
-      <c r="X17" s="11" t="str">
+      <c r="W17" t="str">
+        <v>Trash Mobs (Serpentshrine Cavern)</v>
+      </c>
+      <c r="X17" s="11">
         <f>IF(W17="","",COUNTIF('Loot History'!$K:$K,W17))</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="11" t="str">
@@ -33006,9 +33060,12 @@
         <f>IF(D18="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D18,'Loot History'!$A:$A,0)),""))</f>
         <v>PRIEST</v>
       </c>
-      <c r="X18" s="11" t="str">
+      <c r="W18" t="str">
+        <v>Trash Mobs (SSC / TK)</v>
+      </c>
+      <c r="X18" s="11">
         <f>IF(W18="","",COUNTIF('Loot History'!$K:$K,W18))</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="11" t="str">
@@ -33056,9 +33113,12 @@
         <f>IF(D19="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D19,'Loot History'!$A:$A,0)),""))</f>
         <v>WARRIOR</v>
       </c>
-      <c r="X19" s="11" t="str">
+      <c r="W19" t="str">
+        <v>Trash Mobs (Tempest Keep)</v>
+      </c>
+      <c r="X19" s="11">
         <f>IF(W19="","",COUNTIF('Loot History'!$K:$K,W19))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="11" t="str">
@@ -33106,9 +33166,12 @@
         <f>IF(D20="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D20,'Loot History'!$A:$A,0)),""))</f>
         <v>WARLOCK</v>
       </c>
-      <c r="X20" s="11" t="str">
+      <c r="W20" t="str">
+        <v>Void Reaver</v>
+      </c>
+      <c r="X20" s="11">
         <f>IF(W20="","",COUNTIF('Loot History'!$K:$K,W20))</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="11" t="str">

--- a/RC_Lootcouncil.xlsx
+++ b/RC_Lootcouncil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537786AA-9D76-41D2-A481-DE1EE55EFF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D10FE4E-E3AE-48E4-B53E-9B0C7E5EF18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loot History" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="927">
   <si>
     <t>player</t>
   </si>
@@ -2869,25 +2869,28 @@
     <t>Garona's Signet Ring</t>
   </si>
   <si>
-    <t>Trash Mobs (Serpentshrine Cavern)</t>
-  </si>
-  <si>
-    <t>Raid Bosses (T5/T6) / Vendor</t>
-  </si>
-  <si>
-    <t>Trash Mobs (SSC / TK)</t>
-  </si>
-  <si>
-    <t>Trash Mobs (Tempest Keep)</t>
-  </si>
-  <si>
-    <t>Gruul the Dragonkiller</t>
-  </si>
-  <si>
-    <t>High King Maulgar</t>
-  </si>
-  <si>
-    <t>Fathom-Lord Karathress / Morogrim</t>
+    <t>SSC / TK Trash</t>
+  </si>
+  <si>
+    <t>SSC Trash</t>
+  </si>
+  <si>
+    <t>TK Trash</t>
+  </si>
+  <si>
+    <t>Gruul the Dragonkiller (Gruul's Lair)</t>
+  </si>
+  <si>
+    <t>High King Maulgar (Gruul's Lair)</t>
+  </si>
+  <si>
+    <t>Magtheridon (Magtheridon's Lair)</t>
+  </si>
+  <si>
+    <t>Magtheridon (quest item)</t>
+  </si>
+  <si>
+    <t>Lady Vashj — name unverified</t>
   </si>
 </sst>
 </file>
@@ -4178,7 +4181,7 @@
             <c:strRef>
               <c:f>[0]!chartBossNames</c:f>
               <c:strCache>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
                   <c:v>Al'ar</c:v>
                 </c:pt>
@@ -4186,48 +4189,51 @@
                   <c:v>Fathom-Lord Karathress</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Fathom-Lord Karathress / Morogrim</c:v>
+                  <c:v>Gruul the Dragonkiller (Gruul's Lair)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Gruul the Dragonkiller</c:v>
+                  <c:v>High Astromancer Solarian</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>High Astromancer Solarian</c:v>
+                  <c:v>High King Maulgar (Gruul's Lair)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>High King Maulgar</c:v>
+                  <c:v>Hydross the Unstable</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>Hydross the Unstable</c:v>
+                  <c:v>Kael'thas Sunstrider</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>Kael'thas Sunstrider</c:v>
+                  <c:v>Lady Vashj</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>Lady Vashj</c:v>
+                  <c:v>Lady Vashj — name unverified</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Leotheras the Blind</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Magtheridon</c:v>
+                  <c:v>Magtheridon (Magtheridon's Lair)</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Magtheridon (quest item)</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Morogrim Tidewalker</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>Raid Bosses (T5/T6) / Vendor</c:v>
-                </c:pt>
                 <c:pt idx="13">
-                  <c:v>Trash Mobs (Serpentshrine Cavern)</c:v>
+                  <c:v>SSC / TK Trash</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Trash Mobs (SSC / TK)</c:v>
+                  <c:v>SSC Trash</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Trash Mobs (Tempest Keep)</c:v>
+                  <c:v>The Lurker Below</c:v>
                 </c:pt>
                 <c:pt idx="16">
+                  <c:v>TK Trash</c:v>
+                </c:pt>
+                <c:pt idx="17">
                   <c:v>Void Reaver</c:v>
                 </c:pt>
               </c:strCache>
@@ -4238,57 +4244,60 @@
               <c:f>[0]!chartBossCounts</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="17"/>
+                <c:ptCount val="18"/>
                 <c:pt idx="0">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>9</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>15</c:v>
+                <c:pt idx="4">
+                  <c:v>8</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="9">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>18</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>11</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>11</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>14</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>14</c:v>
+                <c:pt idx="17">
+                  <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7570,7 +7579,7 @@
     <col min="8" max="8" width="5.5" customWidth="1"/>
     <col min="9" max="9" width="9.5" customWidth="1"/>
     <col min="10" max="10" width="47.5" customWidth="1"/>
-    <col min="11" max="11" width="23.375" customWidth="1"/>
+    <col min="11" max="11" width="30" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="37.125" customWidth="1"/>
     <col min="13" max="13" width="35.625" customWidth="1"/>
     <col min="14" max="14" width="10.375" customWidth="1"/>
@@ -7737,7 +7746,7 @@
         <v>265</v>
       </c>
       <c r="K3" t="s">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="L3" t="s">
         <v>786</v>
@@ -7857,7 +7866,7 @@
         <v>265</v>
       </c>
       <c r="K5" t="s">
-        <v>919</v>
+        <v>452</v>
       </c>
       <c r="L5" t="s">
         <v>787</v>
@@ -7920,7 +7929,7 @@
         <v>265</v>
       </c>
       <c r="K6" t="s">
-        <v>919</v>
+        <v>279</v>
       </c>
       <c r="L6" t="s">
         <v>788</v>
@@ -7980,7 +7989,7 @@
         <v>265</v>
       </c>
       <c r="K7" t="s">
-        <v>678</v>
+        <v>452</v>
       </c>
       <c r="L7" t="s">
         <v>789</v>
@@ -8103,7 +8112,7 @@
         <v>265</v>
       </c>
       <c r="K9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="N9">
         <v>1</v>
@@ -8157,7 +8166,7 @@
         <v>265</v>
       </c>
       <c r="K10" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L10" t="s">
         <v>791</v>
@@ -8217,7 +8226,7 @@
         <v>265</v>
       </c>
       <c r="K11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N11" t="s">
         <v>64</v>
@@ -8271,7 +8280,7 @@
         <v>265</v>
       </c>
       <c r="K12" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="L12" t="s">
         <v>792</v>
@@ -8445,7 +8454,7 @@
         <v>265</v>
       </c>
       <c r="K15" t="s">
-        <v>266</v>
+        <v>920</v>
       </c>
       <c r="L15" t="s">
         <v>795</v>
@@ -8505,7 +8514,7 @@
         <v>265</v>
       </c>
       <c r="K16" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="L16" t="s">
         <v>796</v>
@@ -8862,7 +8871,7 @@
         <v>265</v>
       </c>
       <c r="K22" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L22" t="s">
         <v>802</v>
@@ -8922,7 +8931,7 @@
         <v>265</v>
       </c>
       <c r="K23" t="s">
-        <v>678</v>
+        <v>920</v>
       </c>
       <c r="N23">
         <v>4</v>
@@ -9219,7 +9228,7 @@
         <v>101</v>
       </c>
       <c r="K28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L28" t="s">
         <v>806</v>
@@ -9342,7 +9351,7 @@
         <v>101</v>
       </c>
       <c r="K30" t="s">
-        <v>922</v>
+        <v>677</v>
       </c>
       <c r="L30" t="s">
         <v>807</v>
@@ -9579,7 +9588,7 @@
         <v>101</v>
       </c>
       <c r="K34" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L34" t="s">
         <v>811</v>
@@ -9765,7 +9774,7 @@
         <v>101</v>
       </c>
       <c r="K37" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N37">
         <v>2</v>
@@ -9876,7 +9885,7 @@
         <v>101</v>
       </c>
       <c r="K39" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L39" t="s">
         <v>815</v>
@@ -9993,7 +10002,7 @@
         <v>101</v>
       </c>
       <c r="K41" t="s">
-        <v>922</v>
+        <v>678</v>
       </c>
       <c r="L41" t="s">
         <v>817</v>
@@ -10464,7 +10473,7 @@
         <v>265</v>
       </c>
       <c r="K49" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L49" t="s">
         <v>823</v>
@@ -10524,7 +10533,7 @@
         <v>265</v>
       </c>
       <c r="K50" t="s">
-        <v>919</v>
+        <v>452</v>
       </c>
       <c r="L50" t="s">
         <v>824</v>
@@ -10707,7 +10716,7 @@
         <v>265</v>
       </c>
       <c r="K53" t="s">
-        <v>678</v>
+        <v>266</v>
       </c>
       <c r="L53" t="s">
         <v>826</v>
@@ -10824,7 +10833,7 @@
         <v>265</v>
       </c>
       <c r="K55" t="s">
-        <v>53</v>
+        <v>452</v>
       </c>
       <c r="L55" t="s">
         <v>827</v>
@@ -11007,7 +11016,7 @@
         <v>101</v>
       </c>
       <c r="K58" t="s">
-        <v>919</v>
+        <v>677</v>
       </c>
       <c r="L58" t="s">
         <v>830</v>
@@ -11655,7 +11664,7 @@
         <v>101</v>
       </c>
       <c r="K69" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L69" t="s">
         <v>840</v>
@@ -11715,7 +11724,7 @@
         <v>101</v>
       </c>
       <c r="K70" t="s">
-        <v>922</v>
+        <v>212</v>
       </c>
       <c r="L70" t="s">
         <v>804</v>
@@ -11832,7 +11841,7 @@
         <v>101</v>
       </c>
       <c r="K72" t="s">
-        <v>922</v>
+        <v>678</v>
       </c>
       <c r="L72" t="s">
         <v>841</v>
@@ -11895,7 +11904,7 @@
         <v>101</v>
       </c>
       <c r="K73" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="L73" t="s">
         <v>815</v>
@@ -12012,7 +12021,7 @@
         <v>265</v>
       </c>
       <c r="K75" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L75" t="s">
         <v>842</v>
@@ -12072,7 +12081,7 @@
         <v>675</v>
       </c>
       <c r="K76" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L76" t="s">
         <v>843</v>
@@ -12189,7 +12198,7 @@
         <v>675</v>
       </c>
       <c r="K78" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L78" t="s">
         <v>845</v>
@@ -12246,7 +12255,7 @@
         <v>675</v>
       </c>
       <c r="K79" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L79" t="s">
         <v>846</v>
@@ -12303,7 +12312,7 @@
         <v>676</v>
       </c>
       <c r="K80" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L80" t="s">
         <v>846</v>
@@ -12474,7 +12483,7 @@
         <v>265</v>
       </c>
       <c r="K83" t="s">
-        <v>53</v>
+        <v>452</v>
       </c>
       <c r="L83" t="s">
         <v>848</v>
@@ -12597,7 +12606,7 @@
         <v>676</v>
       </c>
       <c r="K85" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L85" t="s">
         <v>849</v>
@@ -12654,7 +12663,7 @@
         <v>676</v>
       </c>
       <c r="K86" t="s">
-        <v>177</v>
+        <v>925</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -12708,7 +12717,7 @@
         <v>265</v>
       </c>
       <c r="K87" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="L87" t="s">
         <v>850</v>
@@ -12768,7 +12777,7 @@
         <v>676</v>
       </c>
       <c r="K88" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L88" t="s">
         <v>851</v>
@@ -12825,7 +12834,7 @@
         <v>675</v>
       </c>
       <c r="K89" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L89" t="s">
         <v>852</v>
@@ -12885,7 +12894,7 @@
         <v>675</v>
       </c>
       <c r="K90" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L90" t="s">
         <v>853</v>
@@ -12942,7 +12951,7 @@
         <v>676</v>
       </c>
       <c r="K91" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L91" t="s">
         <v>854</v>
@@ -13005,7 +13014,7 @@
         <v>265</v>
       </c>
       <c r="K92" t="s">
-        <v>919</v>
+        <v>266</v>
       </c>
       <c r="L92" t="s">
         <v>804</v>
@@ -13068,7 +13077,7 @@
         <v>265</v>
       </c>
       <c r="K93" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L93" t="s">
         <v>855</v>
@@ -13128,7 +13137,7 @@
         <v>265</v>
       </c>
       <c r="K94" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L94" t="s">
         <v>855</v>
@@ -13245,7 +13254,7 @@
         <v>676</v>
       </c>
       <c r="K96" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L96" t="s">
         <v>857</v>
@@ -13482,7 +13491,7 @@
         <v>675</v>
       </c>
       <c r="K100" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L100" t="s">
         <v>860</v>
@@ -13545,7 +13554,7 @@
         <v>265</v>
       </c>
       <c r="K101" t="s">
-        <v>919</v>
+        <v>452</v>
       </c>
       <c r="N101">
         <v>3</v>
@@ -13659,7 +13668,7 @@
         <v>265</v>
       </c>
       <c r="K103" t="s">
-        <v>266</v>
+        <v>920</v>
       </c>
       <c r="L103" t="s">
         <v>724</v>
@@ -13719,7 +13728,7 @@
         <v>675</v>
       </c>
       <c r="K104" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L104" t="s">
         <v>724</v>
@@ -13776,7 +13785,7 @@
         <v>675</v>
       </c>
       <c r="K105" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L105" t="s">
         <v>862</v>
@@ -13947,7 +13956,7 @@
         <v>265</v>
       </c>
       <c r="K108" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L108" t="s">
         <v>802</v>
@@ -14007,7 +14016,7 @@
         <v>676</v>
       </c>
       <c r="K109" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L109" t="s">
         <v>786</v>
@@ -14064,7 +14073,7 @@
         <v>265</v>
       </c>
       <c r="K110" t="s">
-        <v>102</v>
+        <v>266</v>
       </c>
       <c r="L110" t="s">
         <v>863</v>
@@ -14124,7 +14133,7 @@
         <v>675</v>
       </c>
       <c r="K111" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L111" t="s">
         <v>864</v>
@@ -14181,7 +14190,7 @@
         <v>265</v>
       </c>
       <c r="K112" t="s">
-        <v>925</v>
+        <v>452</v>
       </c>
       <c r="L112" t="s">
         <v>812</v>
@@ -14298,7 +14307,7 @@
         <v>676</v>
       </c>
       <c r="K114" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L114" t="s">
         <v>866</v>
@@ -14418,7 +14427,7 @@
         <v>101</v>
       </c>
       <c r="K116" t="s">
-        <v>919</v>
+        <v>677</v>
       </c>
       <c r="L116" t="s">
         <v>867</v>
@@ -14538,7 +14547,7 @@
         <v>101</v>
       </c>
       <c r="K118" t="s">
-        <v>922</v>
+        <v>212</v>
       </c>
       <c r="L118" t="s">
         <v>789</v>
@@ -15129,7 +15138,7 @@
         <v>265</v>
       </c>
       <c r="K128" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N128">
         <v>4</v>
@@ -15183,7 +15192,7 @@
         <v>265</v>
       </c>
       <c r="K129" t="s">
-        <v>539</v>
+        <v>279</v>
       </c>
       <c r="L129" t="s">
         <v>871</v>
@@ -15243,7 +15252,7 @@
         <v>265</v>
       </c>
       <c r="K130" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L130" t="s">
         <v>872</v>
@@ -15303,7 +15312,7 @@
         <v>265</v>
       </c>
       <c r="K131" t="s">
-        <v>919</v>
+        <v>452</v>
       </c>
       <c r="N131">
         <v>4</v>
@@ -15360,7 +15369,7 @@
         <v>265</v>
       </c>
       <c r="K132" t="s">
-        <v>919</v>
+        <v>452</v>
       </c>
       <c r="L132" t="s">
         <v>873</v>
@@ -15420,7 +15429,7 @@
         <v>265</v>
       </c>
       <c r="K133" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N133">
         <v>1</v>
@@ -15474,7 +15483,7 @@
         <v>265</v>
       </c>
       <c r="K134" t="s">
-        <v>678</v>
+        <v>452</v>
       </c>
       <c r="L134" t="s">
         <v>874</v>
@@ -15594,7 +15603,7 @@
         <v>265</v>
       </c>
       <c r="K136" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="L136" t="s">
         <v>876</v>
@@ -15768,7 +15777,7 @@
         <v>265</v>
       </c>
       <c r="K139" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L139" t="s">
         <v>791</v>
@@ -15828,7 +15837,7 @@
         <v>265</v>
       </c>
       <c r="K140" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N140">
         <v>4</v>
@@ -15882,7 +15891,7 @@
         <v>265</v>
       </c>
       <c r="K141" t="s">
-        <v>919</v>
+        <v>266</v>
       </c>
       <c r="L141" t="s">
         <v>818</v>
@@ -16002,7 +16011,7 @@
         <v>265</v>
       </c>
       <c r="K143" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L143" t="s">
         <v>842</v>
@@ -16119,7 +16128,7 @@
         <v>265</v>
       </c>
       <c r="K145" t="s">
-        <v>919</v>
+        <v>53</v>
       </c>
       <c r="L145" t="s">
         <v>879</v>
@@ -16179,7 +16188,7 @@
         <v>265</v>
       </c>
       <c r="K146" t="s">
-        <v>919</v>
+        <v>335</v>
       </c>
       <c r="L146" t="s">
         <v>880</v>
@@ -16299,7 +16308,7 @@
         <v>265</v>
       </c>
       <c r="K148" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="N148">
         <v>1</v>
@@ -16413,7 +16422,7 @@
         <v>265</v>
       </c>
       <c r="K150" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="L150" t="s">
         <v>882</v>
@@ -16473,7 +16482,7 @@
         <v>265</v>
       </c>
       <c r="K151" t="s">
-        <v>335</v>
+        <v>266</v>
       </c>
       <c r="L151" t="s">
         <v>883</v>
@@ -16656,7 +16665,7 @@
         <v>675</v>
       </c>
       <c r="K154" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L154" t="s">
         <v>886</v>
@@ -16713,7 +16722,7 @@
         <v>676</v>
       </c>
       <c r="K155" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L155" t="s">
         <v>887</v>
@@ -16881,7 +16890,7 @@
         <v>675</v>
       </c>
       <c r="K158" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="L158" t="s">
         <v>854</v>
@@ -16944,7 +16953,7 @@
         <v>675</v>
       </c>
       <c r="K159" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L159" t="s">
         <v>889</v>
@@ -17127,7 +17136,7 @@
         <v>101</v>
       </c>
       <c r="K162" t="s">
-        <v>922</v>
+        <v>212</v>
       </c>
       <c r="L162" t="s">
         <v>737</v>
@@ -17187,7 +17196,7 @@
         <v>675</v>
       </c>
       <c r="K163" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L163" t="s">
         <v>892</v>
@@ -17250,7 +17259,7 @@
         <v>675</v>
       </c>
       <c r="K164" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L164" t="s">
         <v>795</v>
@@ -17367,7 +17376,7 @@
         <v>675</v>
       </c>
       <c r="K166" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="L166" t="s">
         <v>814</v>
@@ -17424,7 +17433,7 @@
         <v>675</v>
       </c>
       <c r="K167" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L167" t="s">
         <v>803</v>
@@ -17481,7 +17490,7 @@
         <v>675</v>
       </c>
       <c r="K168" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="L168" t="s">
         <v>803</v>
@@ -17778,7 +17787,7 @@
         <v>675</v>
       </c>
       <c r="K173" t="s">
-        <v>678</v>
+        <v>923</v>
       </c>
       <c r="L173" t="s">
         <v>896</v>
@@ -17841,7 +17850,7 @@
         <v>101</v>
       </c>
       <c r="K174" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L174" t="s">
         <v>897</v>
@@ -17901,7 +17910,7 @@
         <v>676</v>
       </c>
       <c r="K175" t="s">
-        <v>177</v>
+        <v>925</v>
       </c>
       <c r="N175">
         <v>1</v>
@@ -17955,7 +17964,7 @@
         <v>676</v>
       </c>
       <c r="K176" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L176" t="s">
         <v>887</v>
@@ -18012,7 +18021,7 @@
         <v>676</v>
       </c>
       <c r="K177" t="s">
-        <v>177</v>
+        <v>924</v>
       </c>
       <c r="L177" t="s">
         <v>887</v>
@@ -18126,7 +18135,7 @@
         <v>101</v>
       </c>
       <c r="K179" t="s">
-        <v>922</v>
+        <v>102</v>
       </c>
       <c r="L179" t="s">
         <v>884</v>
@@ -32273,12 +32282,12 @@
         <v>MAGE</v>
       </c>
       <c r="W4" t="str" cm="1">
-        <f t="array" ref="W4:W20">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
+        <f t="array" ref="W4:W21">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
         <v>Al'ar</v>
       </c>
       <c r="X4" s="11">
         <f>IF(W4="","",COUNTIF('Loot History'!$K:$K,W4))</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z4" s="4" cm="1">
         <f t="array" ref="Z4:Z11">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!B2:B1000,'Loot History'!B2:B1000&lt;&gt;""))),"")</f>
@@ -32341,7 +32350,7 @@
       </c>
       <c r="X5" s="11">
         <f>IF(W5="","",COUNTIF('Loot History'!$K:$K,W5))</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z5" s="4">
         <v>46161</v>
@@ -32399,11 +32408,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W6" t="str">
-        <v>Fathom-Lord Karathress / Morogrim</v>
+        <v>Gruul the Dragonkiller (Gruul's Lair)</v>
       </c>
       <c r="X6" s="11">
         <f>IF(W6="","",COUNTIF('Loot History'!$K:$K,W6))</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Z6" s="4">
         <v>46163</v>
@@ -32461,11 +32470,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W7" t="str">
-        <v>Gruul the Dragonkiller</v>
+        <v>High Astromancer Solarian</v>
       </c>
       <c r="X7" s="11">
         <f>IF(W7="","",COUNTIF('Loot History'!$K:$K,W7))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z7" s="4">
         <v>46167</v>
@@ -32485,7 +32494,7 @@
       </c>
       <c r="B8" s="7" cm="1">
         <f t="array" ref="B8">SUMPRODUCT(('Loot History'!K2:K1000&lt;&gt;"")/COUNTIF('Loot History'!K2:K1000,'Loot History'!K2:K1000&amp;""))</f>
-        <v>16.999999999999989</v>
+        <v>17.999999999999989</v>
       </c>
       <c r="D8" t="str">
         <v>Fetzine-Thunderstrike</v>
@@ -32523,11 +32532,11 @@
         <v>HUNTER</v>
       </c>
       <c r="W8" t="str">
-        <v>High Astromancer Solarian</v>
+        <v>High King Maulgar (Gruul's Lair)</v>
       </c>
       <c r="X8" s="11">
         <f>IF(W8="","",COUNTIF('Loot History'!$K:$K,W8))</f>
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="4">
         <v>46170</v>
@@ -32578,11 +32587,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W9" t="str">
-        <v>High King Maulgar</v>
+        <v>Hydross the Unstable</v>
       </c>
       <c r="X9" s="11">
         <f>IF(W9="","",COUNTIF('Loot History'!$K:$K,W9))</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z9" s="4">
         <v>46174</v>
@@ -32633,11 +32642,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W10" t="str">
-        <v>Hydross the Unstable</v>
+        <v>Kael'thas Sunstrider</v>
       </c>
       <c r="X10" s="11">
         <f>IF(W10="","",COUNTIF('Loot History'!$K:$K,W10))</f>
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Z10" s="4">
         <v>46177</v>
@@ -32688,11 +32697,11 @@
         <v>SHAMAN</v>
       </c>
       <c r="W11" t="str">
-        <v>Kael'thas Sunstrider</v>
+        <v>Lady Vashj</v>
       </c>
       <c r="X11" s="11">
         <f>IF(W11="","",COUNTIF('Loot History'!$K:$K,W11))</f>
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Z11" s="4">
         <v>46181</v>
@@ -32743,11 +32752,11 @@
         <v>DRUID</v>
       </c>
       <c r="W12" t="str">
-        <v>Lady Vashj</v>
+        <v>Lady Vashj — name unverified</v>
       </c>
       <c r="X12" s="11">
         <f>IF(W12="","",COUNTIF('Loot History'!$K:$K,W12))</f>
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="4"/>
       <c r="AA12" s="11" t="str">
@@ -32800,7 +32809,7 @@
       </c>
       <c r="X13" s="11">
         <f>IF(W13="","",COUNTIF('Loot History'!$K:$K,W13))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z13" s="4"/>
       <c r="AA13" s="11" t="str">
@@ -32849,11 +32858,11 @@
         <v>DRUID</v>
       </c>
       <c r="W14" t="str">
-        <v>Magtheridon</v>
+        <v>Magtheridon (Magtheridon's Lair)</v>
       </c>
       <c r="X14" s="11">
         <f>IF(W14="","",COUNTIF('Loot History'!$K:$K,W14))</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="11" t="str">
@@ -32902,11 +32911,11 @@
         <v>HUNTER</v>
       </c>
       <c r="W15" t="str">
-        <v>Morogrim Tidewalker</v>
+        <v>Magtheridon (quest item)</v>
       </c>
       <c r="X15" s="11">
         <f>IF(W15="","",COUNTIF('Loot History'!$K:$K,W15))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="11" t="str">
@@ -32955,11 +32964,11 @@
         <v>DRUID</v>
       </c>
       <c r="W16" t="str">
-        <v>Raid Bosses (T5/T6) / Vendor</v>
+        <v>Morogrim Tidewalker</v>
       </c>
       <c r="X16" s="11">
         <f>IF(W16="","",COUNTIF('Loot History'!$K:$K,W16))</f>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="11" t="str">
@@ -33008,11 +33017,11 @@
         <v>SHAMAN</v>
       </c>
       <c r="W17" t="str">
-        <v>Trash Mobs (Serpentshrine Cavern)</v>
+        <v>SSC / TK Trash</v>
       </c>
       <c r="X17" s="11">
         <f>IF(W17="","",COUNTIF('Loot History'!$K:$K,W17))</f>
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="11" t="str">
@@ -33061,11 +33070,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W18" t="str">
-        <v>Trash Mobs (SSC / TK)</v>
+        <v>SSC Trash</v>
       </c>
       <c r="X18" s="11">
         <f>IF(W18="","",COUNTIF('Loot History'!$K:$K,W18))</f>
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="11" t="str">
@@ -33114,11 +33123,11 @@
         <v>WARRIOR</v>
       </c>
       <c r="W19" t="str">
-        <v>Trash Mobs (Tempest Keep)</v>
+        <v>The Lurker Below</v>
       </c>
       <c r="X19" s="11">
         <f>IF(W19="","",COUNTIF('Loot History'!$K:$K,W19))</f>
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="11" t="str">
@@ -33167,11 +33176,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W20" t="str">
-        <v>Void Reaver</v>
+        <v>TK Trash</v>
       </c>
       <c r="X20" s="11">
         <f>IF(W20="","",COUNTIF('Loot History'!$K:$K,W20))</f>
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="11" t="str">
@@ -33219,9 +33228,12 @@
         <f>IF(D21="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D21,'Loot History'!$A:$A,0)),""))</f>
         <v>SHAMAN</v>
       </c>
-      <c r="X21" s="11" t="str">
+      <c r="W21" t="str">
+        <v>Void Reaver</v>
+      </c>
+      <c r="X21" s="11">
         <f>IF(W21="","",COUNTIF('Loot History'!$K:$K,W21))</f>
-        <v/>
+        <v>16</v>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="11" t="str">

--- a/RC_Lootcouncil.xlsx
+++ b/RC_Lootcouncil.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D10FE4E-E3AE-48E4-B53E-9B0C7E5EF18D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774A7999-B440-4FE2-B51D-274B2F2DA87E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
+    <workbookView xWindow="4635" yWindow="4635" windowWidth="38700" windowHeight="15345" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loot History" sheetId="1" r:id="rId1"/>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4881" uniqueCount="925">
   <si>
     <t>player</t>
   </si>
@@ -2878,19 +2878,13 @@
     <t>TK Trash</t>
   </si>
   <si>
-    <t>Gruul the Dragonkiller (Gruul's Lair)</t>
-  </si>
-  <si>
-    <t>High King Maulgar (Gruul's Lair)</t>
-  </si>
-  <si>
-    <t>Magtheridon (Magtheridon's Lair)</t>
-  </si>
-  <si>
-    <t>Magtheridon (quest item)</t>
-  </si>
-  <si>
     <t>Lady Vashj — name unverified</t>
+  </si>
+  <si>
+    <t>Gruul the Dragonkiller</t>
+  </si>
+  <si>
+    <t>High King Maulgar</t>
   </si>
 </sst>
 </file>
@@ -4181,7 +4175,7 @@
             <c:strRef>
               <c:f>[0]!chartBossNames</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>Al'ar</c:v>
                 </c:pt>
@@ -4189,13 +4183,13 @@
                   <c:v>Fathom-Lord Karathress</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Gruul the Dragonkiller (Gruul's Lair)</c:v>
+                  <c:v>Gruul the Dragonkiller</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>High Astromancer Solarian</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>High King Maulgar (Gruul's Lair)</c:v>
+                  <c:v>High King Maulgar</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>Hydross the Unstable</c:v>
@@ -4213,27 +4207,24 @@
                   <c:v>Leotheras the Blind</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>Magtheridon (Magtheridon's Lair)</c:v>
+                  <c:v>Magtheridon</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>Magtheridon (quest item)</c:v>
+                  <c:v>Morogrim Tidewalker</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>Morogrim Tidewalker</c:v>
+                  <c:v>SSC / TK Trash</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>SSC / TK Trash</c:v>
+                  <c:v>SSC Trash</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>SSC Trash</c:v>
+                  <c:v>The Lurker Below</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>The Lurker Below</c:v>
+                  <c:v>TK Trash</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>TK Trash</c:v>
-                </c:pt>
-                <c:pt idx="17">
                   <c:v>Void Reaver</c:v>
                 </c:pt>
               </c:strCache>
@@ -4244,7 +4235,7 @@
               <c:f>[0]!chartBossCounts</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>12</c:v>
                 </c:pt>
@@ -4276,27 +4267,24 @@
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>9</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>17</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>10</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="17">
                   <c:v>16</c:v>
                 </c:pt>
               </c:numCache>
@@ -12081,7 +12069,7 @@
         <v>675</v>
       </c>
       <c r="K76" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L76" t="s">
         <v>843</v>
@@ -12198,7 +12186,7 @@
         <v>675</v>
       </c>
       <c r="K78" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L78" t="s">
         <v>845</v>
@@ -12255,7 +12243,7 @@
         <v>675</v>
       </c>
       <c r="K79" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L79" t="s">
         <v>846</v>
@@ -12312,7 +12300,7 @@
         <v>676</v>
       </c>
       <c r="K80" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L80" t="s">
         <v>846</v>
@@ -12606,7 +12594,7 @@
         <v>676</v>
       </c>
       <c r="K85" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L85" t="s">
         <v>849</v>
@@ -12663,7 +12651,7 @@
         <v>676</v>
       </c>
       <c r="K86" t="s">
-        <v>925</v>
+        <v>177</v>
       </c>
       <c r="N86">
         <v>1</v>
@@ -12717,7 +12705,7 @@
         <v>265</v>
       </c>
       <c r="K87" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="L87" t="s">
         <v>850</v>
@@ -12777,7 +12765,7 @@
         <v>676</v>
       </c>
       <c r="K88" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L88" t="s">
         <v>851</v>
@@ -12834,7 +12822,7 @@
         <v>675</v>
       </c>
       <c r="K89" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L89" t="s">
         <v>852</v>
@@ -12894,7 +12882,7 @@
         <v>675</v>
       </c>
       <c r="K90" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L90" t="s">
         <v>853</v>
@@ -12951,7 +12939,7 @@
         <v>676</v>
       </c>
       <c r="K91" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L91" t="s">
         <v>854</v>
@@ -13254,7 +13242,7 @@
         <v>676</v>
       </c>
       <c r="K96" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L96" t="s">
         <v>857</v>
@@ -13491,7 +13479,7 @@
         <v>675</v>
       </c>
       <c r="K100" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L100" t="s">
         <v>860</v>
@@ -13728,7 +13716,7 @@
         <v>675</v>
       </c>
       <c r="K104" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L104" t="s">
         <v>724</v>
@@ -13785,7 +13773,7 @@
         <v>675</v>
       </c>
       <c r="K105" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L105" t="s">
         <v>862</v>
@@ -14016,7 +14004,7 @@
         <v>676</v>
       </c>
       <c r="K109" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L109" t="s">
         <v>786</v>
@@ -14133,7 +14121,7 @@
         <v>675</v>
       </c>
       <c r="K111" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L111" t="s">
         <v>864</v>
@@ -14307,7 +14295,7 @@
         <v>676</v>
       </c>
       <c r="K114" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L114" t="s">
         <v>866</v>
@@ -16665,7 +16653,7 @@
         <v>675</v>
       </c>
       <c r="K154" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L154" t="s">
         <v>886</v>
@@ -16722,7 +16710,7 @@
         <v>676</v>
       </c>
       <c r="K155" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L155" t="s">
         <v>887</v>
@@ -16890,7 +16878,7 @@
         <v>675</v>
       </c>
       <c r="K158" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L158" t="s">
         <v>854</v>
@@ -16953,7 +16941,7 @@
         <v>675</v>
       </c>
       <c r="K159" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L159" t="s">
         <v>889</v>
@@ -17196,7 +17184,7 @@
         <v>675</v>
       </c>
       <c r="K163" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L163" t="s">
         <v>892</v>
@@ -17259,7 +17247,7 @@
         <v>675</v>
       </c>
       <c r="K164" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L164" t="s">
         <v>795</v>
@@ -17376,7 +17364,7 @@
         <v>675</v>
       </c>
       <c r="K166" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L166" t="s">
         <v>814</v>
@@ -17433,7 +17421,7 @@
         <v>675</v>
       </c>
       <c r="K167" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L167" t="s">
         <v>803</v>
@@ -17490,7 +17478,7 @@
         <v>675</v>
       </c>
       <c r="K168" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="L168" t="s">
         <v>803</v>
@@ -17787,7 +17775,7 @@
         <v>675</v>
       </c>
       <c r="K173" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="L173" t="s">
         <v>896</v>
@@ -17910,7 +17898,7 @@
         <v>676</v>
       </c>
       <c r="K175" t="s">
-        <v>925</v>
+        <v>177</v>
       </c>
       <c r="N175">
         <v>1</v>
@@ -17964,7 +17952,7 @@
         <v>676</v>
       </c>
       <c r="K176" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L176" t="s">
         <v>887</v>
@@ -18021,7 +18009,7 @@
         <v>676</v>
       </c>
       <c r="K177" t="s">
-        <v>924</v>
+        <v>177</v>
       </c>
       <c r="L177" t="s">
         <v>887</v>
@@ -32282,7 +32270,7 @@
         <v>MAGE</v>
       </c>
       <c r="W4" t="str" cm="1">
-        <f t="array" ref="W4:W21">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
+        <f t="array" ref="W4:W20">IFERROR(_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!K2:K1000,'Loot History'!K2:K1000&lt;&gt;""))),"")</f>
         <v>Al'ar</v>
       </c>
       <c r="X4" s="11">
@@ -32408,7 +32396,7 @@
         <v>PRIEST</v>
       </c>
       <c r="W6" t="str">
-        <v>Gruul the Dragonkiller (Gruul's Lair)</v>
+        <v>Gruul the Dragonkiller</v>
       </c>
       <c r="X6" s="11">
         <f>IF(W6="","",COUNTIF('Loot History'!$K:$K,W6))</f>
@@ -32494,7 +32482,7 @@
       </c>
       <c r="B8" s="7" cm="1">
         <f t="array" ref="B8">SUMPRODUCT(('Loot History'!K2:K1000&lt;&gt;"")/COUNTIF('Loot History'!K2:K1000,'Loot History'!K2:K1000&amp;""))</f>
-        <v>17.999999999999989</v>
+        <v>17</v>
       </c>
       <c r="D8" t="str">
         <v>Fetzine-Thunderstrike</v>
@@ -32532,7 +32520,7 @@
         <v>HUNTER</v>
       </c>
       <c r="W8" t="str">
-        <v>High King Maulgar (Gruul's Lair)</v>
+        <v>High King Maulgar</v>
       </c>
       <c r="X8" s="11">
         <f>IF(W8="","",COUNTIF('Loot History'!$K:$K,W8))</f>
@@ -32858,11 +32846,11 @@
         <v>DRUID</v>
       </c>
       <c r="W14" t="str">
-        <v>Magtheridon (Magtheridon's Lair)</v>
+        <v>Magtheridon</v>
       </c>
       <c r="X14" s="11">
         <f>IF(W14="","",COUNTIF('Loot History'!$K:$K,W14))</f>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z14" s="4"/>
       <c r="AA14" s="11" t="str">
@@ -32911,11 +32899,11 @@
         <v>HUNTER</v>
       </c>
       <c r="W15" t="str">
-        <v>Magtheridon (quest item)</v>
+        <v>Morogrim Tidewalker</v>
       </c>
       <c r="X15" s="11">
         <f>IF(W15="","",COUNTIF('Loot History'!$K:$K,W15))</f>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Z15" s="4"/>
       <c r="AA15" s="11" t="str">
@@ -32964,11 +32952,11 @@
         <v>DRUID</v>
       </c>
       <c r="W16" t="str">
-        <v>Morogrim Tidewalker</v>
+        <v>SSC / TK Trash</v>
       </c>
       <c r="X16" s="11">
         <f>IF(W16="","",COUNTIF('Loot History'!$K:$K,W16))</f>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Z16" s="4"/>
       <c r="AA16" s="11" t="str">
@@ -33017,11 +33005,11 @@
         <v>SHAMAN</v>
       </c>
       <c r="W17" t="str">
-        <v>SSC / TK Trash</v>
+        <v>SSC Trash</v>
       </c>
       <c r="X17" s="11">
         <f>IF(W17="","",COUNTIF('Loot History'!$K:$K,W17))</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="Z17" s="4"/>
       <c r="AA17" s="11" t="str">
@@ -33070,11 +33058,11 @@
         <v>PRIEST</v>
       </c>
       <c r="W18" t="str">
-        <v>SSC Trash</v>
+        <v>The Lurker Below</v>
       </c>
       <c r="X18" s="11">
         <f>IF(W18="","",COUNTIF('Loot History'!$K:$K,W18))</f>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Z18" s="4"/>
       <c r="AA18" s="11" t="str">
@@ -33123,11 +33111,11 @@
         <v>WARRIOR</v>
       </c>
       <c r="W19" t="str">
-        <v>The Lurker Below</v>
+        <v>TK Trash</v>
       </c>
       <c r="X19" s="11">
         <f>IF(W19="","",COUNTIF('Loot History'!$K:$K,W19))</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Z19" s="4"/>
       <c r="AA19" s="11" t="str">
@@ -33176,11 +33164,11 @@
         <v>WARLOCK</v>
       </c>
       <c r="W20" t="str">
-        <v>TK Trash</v>
+        <v>Void Reaver</v>
       </c>
       <c r="X20" s="11">
         <f>IF(W20="","",COUNTIF('Loot History'!$K:$K,W20))</f>
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="Z20" s="4"/>
       <c r="AA20" s="11" t="str">
@@ -33228,12 +33216,9 @@
         <f>IF(D21="","",IFERROR(INDEX('Loot History'!$I:$I,MATCH(D21,'Loot History'!$A:$A,0)),""))</f>
         <v>SHAMAN</v>
       </c>
-      <c r="W21" t="str">
-        <v>Void Reaver</v>
-      </c>
-      <c r="X21" s="11">
+      <c r="X21" s="11" t="str">
         <f>IF(W21="","",COUNTIF('Loot History'!$K:$K,W21))</f>
-        <v>16</v>
+        <v/>
       </c>
       <c r="Z21" s="4"/>
       <c r="AA21" s="11" t="str">

--- a/RC_Lootcouncil.xlsx
+++ b/RC_Lootcouncil.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cpf\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/152803c6536e24e3/Privat/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C058CDC-6D93-49C8-9F94-E7EA4ADCBE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="13_ncr:1_{3C058CDC-6D93-49C8-9F94-E7EA4ADCBE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1025472D-504F-B240-9B3B-CE3E6D520424}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
+    <workbookView xWindow="8480" yWindow="4140" windowWidth="51840" windowHeight="21120" xr2:uid="{8A8C0742-13A5-1542-BAF7-E1A001F7B0C0}"/>
   </bookViews>
   <sheets>
     <sheet name="Loot History" sheetId="1" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3583" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3590" uniqueCount="670">
   <si>
     <t>player</t>
   </si>
@@ -2112,6 +2112,12 @@
   </si>
   <si>
     <t>Timelapse Shard</t>
+  </si>
+  <si>
+    <t>Left Guild</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
@@ -2314,7 +2320,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2873,7 +2879,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3282,7 +3288,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3722,7 +3728,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6805,33 +6811,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19451AA2-23CF-6249-8587-EF34CF3BDA66}">
-  <dimension ref="A1:U279"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V279"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="35.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="26" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="42.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="50" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6895,8 +6901,11 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="3" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -6956,7 +6965,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -7019,7 +7028,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -7082,7 +7091,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -7145,7 +7154,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -7208,7 +7217,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -7271,7 +7280,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -7334,7 +7343,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -7391,7 +7400,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>53</v>
       </c>
@@ -7454,7 +7463,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -7511,7 +7520,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -7574,7 +7583,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -7634,7 +7643,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -7694,7 +7703,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -7757,7 +7766,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -7820,7 +7829,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>77</v>
       </c>
@@ -7880,7 +7889,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>78</v>
       </c>
@@ -7945,8 +7954,11 @@
         <f t="shared" si="0"/>
         <v>46160</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -8006,7 +8018,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>81</v>
       </c>
@@ -8066,7 +8078,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>81</v>
       </c>
@@ -8126,7 +8138,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -8189,7 +8201,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>87</v>
       </c>
@@ -8249,7 +8261,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>87</v>
       </c>
@@ -8309,7 +8321,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>91</v>
       </c>
@@ -8372,7 +8384,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>93</v>
       </c>
@@ -8435,7 +8447,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>95</v>
       </c>
@@ -8495,7 +8507,7 @@
         <v>46160</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>96</v>
       </c>
@@ -8560,8 +8572,11 @@
         <f t="shared" si="0"/>
         <v>46161</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>102</v>
       </c>
@@ -8624,7 +8639,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>53</v>
       </c>
@@ -8687,7 +8702,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>53</v>
       </c>
@@ -8747,7 +8762,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -8810,7 +8825,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -8873,7 +8888,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -8936,7 +8951,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>84</v>
       </c>
@@ -8999,7 +9014,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>84</v>
       </c>
@@ -9062,7 +9077,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -9119,7 +9134,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -9179,7 +9194,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -9241,8 +9256,11 @@
         <f t="shared" si="1"/>
         <v>46161</v>
       </c>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V39" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -9301,8 +9319,11 @@
         <f t="shared" si="1"/>
         <v>46161</v>
       </c>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V40" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>93</v>
       </c>
@@ -9365,7 +9386,7 @@
         <v>46161</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>124</v>
       </c>
@@ -9428,7 +9449,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>124</v>
       </c>
@@ -9488,7 +9509,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>127</v>
       </c>
@@ -9548,7 +9569,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>27</v>
       </c>
@@ -9608,7 +9629,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -9671,7 +9692,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>53</v>
       </c>
@@ -9734,7 +9755,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>70</v>
       </c>
@@ -9794,7 +9815,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>75</v>
       </c>
@@ -9857,7 +9878,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>81</v>
       </c>
@@ -9920,7 +9941,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>84</v>
       </c>
@@ -9983,7 +10004,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>91</v>
       </c>
@@ -10043,7 +10064,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>122</v>
       </c>
@@ -10105,8 +10126,11 @@
         <f t="shared" si="1"/>
         <v>46163</v>
       </c>
-    </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V53" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>93</v>
       </c>
@@ -10166,7 +10190,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>138</v>
       </c>
@@ -10229,7 +10253,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>140</v>
       </c>
@@ -10295,7 +10319,7 @@
         <v>46163</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>127</v>
       </c>
@@ -10358,7 +10382,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>96</v>
       </c>
@@ -10423,8 +10447,11 @@
         <f t="shared" si="1"/>
         <v>46167</v>
       </c>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V58" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>21</v>
       </c>
@@ -10484,7 +10511,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>21</v>
       </c>
@@ -10547,7 +10574,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>28</v>
       </c>
@@ -10610,7 +10637,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>44</v>
       </c>
@@ -10670,7 +10697,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>150</v>
       </c>
@@ -10730,7 +10757,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>150</v>
       </c>
@@ -10790,7 +10817,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>150</v>
       </c>
@@ -10853,7 +10880,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -10913,7 +10940,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>53</v>
       </c>
@@ -10973,7 +11000,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -11036,7 +11063,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>154</v>
       </c>
@@ -11099,7 +11126,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -11162,7 +11189,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -11219,7 +11246,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>160</v>
       </c>
@@ -11282,7 +11309,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>140</v>
       </c>
@@ -11345,7 +11372,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>67</v>
       </c>
@@ -11405,7 +11432,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>164</v>
       </c>
@@ -11468,7 +11495,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>164</v>
       </c>
@@ -11531,7 +11558,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>102</v>
       </c>
@@ -11591,7 +11618,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>102</v>
       </c>
@@ -11651,7 +11678,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>102</v>
       </c>
@@ -11711,7 +11738,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>102</v>
       </c>
@@ -11771,7 +11798,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>21</v>
       </c>
@@ -11831,7 +11858,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>154</v>
       </c>
@@ -11891,7 +11918,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>75</v>
       </c>
@@ -11954,7 +11981,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -12017,7 +12044,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>75</v>
       </c>
@@ -12077,7 +12104,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>75</v>
       </c>
@@ -12134,7 +12161,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>44</v>
       </c>
@@ -12197,7 +12224,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>44</v>
       </c>
@@ -12257,7 +12284,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>150</v>
       </c>
@@ -12320,7 +12347,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>177</v>
       </c>
@@ -12380,7 +12407,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>177</v>
       </c>
@@ -12443,7 +12470,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -12506,7 +12533,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>27</v>
       </c>
@@ -12566,7 +12593,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>95</v>
       </c>
@@ -12632,7 +12659,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -12692,7 +12719,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>53</v>
       </c>
@@ -12755,7 +12782,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>53</v>
       </c>
@@ -12818,7 +12845,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>140</v>
       </c>
@@ -12878,7 +12905,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>140</v>
       </c>
@@ -12938,7 +12965,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>140</v>
       </c>
@@ -13001,7 +13028,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>140</v>
       </c>
@@ -13061,7 +13088,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>140</v>
       </c>
@@ -13121,7 +13148,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>93</v>
       </c>
@@ -13181,7 +13208,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>63</v>
       </c>
@@ -13241,7 +13268,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>124</v>
       </c>
@@ -13304,7 +13331,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>124</v>
       </c>
@@ -13364,7 +13391,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="107" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>138</v>
       </c>
@@ -13427,7 +13454,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="108" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>138</v>
       </c>
@@ -13487,7 +13514,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="109" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>84</v>
       </c>
@@ -13550,7 +13577,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="110" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>84</v>
       </c>
@@ -13610,7 +13637,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="111" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>127</v>
       </c>
@@ -13673,7 +13700,7 @@
         <v>46170</v>
       </c>
     </row>
-    <row r="112" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>124</v>
       </c>
@@ -13733,7 +13760,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="113" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>195</v>
       </c>
@@ -13796,7 +13823,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="114" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>150</v>
       </c>
@@ -13859,7 +13886,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="115" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>140</v>
       </c>
@@ -13922,7 +13949,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="116" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>27</v>
       </c>
@@ -13982,7 +14009,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="117" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -14045,7 +14072,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="118" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>21</v>
       </c>
@@ -14108,7 +14135,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="119" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>63</v>
       </c>
@@ -14171,7 +14198,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="120" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>63</v>
       </c>
@@ -14231,7 +14258,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="121" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>102</v>
       </c>
@@ -14294,7 +14321,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="122" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>138</v>
       </c>
@@ -14354,7 +14381,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="123" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>87</v>
       </c>
@@ -14411,7 +14438,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="124" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>75</v>
       </c>
@@ -14471,7 +14498,7 @@
         <v>46174</v>
       </c>
     </row>
-    <row r="125" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -14528,7 +14555,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>236</v>
       </c>
@@ -14591,7 +14618,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>28</v>
       </c>
@@ -14654,7 +14681,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>28</v>
       </c>
@@ -14714,7 +14741,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>53</v>
       </c>
@@ -14777,7 +14804,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="130" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>164</v>
       </c>
@@ -14834,7 +14861,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="131" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>164</v>
       </c>
@@ -14897,7 +14924,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="132" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>154</v>
       </c>
@@ -14960,7 +14987,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="133" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>154</v>
       </c>
@@ -15023,7 +15050,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="134" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>75</v>
       </c>
@@ -15083,7 +15110,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="135" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>77</v>
       </c>
@@ -15143,7 +15170,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="136" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>84</v>
       </c>
@@ -15206,7 +15233,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="137" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>84</v>
       </c>
@@ -15263,7 +15290,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="138" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>84</v>
       </c>
@@ -15326,7 +15353,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="139" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>84</v>
       </c>
@@ -15389,7 +15416,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="140" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -15452,7 +15479,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="141" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>140</v>
       </c>
@@ -15512,7 +15539,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="142" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>140</v>
       </c>
@@ -15575,7 +15602,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="143" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>268</v>
       </c>
@@ -15638,7 +15665,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="144" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>102</v>
       </c>
@@ -15698,7 +15725,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="145" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>138</v>
       </c>
@@ -15755,7 +15782,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="146" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>95</v>
       </c>
@@ -15818,7 +15845,7 @@
         <v>46177</v>
       </c>
     </row>
-    <row r="147" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>127</v>
       </c>
@@ -15881,7 +15908,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="148" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>127</v>
       </c>
@@ -15944,7 +15971,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="149" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>127</v>
       </c>
@@ -16004,7 +16031,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="150" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>127</v>
       </c>
@@ -16064,7 +16091,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="151" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>236</v>
       </c>
@@ -16124,7 +16151,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="152" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>93</v>
       </c>
@@ -16181,7 +16208,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="153" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>177</v>
       </c>
@@ -16244,7 +16271,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="154" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>177</v>
       </c>
@@ -16304,7 +16331,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="155" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>67</v>
       </c>
@@ -16370,7 +16397,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="156" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>164</v>
       </c>
@@ -16433,7 +16460,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="157" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>70</v>
       </c>
@@ -16496,7 +16523,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="158" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>154</v>
       </c>
@@ -16559,7 +16586,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>75</v>
       </c>
@@ -16619,7 +16646,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="160" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>77</v>
       </c>
@@ -16679,7 +16706,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>77</v>
       </c>
@@ -16739,7 +16766,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>195</v>
       </c>
@@ -16802,7 +16829,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>84</v>
       </c>
@@ -16862,7 +16889,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>87</v>
       </c>
@@ -16925,7 +16952,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>81</v>
       </c>
@@ -16985,7 +17012,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>81</v>
       </c>
@@ -17048,7 +17075,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>140</v>
       </c>
@@ -17111,7 +17138,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>140</v>
       </c>
@@ -17168,7 +17195,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>268</v>
       </c>
@@ -17228,7 +17255,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>268</v>
       </c>
@@ -17288,7 +17315,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>160</v>
       </c>
@@ -17348,7 +17375,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>160</v>
       </c>
@@ -17411,7 +17438,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>160</v>
       </c>
@@ -17471,7 +17498,7 @@
         <v>46181</v>
       </c>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>124</v>
       </c>
@@ -17534,7 +17561,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>124</v>
       </c>
@@ -17594,7 +17621,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>87</v>
       </c>
@@ -17657,7 +17684,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="177" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>87</v>
       </c>
@@ -17720,7 +17747,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="178" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>518</v>
       </c>
@@ -17780,7 +17807,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="179" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>518</v>
       </c>
@@ -17843,7 +17870,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="180" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>70</v>
       </c>
@@ -17906,7 +17933,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="181" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>21</v>
       </c>
@@ -17969,7 +17996,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="182" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>75</v>
       </c>
@@ -18032,7 +18059,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="183" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>77</v>
       </c>
@@ -18095,7 +18122,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="184" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>77</v>
       </c>
@@ -18158,7 +18185,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="185" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>195</v>
       </c>
@@ -18221,7 +18248,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="186" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>195</v>
       </c>
@@ -18284,7 +18311,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="187" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>195</v>
       </c>
@@ -18347,7 +18374,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="188" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>150</v>
       </c>
@@ -18410,7 +18437,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="189" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>150</v>
       </c>
@@ -18473,7 +18500,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="190" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>150</v>
       </c>
@@ -18536,7 +18563,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="191" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>102</v>
       </c>
@@ -18599,7 +18626,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="192" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>102</v>
       </c>
@@ -18665,7 +18692,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="193" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>102</v>
       </c>
@@ -18731,7 +18758,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="194" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>81</v>
       </c>
@@ -18794,7 +18821,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="195" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>81</v>
       </c>
@@ -18857,7 +18884,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="196" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>27</v>
       </c>
@@ -18917,7 +18944,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="197" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>95</v>
       </c>
@@ -18974,7 +19001,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="198" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>53</v>
       </c>
@@ -19034,7 +19061,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="199" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>160</v>
       </c>
@@ -19097,7 +19124,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="200" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>140</v>
       </c>
@@ -19160,7 +19187,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="201" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>140</v>
       </c>
@@ -19223,7 +19250,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="202" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>63</v>
       </c>
@@ -19283,7 +19310,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="203" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>63</v>
       </c>
@@ -19346,7 +19373,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="204" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>44</v>
       </c>
@@ -19406,7 +19433,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>44</v>
       </c>
@@ -19466,7 +19493,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>44</v>
       </c>
@@ -19526,7 +19553,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>138</v>
       </c>
@@ -19589,7 +19616,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="208" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>138</v>
       </c>
@@ -19649,7 +19676,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="209" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>138</v>
       </c>
@@ -19712,7 +19739,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="210" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>164</v>
       </c>
@@ -19775,7 +19802,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="211" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>67</v>
       </c>
@@ -19838,7 +19865,7 @@
         <v>46188</v>
       </c>
     </row>
-    <row r="212" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>124</v>
       </c>
@@ -19901,7 +19928,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="213" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>124</v>
       </c>
@@ -19964,7 +19991,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="214" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>91</v>
       </c>
@@ -20027,7 +20054,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="215" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>28</v>
       </c>
@@ -20090,7 +20117,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="216" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>53</v>
       </c>
@@ -20153,7 +20180,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="217" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>70</v>
       </c>
@@ -20213,7 +20240,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="218" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>154</v>
       </c>
@@ -20273,7 +20300,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="219" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>588</v>
       </c>
@@ -20336,7 +20363,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="220" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>588</v>
       </c>
@@ -20396,7 +20423,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="221" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>591</v>
       </c>
@@ -20459,7 +20486,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="222" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>75</v>
       </c>
@@ -20525,7 +20552,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>195</v>
       </c>
@@ -20585,7 +20612,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="224" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>81</v>
       </c>
@@ -20645,7 +20672,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="225" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>81</v>
       </c>
@@ -20708,7 +20735,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="226" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>81</v>
       </c>
@@ -20768,7 +20795,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="227" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>81</v>
       </c>
@@ -20828,7 +20855,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="228" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>81</v>
       </c>
@@ -20891,7 +20918,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="229" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>81</v>
       </c>
@@ -20954,7 +20981,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="230" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>81</v>
       </c>
@@ -21014,7 +21041,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="231" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>102</v>
       </c>
@@ -21077,7 +21104,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="232" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>102</v>
       </c>
@@ -21140,7 +21167,7 @@
         <v>46195</v>
       </c>
     </row>
-    <row r="233" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>124</v>
       </c>
@@ -21206,7 +21233,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>518</v>
       </c>
@@ -21269,7 +21296,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="235" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>91</v>
       </c>
@@ -21329,7 +21356,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="236" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>580</v>
       </c>
@@ -21389,7 +21416,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="237" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>28</v>
       </c>
@@ -21452,7 +21479,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="238" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>28</v>
       </c>
@@ -21515,7 +21542,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="239" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>44</v>
       </c>
@@ -21578,7 +21605,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>53</v>
       </c>
@@ -21641,7 +21668,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="241" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>53</v>
       </c>
@@ -21701,7 +21728,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="242" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>53</v>
       </c>
@@ -21764,7 +21791,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="243" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>53</v>
       </c>
@@ -21824,7 +21851,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="244" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>21</v>
       </c>
@@ -21887,7 +21914,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="245" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>588</v>
       </c>
@@ -21950,7 +21977,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>591</v>
       </c>
@@ -22013,7 +22040,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="247" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>591</v>
       </c>
@@ -22073,7 +22100,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="248" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>591</v>
       </c>
@@ -22136,7 +22163,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="249" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>75</v>
       </c>
@@ -22199,7 +22226,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="250" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>102</v>
       </c>
@@ -22262,7 +22289,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="251" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>127</v>
       </c>
@@ -22325,7 +22352,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="252" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>127</v>
       </c>
@@ -22388,7 +22415,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="253" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>138</v>
       </c>
@@ -22451,7 +22478,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="254" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>84</v>
       </c>
@@ -22511,7 +22538,7 @@
         <v>46198</v>
       </c>
     </row>
-    <row r="255" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>518</v>
       </c>
@@ -22574,7 +22601,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="256" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>518</v>
       </c>
@@ -22634,7 +22661,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="257" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>28</v>
       </c>
@@ -22697,7 +22724,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="258" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>28</v>
       </c>
@@ -22760,7 +22787,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>28</v>
       </c>
@@ -22823,7 +22850,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="260" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>44</v>
       </c>
@@ -22886,7 +22913,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="261" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>150</v>
       </c>
@@ -22949,7 +22976,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="262" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>27</v>
       </c>
@@ -23012,7 +23039,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="263" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>53</v>
       </c>
@@ -23075,7 +23102,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="264" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>70</v>
       </c>
@@ -23135,7 +23162,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="265" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>70</v>
       </c>
@@ -23198,7 +23225,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="266" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>588</v>
       </c>
@@ -23261,7 +23288,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="267" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>588</v>
       </c>
@@ -23324,7 +23351,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>87</v>
       </c>
@@ -23387,7 +23414,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="269" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>87</v>
       </c>
@@ -23450,7 +23477,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="270" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>81</v>
       </c>
@@ -23513,7 +23540,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="271" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>81</v>
       </c>
@@ -23576,7 +23603,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="272" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>268</v>
       </c>
@@ -23639,7 +23666,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="273" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>268</v>
       </c>
@@ -23699,7 +23726,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>160</v>
       </c>
@@ -23762,7 +23789,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="275" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>127</v>
       </c>
@@ -23822,7 +23849,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="276" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>127</v>
       </c>
@@ -23882,7 +23909,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="277" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>95</v>
       </c>
@@ -23948,7 +23975,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="278" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>95</v>
       </c>
@@ -24011,7 +24038,7 @@
         <v>46202</v>
       </c>
     </row>
-    <row r="279" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>84</v>
       </c>
@@ -24084,17 +24111,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97981486-30C0-456D-A312-31B9273B5D63}">
   <dimension ref="A1:S200"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="46.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="24.625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="24.6640625" style="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" ht="22" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>203</v>
       </c>
@@ -24102,13 +24129,13 @@
         <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="S2" s="23" t="str" cm="1">
         <f t="array" ref="S2:S37">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Loot History'!A2:A1987,'Loot History'!A2:A1987&lt;&gt;"")))</f>
         <v>Actitibe-Thunderstrike</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>205</v>
       </c>
@@ -24119,12 +24146,12 @@
         <v>Aethrîa-Thunderstrike</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="S4" s="23" t="str">
         <v>Alàén-Thunderstrike</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="19" t="s">
         <v>206</v>
       </c>
@@ -24144,7 +24171,7 @@
         <v>Bigfutti-Thunderstrike</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="str" cm="1">
         <f t="array" ref="A6:E9">IF($B$3="","← Select a player above",_xlfn._xlws.FILTER(_xlfn.HSTACK('Loot History'!D2:D176,'Loot History'!J2:J176,'Loot History'!B2:B176,'Loot History'!C2:C176,'Loot History'!G2:G176),'Loot History'!A2:A176=$B$3,"No items found for this player"))</f>
         <v>Serpent-Coil Braid</v>
@@ -24165,7 +24192,7 @@
         <v>Desquite-Thunderstrike</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <v>Pauldrons of the Vanquished Hero</v>
       </c>
@@ -24185,7 +24212,7 @@
         <v>Fetzine-Thunderstrike</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <v>Gloves of the Vanquished Hero</v>
       </c>
@@ -24205,7 +24232,7 @@
         <v>Flieege-Thunderstrike</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <v>Chestguard of the Vanquished Hero</v>
       </c>
@@ -24225,851 +24252,851 @@
         <v>Gerdarogers-Thunderstrike</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="20"/>
       <c r="D10" s="21"/>
       <c r="S10" s="23" t="str">
         <v>Gorgohc-Thunderstrike</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="20"/>
       <c r="D11" s="21"/>
       <c r="S11" s="23" t="str">
         <v>Grathmok-Thunderstrike</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="20"/>
       <c r="D12" s="21"/>
       <c r="S12" s="23" t="str">
         <v>Heislbärt-Thunderstrike</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="20"/>
       <c r="D13" s="21"/>
       <c r="S13" s="23" t="str">
         <v>Hutro-Thunderstrike</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="20"/>
       <c r="D14" s="21"/>
       <c r="S14" s="23" t="str">
         <v>Keindaemon-Thunderstrike</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="20"/>
       <c r="D15" s="21"/>
       <c r="S15" s="23" t="str">
         <v>Klaaw-Thunderstrike</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C16" s="20"/>
       <c r="D16" s="21"/>
       <c r="S16" s="23" t="str">
         <v>Lilyasx-Thunderstrike</v>
       </c>
     </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="20"/>
       <c r="D17" s="21"/>
       <c r="S17" s="23" t="str">
         <v>Mahway-Thunderstrike</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="20"/>
       <c r="D18" s="21"/>
       <c r="S18" s="23" t="str">
         <v>Mardinez-Thunderstrike</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="20"/>
       <c r="D19" s="21"/>
       <c r="S19" s="23" t="str">
         <v>Mokrash-Thunderstrike</v>
       </c>
     </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="20"/>
       <c r="D20" s="21"/>
       <c r="S20" s="23" t="str">
         <v>Mommyfrieren-Thunderstrike</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="20"/>
       <c r="D21" s="21"/>
       <c r="S21" s="23" t="str">
         <v>Oßa-Thunderstrike</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="20"/>
       <c r="D22" s="21"/>
       <c r="S22" s="23" t="str">
         <v>Razoga-Thunderstrike</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="20"/>
       <c r="D23" s="21"/>
       <c r="S23" s="23" t="str">
         <v>Reazø-Thunderstrike</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="20"/>
       <c r="D24" s="21"/>
       <c r="S24" s="23" t="str">
         <v>Reezø-Thunderstrike</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="20"/>
       <c r="D25" s="21"/>
       <c r="S25" s="23" t="str">
         <v>Ribsz-Thunderstrike</v>
       </c>
     </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="20"/>
       <c r="D26" s="21"/>
       <c r="S26" s="23" t="str">
         <v>Sanderon-Thunderstrike</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="20"/>
       <c r="D27" s="21"/>
       <c r="S27" s="23" t="str">
         <v>Shreklich-Thunderstrike</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="20"/>
       <c r="D28" s="21"/>
       <c r="S28" s="23" t="str">
         <v>Spewspew-Thunderstrike</v>
       </c>
     </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="20"/>
       <c r="D29" s="21"/>
       <c r="S29" s="23" t="str">
         <v>Supmyaeth-Thunderstrike</v>
       </c>
     </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="20"/>
       <c r="D30" s="21"/>
       <c r="S30" s="23" t="str">
         <v>Tastycake-Thunderstrike</v>
       </c>
     </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="20"/>
       <c r="D31" s="21"/>
       <c r="S31" s="23" t="str">
         <v>Tommypenn-Thunderstrike</v>
       </c>
     </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="20"/>
       <c r="D32" s="21"/>
       <c r="S32" s="23" t="str">
         <v>Tuarendrood-Thunderstrike</v>
       </c>
     </row>
-    <row r="33" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C33" s="20"/>
       <c r="D33" s="21"/>
       <c r="S33" s="23" t="str">
         <v>Xænd-Thunderstrike</v>
       </c>
     </row>
-    <row r="34" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C34" s="20"/>
       <c r="D34" s="21"/>
       <c r="S34" s="23" t="str">
         <v>Xaganat-Thunderstrike</v>
       </c>
     </row>
-    <row r="35" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C35" s="20"/>
       <c r="D35" s="21"/>
       <c r="S35" s="23" t="str">
         <v>Zabipala-Thunderstrike</v>
       </c>
     </row>
-    <row r="36" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C36" s="20"/>
       <c r="D36" s="21"/>
       <c r="S36" s="23" t="str">
         <v>Zerleger-Thunderstrike</v>
       </c>
     </row>
-    <row r="37" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C37" s="20"/>
       <c r="D37" s="21"/>
       <c r="S37" s="23" t="str">
         <v>Zzou-Thunderstrike</v>
       </c>
     </row>
-    <row r="38" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C38" s="20"/>
       <c r="D38" s="21"/>
     </row>
-    <row r="39" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C39" s="20"/>
       <c r="D39" s="21"/>
     </row>
-    <row r="40" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C40" s="20"/>
       <c r="D40" s="21"/>
     </row>
-    <row r="41" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C41" s="20"/>
       <c r="D41" s="21"/>
     </row>
-    <row r="42" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C42" s="20"/>
       <c r="D42" s="21"/>
     </row>
-    <row r="43" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C43" s="20"/>
       <c r="D43" s="21"/>
     </row>
-    <row r="44" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C44" s="20"/>
       <c r="D44" s="21"/>
     </row>
-    <row r="45" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C45" s="20"/>
       <c r="D45" s="21"/>
     </row>
-    <row r="46" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C46" s="20"/>
       <c r="D46" s="21"/>
     </row>
-    <row r="47" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C47" s="20"/>
       <c r="D47" s="21"/>
     </row>
-    <row r="48" spans="3:19" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C48" s="20"/>
       <c r="D48" s="21"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C49" s="20"/>
       <c r="D49" s="21"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C50" s="20"/>
       <c r="D50" s="21"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C51" s="20"/>
       <c r="D51" s="21"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C52" s="20"/>
       <c r="D52" s="21"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C53" s="20"/>
       <c r="D53" s="21"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C54" s="20"/>
       <c r="D54" s="21"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C55" s="20"/>
       <c r="D55" s="21"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C56" s="20"/>
       <c r="D56" s="21"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C57" s="20"/>
       <c r="D57" s="21"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C58" s="20"/>
       <c r="D58" s="21"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C59" s="20"/>
       <c r="D59" s="21"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C60" s="20"/>
       <c r="D60" s="21"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C61" s="20"/>
       <c r="D61" s="21"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C62" s="20"/>
       <c r="D62" s="21"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C63" s="20"/>
       <c r="D63" s="21"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C64" s="20"/>
       <c r="D64" s="21"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C65" s="20"/>
       <c r="D65" s="21"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C66" s="20"/>
       <c r="D66" s="21"/>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C67" s="20"/>
       <c r="D67" s="21"/>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C68" s="20"/>
       <c r="D68" s="21"/>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C69" s="20"/>
       <c r="D69" s="21"/>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C70" s="20"/>
       <c r="D70" s="21"/>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C71" s="20"/>
       <c r="D71" s="21"/>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C72" s="20"/>
       <c r="D72" s="21"/>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C73" s="20"/>
       <c r="D73" s="21"/>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C74" s="20"/>
       <c r="D74" s="21"/>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C75" s="20"/>
       <c r="D75" s="21"/>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C76" s="20"/>
       <c r="D76" s="21"/>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C77" s="20"/>
       <c r="D77" s="21"/>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C78" s="20"/>
       <c r="D78" s="21"/>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C79" s="20"/>
       <c r="D79" s="21"/>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C80" s="20"/>
       <c r="D80" s="21"/>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C81" s="20"/>
       <c r="D81" s="21"/>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C82" s="20"/>
       <c r="D82" s="21"/>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C83" s="20"/>
       <c r="D83" s="21"/>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C84" s="20"/>
       <c r="D84" s="21"/>
     </row>
-    <row r="85" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C85" s="20"/>
       <c r="D85" s="21"/>
     </row>
-    <row r="86" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C86" s="20"/>
       <c r="D86" s="21"/>
     </row>
-    <row r="87" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C87" s="20"/>
       <c r="D87" s="21"/>
     </row>
-    <row r="88" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C88" s="20"/>
       <c r="D88" s="21"/>
     </row>
-    <row r="89" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C89" s="20"/>
       <c r="D89" s="21"/>
     </row>
-    <row r="90" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C90" s="20"/>
       <c r="D90" s="21"/>
     </row>
-    <row r="91" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C91" s="20"/>
       <c r="D91" s="21"/>
     </row>
-    <row r="92" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C92" s="20"/>
       <c r="D92" s="21"/>
     </row>
-    <row r="93" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C93" s="20"/>
       <c r="D93" s="21"/>
     </row>
-    <row r="94" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C94" s="20"/>
       <c r="D94" s="21"/>
     </row>
-    <row r="95" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C95" s="20"/>
       <c r="D95" s="21"/>
     </row>
-    <row r="96" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C96" s="20"/>
       <c r="D96" s="21"/>
     </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C97" s="20"/>
       <c r="D97" s="21"/>
     </row>
-    <row r="98" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C98" s="20"/>
       <c r="D98" s="21"/>
     </row>
-    <row r="99" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C99" s="20"/>
       <c r="D99" s="21"/>
     </row>
-    <row r="100" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C100" s="20"/>
       <c r="D100" s="21"/>
     </row>
-    <row r="101" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C101" s="20"/>
       <c r="D101" s="21"/>
     </row>
-    <row r="102" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C102" s="20"/>
       <c r="D102" s="21"/>
     </row>
-    <row r="103" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C103" s="20"/>
       <c r="D103" s="21"/>
     </row>
-    <row r="104" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C104" s="20"/>
       <c r="D104" s="21"/>
     </row>
-    <row r="105" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C105" s="20"/>
       <c r="D105" s="21"/>
     </row>
-    <row r="106" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C106" s="20"/>
       <c r="D106" s="21"/>
     </row>
-    <row r="107" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C107" s="20"/>
       <c r="D107" s="21"/>
     </row>
-    <row r="108" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C108" s="20"/>
       <c r="D108" s="21"/>
     </row>
-    <row r="109" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C109" s="20"/>
       <c r="D109" s="21"/>
     </row>
-    <row r="110" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C110" s="20"/>
       <c r="D110" s="21"/>
     </row>
-    <row r="111" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C111" s="20"/>
       <c r="D111" s="21"/>
     </row>
-    <row r="112" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C112" s="20"/>
       <c r="D112" s="21"/>
     </row>
-    <row r="113" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C113" s="20"/>
       <c r="D113" s="21"/>
     </row>
-    <row r="114" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C114" s="20"/>
       <c r="D114" s="21"/>
     </row>
-    <row r="115" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C115" s="20"/>
       <c r="D115" s="21"/>
     </row>
-    <row r="116" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C116" s="20"/>
       <c r="D116" s="21"/>
     </row>
-    <row r="117" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C117" s="20"/>
       <c r="D117" s="21"/>
     </row>
-    <row r="118" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C118" s="20"/>
       <c r="D118" s="21"/>
     </row>
-    <row r="119" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C119" s="20"/>
       <c r="D119" s="21"/>
     </row>
-    <row r="120" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C120" s="20"/>
       <c r="D120" s="21"/>
     </row>
-    <row r="121" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C121" s="20"/>
       <c r="D121" s="21"/>
     </row>
-    <row r="122" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C122" s="20"/>
       <c r="D122" s="21"/>
     </row>
-    <row r="123" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C123" s="20"/>
       <c r="D123" s="21"/>
     </row>
-    <row r="124" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C124" s="20"/>
       <c r="D124" s="21"/>
     </row>
-    <row r="125" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C125" s="20"/>
       <c r="D125" s="21"/>
     </row>
-    <row r="126" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C126" s="20"/>
       <c r="D126" s="21"/>
     </row>
-    <row r="127" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C127" s="20"/>
       <c r="D127" s="21"/>
     </row>
-    <row r="128" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C128" s="20"/>
       <c r="D128" s="21"/>
     </row>
-    <row r="129" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C129" s="20"/>
       <c r="D129" s="21"/>
     </row>
-    <row r="130" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C130" s="20"/>
       <c r="D130" s="21"/>
     </row>
-    <row r="131" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C131" s="20"/>
       <c r="D131" s="21"/>
     </row>
-    <row r="132" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C132" s="20"/>
       <c r="D132" s="21"/>
     </row>
-    <row r="133" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C133" s="20"/>
       <c r="D133" s="21"/>
     </row>
-    <row r="134" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C134" s="20"/>
       <c r="D134" s="21"/>
     </row>
-    <row r="135" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C135" s="20"/>
       <c r="D135" s="21"/>
     </row>
-    <row r="136" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C136" s="20"/>
       <c r="D136" s="21"/>
     </row>
-    <row r="137" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C137" s="20"/>
       <c r="D137" s="21"/>
     </row>
-    <row r="138" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C138" s="20"/>
       <c r="D138" s="21"/>
     </row>
-    <row r="139" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C139" s="20"/>
       <c r="D139" s="21"/>
     </row>
-    <row r="140" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C140" s="20"/>
       <c r="D140" s="21"/>
     </row>
-    <row r="141" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C141" s="20"/>
       <c r="D141" s="21"/>
     </row>
-    <row r="142" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C142" s="20"/>
       <c r="D142" s="21"/>
     </row>
-    <row r="143" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C143" s="20"/>
       <c r="D143" s="21"/>
     </row>
-    <row r="144" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C144" s="20"/>
       <c r="D144" s="21"/>
     </row>
-    <row r="145" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C145" s="20"/>
       <c r="D145" s="21"/>
     </row>
-    <row r="146" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C146" s="20"/>
       <c r="D146" s="21"/>
     </row>
-    <row r="147" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C147" s="20"/>
       <c r="D147" s="21"/>
     </row>
-    <row r="148" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C148" s="20"/>
       <c r="D148" s="21"/>
     </row>
-    <row r="149" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C149" s="20"/>
       <c r="D149" s="21"/>
     </row>
-    <row r="150" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C150" s="20"/>
       <c r="D150" s="21"/>
     </row>
-    <row r="151" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C151" s="20"/>
       <c r="D151" s="21"/>
     </row>
-    <row r="152" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C152" s="20"/>
       <c r="D152" s="21"/>
     </row>
-    <row r="153" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C153" s="20"/>
       <c r="D153" s="21"/>
     </row>
-    <row r="154" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C154" s="20"/>
       <c r="D154" s="21"/>
     </row>
-    <row r="155" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C155" s="20"/>
       <c r="D155" s="21"/>
     </row>
-    <row r="156" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C156" s="20"/>
       <c r="D156" s="21"/>
     </row>
-    <row r="157" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C157" s="20"/>
       <c r="D157" s="21"/>
     </row>
-    <row r="158" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C158" s="20"/>
       <c r="D158" s="21"/>
     </row>
-    <row r="159" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C159" s="20"/>
       <c r="D159" s="21"/>
     </row>
-    <row r="160" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C160" s="20"/>
       <c r="D160" s="21"/>
     </row>
-    <row r="161" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C161" s="20"/>
       <c r="D161" s="21"/>
     </row>
-    <row r="162" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C162" s="20"/>
       <c r="D162" s="21"/>
     </row>
-    <row r="163" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C163" s="20"/>
       <c r="D163" s="21"/>
     </row>
-    <row r="164" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C164" s="20"/>
       <c r="D164" s="21"/>
     </row>
-    <row r="165" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C165" s="20"/>
       <c r="D165" s="21"/>
     </row>
-    <row r="166" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C166" s="20"/>
       <c r="D166" s="21"/>
     </row>
-    <row r="167" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C167" s="20"/>
       <c r="D167" s="21"/>
     </row>
-    <row r="168" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C168" s="20"/>
       <c r="D168" s="21"/>
     </row>
-    <row r="169" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C169" s="20"/>
       <c r="D169" s="21"/>
     </row>
-    <row r="170" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C170" s="20"/>
       <c r="D170" s="21"/>
     </row>
-    <row r="171" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C171" s="20"/>
       <c r="D171" s="21"/>
     </row>
-    <row r="172" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C172" s="20"/>
       <c r="D172" s="21"/>
     </row>
-    <row r="173" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C173" s="20"/>
       <c r="D173" s="21"/>
     </row>
-    <row r="174" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C174" s="20"/>
       <c r="D174" s="21"/>
     </row>
-    <row r="175" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C175" s="20"/>
       <c r="D175" s="21"/>
     </row>
-    <row r="176" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C176" s="20"/>
       <c r="D176" s="21"/>
     </row>
-    <row r="177" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C177" s="20"/>
       <c r="D177" s="21"/>
     </row>
-    <row r="178" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C178" s="20"/>
       <c r="D178" s="21"/>
     </row>
-    <row r="179" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C179" s="20"/>
       <c r="D179" s="21"/>
     </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C180" s="20"/>
       <c r="D180" s="21"/>
     </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C181" s="20"/>
       <c r="D181" s="21"/>
     </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C182" s="20"/>
       <c r="D182" s="21"/>
     </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C183" s="20"/>
       <c r="D183" s="21"/>
     </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C184" s="20"/>
       <c r="D184" s="21"/>
     </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C185" s="20"/>
       <c r="D185" s="21"/>
     </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C186" s="20"/>
       <c r="D186" s="21"/>
     </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C187" s="20"/>
       <c r="D187" s="21"/>
     </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C188" s="20"/>
       <c r="D188" s="21"/>
     </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C189" s="20"/>
       <c r="D189" s="21"/>
     </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C190" s="20"/>
       <c r="D190" s="21"/>
     </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C191" s="20"/>
       <c r="D191" s="21"/>
     </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C192" s="20"/>
       <c r="D192" s="21"/>
     </row>
-    <row r="193" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C193" s="20"/>
       <c r="D193" s="21"/>
     </row>
-    <row r="194" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C194" s="20"/>
       <c r="D194" s="21"/>
     </row>
-    <row r="195" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C195" s="20"/>
       <c r="D195" s="21"/>
     </row>
-    <row r="196" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C196" s="20"/>
       <c r="D196" s="21"/>
     </row>
-    <row r="197" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C197" s="20"/>
       <c r="D197" s="21"/>
     </row>
-    <row r="198" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C198" s="20"/>
       <c r="D198" s="21"/>
     </row>
-    <row r="199" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C199" s="20"/>
       <c r="D199" s="21"/>
     </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="3:4" x14ac:dyDescent="0.2">
       <c r="C200" s="20"/>
       <c r="D200" s="21"/>
     </row>
@@ -25086,25 +25113,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{856EE92F-C729-40DA-9986-D43C127C499F}">
   <dimension ref="A1:AK283"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="11" width="11.625" customWidth="1"/>
+    <col min="5" max="11" width="11.6640625" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="4.625" customWidth="1"/>
-    <col min="14" max="21" width="11.625" customWidth="1"/>
-    <col min="22" max="22" width="4.625" customWidth="1"/>
-    <col min="23" max="23" width="28.375" customWidth="1"/>
-    <col min="24" max="24" width="11.625" customWidth="1"/>
-    <col min="25" max="25" width="10.875" customWidth="1"/>
-    <col min="26" max="26" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="8.125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="56.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.6640625" customWidth="1"/>
+    <col min="14" max="21" width="11.6640625" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" customWidth="1"/>
+    <col min="23" max="23" width="28.33203125" customWidth="1"/>
+    <col min="24" max="24" width="11.6640625" customWidth="1"/>
+    <col min="25" max="25" width="10.83203125" customWidth="1"/>
+    <col min="26" max="26" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="56.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>211</v>
       </c>
@@ -25112,7 +25139,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D2" s="14" t="s">
         <v>213</v>
       </c>
@@ -25150,7 +25177,7 @@
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
     </row>
-    <row r="3" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>219</v>
       </c>
@@ -25210,7 +25237,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>223</v>
       </c>
@@ -25274,7 +25301,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>224</v>
       </c>
@@ -25336,7 +25363,7 @@
         <v>Tempest Keep-25 Player</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>225</v>
       </c>
@@ -25398,7 +25425,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>226</v>
       </c>
@@ -25460,7 +25487,7 @@
         <v>Tempest Keep-25 Player</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:28" ht="19" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>227</v>
       </c>
@@ -25522,7 +25549,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D9" t="str">
         <v>Flieege-Thunderstrike</v>
       </c>
@@ -25577,7 +25604,7 @@
         <v>Tempest Keep-25 Player</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D10" t="str">
         <v>Gerdarogers-Thunderstrike</v>
       </c>
@@ -25632,7 +25659,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D11" t="str">
         <v>Gorgohc-Thunderstrike</v>
       </c>
@@ -25687,7 +25714,7 @@
         <v>Tempest Keep-25 Player</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D12" t="str">
         <v>Grathmok-Thunderstrike</v>
       </c>
@@ -25742,7 +25769,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D13" t="str">
         <v>Heislbärt-Thunderstrike</v>
       </c>
@@ -25797,7 +25824,7 @@
         <v>Tempest Keep-25 Player</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D14" t="str">
         <v>Hutro-Thunderstrike</v>
       </c>
@@ -25852,7 +25879,7 @@
         <v>Coilfang: Serpentshrine Cavern-25 Player</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D15" t="str">
         <v>Keindaemon-Thunderstrike</v>
       </c>
@@ -25907,7 +25934,7 @@
         <v>Gruuls Lair-25 Player</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" t="str">
         <v>Klaaw-Thunderstrike</v>
       </c>
@@ -25960,7 +25987,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D17" t="str">
         <v>Lilyasx-Thunderstrike</v>
       </c>
@@ -26013,7 +26040,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D18" t="str">
         <v>Mahway-Thunderstrike</v>
       </c>
@@ -26066,7 +26093,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D19" t="str">
         <v>Mardinez-Thunderstrike</v>
       </c>
@@ -26119,7 +26146,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D20" t="str">
         <v>Mokrash-Thunderstrike</v>
       </c>
@@ -26169,7 +26196,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D21" t="str">
         <v>Mommyfrieren-Thunderstrike</v>
       </c>
@@ -26219,7 +26246,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D22" t="str">
         <v>Oßa-Thunderstrike</v>
       </c>
@@ -26269,7 +26296,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D23" t="str">
         <v>Razoga-Thunderstrike</v>
       </c>
@@ -26319,7 +26346,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D24" t="str">
         <v>Reazø-Thunderstrike</v>
       </c>
@@ -26369,7 +26396,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D25" t="str">
         <v>Reezø-Thunderstrike</v>
       </c>
@@ -26419,7 +26446,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D26" t="str">
         <v>Ribsz-Thunderstrike</v>
       </c>
@@ -26469,7 +26496,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D27" t="str">
         <v>Sanderon-Thunderstrike</v>
       </c>
@@ -26519,7 +26546,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D28" t="str">
         <v>Shreklich-Thunderstrike</v>
       </c>
@@ -26569,7 +26596,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D29" t="str">
         <v>Spewspew-Thunderstrike</v>
       </c>
@@ -26619,7 +26646,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D30" t="str">
         <v>Supmyaeth-Thunderstrike</v>
       </c>
@@ -26669,7 +26696,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D31" t="str">
         <v>Tastycake-Thunderstrike</v>
       </c>
@@ -26719,7 +26746,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D32" t="str">
         <v>Tommypenn-Thunderstrike</v>
       </c>
@@ -26765,7 +26792,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D33" t="str">
         <v>Tuarendrood-Thunderstrike</v>
       </c>
@@ -26811,7 +26838,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D34" t="str">
         <v>Xænd-Thunderstrike</v>
       </c>
@@ -26857,7 +26884,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D35" t="str">
         <v>Xaganat-Thunderstrike</v>
       </c>
@@ -26903,7 +26930,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D36" t="str">
         <v>Zabipala-Thunderstrike</v>
       </c>
@@ -26949,7 +26976,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D37" t="str">
         <v>Zerleger-Thunderstrike</v>
       </c>
@@ -26995,7 +27022,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:28" x14ac:dyDescent="0.2">
       <c r="D38" t="str">
         <v>Zzou-Thunderstrike</v>
       </c>
@@ -27041,7 +27068,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z39" s="4"/>
       <c r="AA39" s="11" t="str">
         <f>IF(Z39="","",COUNTIF('Loot History'!$B:$B,Z39))</f>
@@ -27052,7 +27079,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z40" s="4"/>
       <c r="AA40" s="11" t="str">
         <f>IF(Z40="","",COUNTIF('Loot History'!$B:$B,Z40))</f>
@@ -27063,7 +27090,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z41" s="4"/>
       <c r="AA41" s="11" t="str">
         <f>IF(Z41="","",COUNTIF('Loot History'!$B:$B,Z41))</f>
@@ -27074,7 +27101,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z42" s="4"/>
       <c r="AA42" s="11" t="str">
         <f>IF(Z42="","",COUNTIF('Loot History'!$B:$B,Z42))</f>
@@ -27085,7 +27112,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z43" s="4"/>
       <c r="AA43" s="11" t="str">
         <f>IF(Z43="","",COUNTIF('Loot History'!$B:$B,Z43))</f>
@@ -27096,7 +27123,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:28" x14ac:dyDescent="0.2">
       <c r="Z44" s="4"/>
       <c r="AA44" s="11" t="str">
         <f>IF(Z44="","",COUNTIF('Loot History'!$B:$B,Z44))</f>
@@ -27107,7 +27134,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:28" x14ac:dyDescent="0.2">
       <c r="E45" s="11" t="str">
         <f>IF(D45="","",COUNTIF('Loot History'!$A:$A,D45))</f>
         <v/>
@@ -27150,7 +27177,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:28" x14ac:dyDescent="0.2">
       <c r="E46" s="11" t="str">
         <f>IF(D46="","",COUNTIF('Loot History'!$A:$A,D46))</f>
         <v/>
@@ -27193,7 +27220,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:28" x14ac:dyDescent="0.2">
       <c r="E47" s="11" t="str">
         <f>IF(D47="","",COUNTIF('Loot History'!$A:$A,D47))</f>
         <v/>
@@ -27236,7 +27263,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="4:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:28" x14ac:dyDescent="0.2">
       <c r="E48" s="11" t="str">
         <f>IF(D48="","",COUNTIF('Loot History'!$A:$A,D48))</f>
         <v/>
@@ -27279,7 +27306,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E49" s="11" t="str">
         <f>IF(D49="","",COUNTIF('Loot History'!$A:$A,D49))</f>
         <v/>
@@ -27322,7 +27349,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E50" s="11" t="str">
         <f>IF(D50="","",COUNTIF('Loot History'!$A:$A,D50))</f>
         <v/>
@@ -27365,7 +27392,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E51" s="11" t="str">
         <f>IF(D51="","",COUNTIF('Loot History'!$A:$A,D51))</f>
         <v/>
@@ -27408,7 +27435,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E52" s="11" t="str">
         <f>IF(D52="","",COUNTIF('Loot History'!$A:$A,D52))</f>
         <v/>
@@ -27451,7 +27478,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E53" s="11" t="str">
         <f>IF(D53="","",COUNTIF('Loot History'!$A:$A,D53))</f>
         <v/>
@@ -27494,7 +27521,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E54" s="11" t="str">
         <f>IF(D54="","",COUNTIF('Loot History'!$A:$A,D54))</f>
         <v/>
@@ -27528,7 +27555,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E55" s="11" t="str">
         <f>IF(D55="","",COUNTIF('Loot History'!$A:$A,D55))</f>
         <v/>
@@ -27562,7 +27589,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E56" s="11" t="str">
         <f>IF(D56="","",COUNTIF('Loot History'!$A:$A,D56))</f>
         <v/>
@@ -27596,7 +27623,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E57" s="11" t="str">
         <f>IF(D57="","",COUNTIF('Loot History'!$A:$A,D57))</f>
         <v/>
@@ -27630,7 +27657,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E58" s="11" t="str">
         <f>IF(D58="","",COUNTIF('Loot History'!$A:$A,D58))</f>
         <v/>
@@ -27664,7 +27691,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E59" s="11" t="str">
         <f>IF(D59="","",COUNTIF('Loot History'!$A:$A,D59))</f>
         <v/>
@@ -27698,7 +27725,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E60" s="11" t="str">
         <f>IF(D60="","",COUNTIF('Loot History'!$A:$A,D60))</f>
         <v/>
@@ -27732,7 +27759,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E61" s="11" t="str">
         <f>IF(D61="","",COUNTIF('Loot History'!$A:$A,D61))</f>
         <v/>
@@ -27766,7 +27793,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E62" s="11" t="str">
         <f>IF(D62="","",COUNTIF('Loot History'!$A:$A,D62))</f>
         <v/>
@@ -27800,7 +27827,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E63" s="11" t="str">
         <f>IF(D63="","",COUNTIF('Loot History'!$A:$A,D63))</f>
         <v/>
@@ -27834,7 +27861,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="5:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="5:28" x14ac:dyDescent="0.2">
       <c r="E64" s="11" t="str">
         <f>IF(D64="","",COUNTIF('Loot History'!$A:$A,D64))</f>
         <v/>
@@ -27868,7 +27895,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E65" s="11" t="str">
         <f>IF(D65="","",COUNTIF('Loot History'!$A:$A,D65))</f>
         <v/>
@@ -27902,7 +27929,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E66" s="11" t="str">
         <f>IF(D66="","",COUNTIF('Loot History'!$A:$A,D66))</f>
         <v/>
@@ -27936,7 +27963,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E67" s="11" t="str">
         <f>IF(D67="","",COUNTIF('Loot History'!$A:$A,D67))</f>
         <v/>
@@ -27970,7 +27997,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E68" s="11" t="str">
         <f>IF(D68="","",COUNTIF('Loot History'!$A:$A,D68))</f>
         <v/>
@@ -28004,7 +28031,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E69" s="11" t="str">
         <f>IF(D69="","",COUNTIF('Loot History'!$A:$A,D69))</f>
         <v/>
@@ -28038,7 +28065,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E70" s="11" t="str">
         <f>IF(D70="","",COUNTIF('Loot History'!$A:$A,D70))</f>
         <v/>
@@ -28072,7 +28099,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E71" s="11" t="str">
         <f>IF(D71="","",COUNTIF('Loot History'!$A:$A,D71))</f>
         <v/>
@@ -28106,7 +28133,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E72" s="11" t="str">
         <f>IF(D72="","",COUNTIF('Loot History'!$A:$A,D72))</f>
         <v/>
@@ -28140,7 +28167,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E73" s="11" t="str">
         <f>IF(D73="","",COUNTIF('Loot History'!$A:$A,D73))</f>
         <v/>
@@ -28174,7 +28201,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E74" s="11" t="str">
         <f>IF(D74="","",COUNTIF('Loot History'!$A:$A,D74))</f>
         <v/>
@@ -28208,7 +28235,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E75" s="11" t="str">
         <f>IF(D75="","",COUNTIF('Loot History'!$A:$A,D75))</f>
         <v/>
@@ -28242,7 +28269,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E76" s="11" t="str">
         <f>IF(D76="","",COUNTIF('Loot History'!$A:$A,D76))</f>
         <v/>
@@ -28276,7 +28303,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E77" s="11" t="str">
         <f>IF(D77="","",COUNTIF('Loot History'!$A:$A,D77))</f>
         <v/>
@@ -28310,7 +28337,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E78" s="11" t="str">
         <f>IF(D78="","",COUNTIF('Loot History'!$A:$A,D78))</f>
         <v/>
@@ -28344,7 +28371,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E79" s="11" t="str">
         <f>IF(D79="","",COUNTIF('Loot History'!$A:$A,D79))</f>
         <v/>
@@ -28378,7 +28405,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E80" s="11" t="str">
         <f>IF(D80="","",COUNTIF('Loot History'!$A:$A,D80))</f>
         <v/>
@@ -28412,7 +28439,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E81" s="11" t="str">
         <f>IF(D81="","",COUNTIF('Loot History'!$A:$A,D81))</f>
         <v/>
@@ -28446,7 +28473,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E82" s="11" t="str">
         <f>IF(D82="","",COUNTIF('Loot History'!$A:$A,D82))</f>
         <v/>
@@ -28480,7 +28507,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E83" s="11" t="str">
         <f>IF(D83="","",COUNTIF('Loot History'!$A:$A,D83))</f>
         <v/>
@@ -28514,7 +28541,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E84" s="11" t="str">
         <f>IF(D84="","",COUNTIF('Loot History'!$A:$A,D84))</f>
         <v/>
@@ -28548,7 +28575,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E85" s="11" t="str">
         <f>IF(D85="","",COUNTIF('Loot History'!$A:$A,D85))</f>
         <v/>
@@ -28582,7 +28609,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E86" s="11" t="str">
         <f>IF(D86="","",COUNTIF('Loot History'!$A:$A,D86))</f>
         <v/>
@@ -28616,7 +28643,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E87" s="11" t="str">
         <f>IF(D87="","",COUNTIF('Loot History'!$A:$A,D87))</f>
         <v/>
@@ -28650,7 +28677,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E88" s="11" t="str">
         <f>IF(D88="","",COUNTIF('Loot History'!$A:$A,D88))</f>
         <v/>
@@ -28684,7 +28711,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E89" s="11" t="str">
         <f>IF(D89="","",COUNTIF('Loot History'!$A:$A,D89))</f>
         <v/>
@@ -28718,7 +28745,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E90" s="11" t="str">
         <f>IF(D90="","",COUNTIF('Loot History'!$A:$A,D90))</f>
         <v/>
@@ -28752,7 +28779,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E91" s="11" t="str">
         <f>IF(D91="","",COUNTIF('Loot History'!$A:$A,D91))</f>
         <v/>
@@ -28786,7 +28813,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E92" s="11" t="str">
         <f>IF(D92="","",COUNTIF('Loot History'!$A:$A,D92))</f>
         <v/>
@@ -28820,7 +28847,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E93" s="11" t="str">
         <f>IF(D93="","",COUNTIF('Loot History'!$A:$A,D93))</f>
         <v/>
@@ -28854,7 +28881,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E94" s="11" t="str">
         <f>IF(D94="","",COUNTIF('Loot History'!$A:$A,D94))</f>
         <v/>
@@ -28888,7 +28915,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E95" s="11" t="str">
         <f>IF(D95="","",COUNTIF('Loot History'!$A:$A,D95))</f>
         <v/>
@@ -28922,7 +28949,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E96" s="11" t="str">
         <f>IF(D96="","",COUNTIF('Loot History'!$A:$A,D96))</f>
         <v/>
@@ -28956,7 +28983,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E97" s="11" t="str">
         <f>IF(D97="","",COUNTIF('Loot History'!$A:$A,D97))</f>
         <v/>
@@ -28990,7 +29017,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E98" s="11" t="str">
         <f>IF(D98="","",COUNTIF('Loot History'!$A:$A,D98))</f>
         <v/>
@@ -29024,7 +29051,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E99" s="11" t="str">
         <f>IF(D99="","",COUNTIF('Loot History'!$A:$A,D99))</f>
         <v/>
@@ -29058,7 +29085,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E100" s="11" t="str">
         <f>IF(D100="","",COUNTIF('Loot History'!$A:$A,D100))</f>
         <v/>
@@ -29092,7 +29119,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E101" s="11" t="str">
         <f>IF(D101="","",COUNTIF('Loot History'!$A:$A,D101))</f>
         <v/>
@@ -29126,7 +29153,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E102" s="11" t="str">
         <f>IF(D102="","",COUNTIF('Loot History'!$A:$A,D102))</f>
         <v/>
@@ -29160,7 +29187,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E103" s="11" t="str">
         <f>IF(D103="","",COUNTIF('Loot History'!$A:$A,D103))</f>
         <v/>
@@ -29194,7 +29221,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E104" s="11" t="str">
         <f>IF(D104="","",COUNTIF('Loot History'!$A:$A,D104))</f>
         <v/>
@@ -29228,7 +29255,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E105" s="11" t="str">
         <f>IF(D105="","",COUNTIF('Loot History'!$A:$A,D105))</f>
         <v/>
@@ -29262,7 +29289,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E106" s="11" t="str">
         <f>IF(D106="","",COUNTIF('Loot History'!$A:$A,D106))</f>
         <v/>
@@ -29296,7 +29323,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E107" s="11" t="str">
         <f>IF(D107="","",COUNTIF('Loot History'!$A:$A,D107))</f>
         <v/>
@@ -29330,7 +29357,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E108" s="11" t="str">
         <f>IF(D108="","",COUNTIF('Loot History'!$A:$A,D108))</f>
         <v/>
@@ -29364,7 +29391,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E109" s="11" t="str">
         <f>IF(D109="","",COUNTIF('Loot History'!$A:$A,D109))</f>
         <v/>
@@ -29398,7 +29425,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E110" s="11" t="str">
         <f>IF(D110="","",COUNTIF('Loot History'!$A:$A,D110))</f>
         <v/>
@@ -29432,7 +29459,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E111" s="11" t="str">
         <f>IF(D111="","",COUNTIF('Loot History'!$A:$A,D111))</f>
         <v/>
@@ -29466,7 +29493,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E112" s="11" t="str">
         <f>IF(D112="","",COUNTIF('Loot History'!$A:$A,D112))</f>
         <v/>
@@ -29500,7 +29527,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E113" s="11" t="str">
         <f>IF(D113="","",COUNTIF('Loot History'!$A:$A,D113))</f>
         <v/>
@@ -29534,7 +29561,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E114" s="11" t="str">
         <f>IF(D114="","",COUNTIF('Loot History'!$A:$A,D114))</f>
         <v/>
@@ -29568,7 +29595,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E115" s="11" t="str">
         <f>IF(D115="","",COUNTIF('Loot History'!$A:$A,D115))</f>
         <v/>
@@ -29602,7 +29629,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E116" s="11" t="str">
         <f>IF(D116="","",COUNTIF('Loot History'!$A:$A,D116))</f>
         <v/>
@@ -29636,7 +29663,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E117" s="11" t="str">
         <f>IF(D117="","",COUNTIF('Loot History'!$A:$A,D117))</f>
         <v/>
@@ -29670,7 +29697,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E118" s="11" t="str">
         <f>IF(D118="","",COUNTIF('Loot History'!$A:$A,D118))</f>
         <v/>
@@ -29704,7 +29731,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E119" s="11" t="str">
         <f>IF(D119="","",COUNTIF('Loot History'!$A:$A,D119))</f>
         <v/>
@@ -29738,7 +29765,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E120" s="11" t="str">
         <f>IF(D120="","",COUNTIF('Loot History'!$A:$A,D120))</f>
         <v/>
@@ -29772,7 +29799,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E121" s="11" t="str">
         <f>IF(D121="","",COUNTIF('Loot History'!$A:$A,D121))</f>
         <v/>
@@ -29806,7 +29833,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E122" s="11" t="str">
         <f>IF(D122="","",COUNTIF('Loot History'!$A:$A,D122))</f>
         <v/>
@@ -29840,7 +29867,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E123" s="11" t="str">
         <f>IF(D123="","",COUNTIF('Loot History'!$A:$A,D123))</f>
         <v/>
@@ -29874,7 +29901,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E124" s="11" t="str">
         <f>IF(D124="","",COUNTIF('Loot History'!$A:$A,D124))</f>
         <v/>
@@ -29908,7 +29935,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E125" s="11" t="str">
         <f>IF(D125="","",COUNTIF('Loot History'!$A:$A,D125))</f>
         <v/>
@@ -29942,7 +29969,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E126" s="11" t="str">
         <f>IF(D126="","",COUNTIF('Loot History'!$A:$A,D126))</f>
         <v/>
@@ -29976,7 +30003,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E127" s="11" t="str">
         <f>IF(D127="","",COUNTIF('Loot History'!$A:$A,D127))</f>
         <v/>
@@ -30010,7 +30037,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E128" s="11" t="str">
         <f>IF(D128="","",COUNTIF('Loot History'!$A:$A,D128))</f>
         <v/>
@@ -30044,7 +30071,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E129" s="11" t="str">
         <f>IF(D129="","",COUNTIF('Loot History'!$A:$A,D129))</f>
         <v/>
@@ -30078,7 +30105,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E130" s="11" t="str">
         <f>IF(D130="","",COUNTIF('Loot History'!$A:$A,D130))</f>
         <v/>
@@ -30112,7 +30139,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E131" s="11" t="str">
         <f>IF(D131="","",COUNTIF('Loot History'!$A:$A,D131))</f>
         <v/>
@@ -30146,7 +30173,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E132" s="11" t="str">
         <f>IF(D132="","",COUNTIF('Loot History'!$A:$A,D132))</f>
         <v/>
@@ -30180,7 +30207,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E133" s="11" t="str">
         <f>IF(D133="","",COUNTIF('Loot History'!$A:$A,D133))</f>
         <v/>
@@ -30214,7 +30241,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E134" s="11" t="str">
         <f>IF(D134="","",COUNTIF('Loot History'!$A:$A,D134))</f>
         <v/>
@@ -30248,7 +30275,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E135" s="11" t="str">
         <f>IF(D135="","",COUNTIF('Loot History'!$A:$A,D135))</f>
         <v/>
@@ -30282,7 +30309,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E136" s="11" t="str">
         <f>IF(D136="","",COUNTIF('Loot History'!$A:$A,D136))</f>
         <v/>
@@ -30316,7 +30343,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E137" s="11" t="str">
         <f>IF(D137="","",COUNTIF('Loot History'!$A:$A,D137))</f>
         <v/>
@@ -30350,7 +30377,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E138" s="11" t="str">
         <f>IF(D138="","",COUNTIF('Loot History'!$A:$A,D138))</f>
         <v/>
@@ -30384,7 +30411,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E139" s="11" t="str">
         <f>IF(D139="","",COUNTIF('Loot History'!$A:$A,D139))</f>
         <v/>
@@ -30418,7 +30445,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E140" s="11" t="str">
         <f>IF(D140="","",COUNTIF('Loot History'!$A:$A,D140))</f>
         <v/>
@@ -30452,7 +30479,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E141" s="11" t="str">
         <f>IF(D141="","",COUNTIF('Loot History'!$A:$A,D141))</f>
         <v/>
@@ -30486,7 +30513,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E142" s="11" t="str">
         <f>IF(D142="","",COUNTIF('Loot History'!$A:$A,D142))</f>
         <v/>
@@ -30520,7 +30547,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E143" s="11" t="str">
         <f>IF(D143="","",COUNTIF('Loot History'!$A:$A,D143))</f>
         <v/>
@@ -30554,7 +30581,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E144" s="11" t="str">
         <f>IF(D144="","",COUNTIF('Loot History'!$A:$A,D144))</f>
         <v/>
@@ -30588,7 +30615,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="145" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E145" s="11" t="str">
         <f>IF(D145="","",COUNTIF('Loot History'!$A:$A,D145))</f>
         <v/>
@@ -30622,7 +30649,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="146" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E146" s="11" t="str">
         <f>IF(D146="","",COUNTIF('Loot History'!$A:$A,D146))</f>
         <v/>
@@ -30656,7 +30683,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="147" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E147" s="11" t="str">
         <f>IF(D147="","",COUNTIF('Loot History'!$A:$A,D147))</f>
         <v/>
@@ -30690,7 +30717,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="148" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E148" s="11" t="str">
         <f>IF(D148="","",COUNTIF('Loot History'!$A:$A,D148))</f>
         <v/>
@@ -30724,7 +30751,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="149" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E149" s="11" t="str">
         <f>IF(D149="","",COUNTIF('Loot History'!$A:$A,D149))</f>
         <v/>
@@ -30758,7 +30785,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="150" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E150" s="11" t="str">
         <f>IF(D150="","",COUNTIF('Loot History'!$A:$A,D150))</f>
         <v/>
@@ -30792,7 +30819,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="151" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E151" s="11" t="str">
         <f>IF(D151="","",COUNTIF('Loot History'!$A:$A,D151))</f>
         <v/>
@@ -30826,7 +30853,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="152" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E152" s="11" t="str">
         <f>IF(D152="","",COUNTIF('Loot History'!$A:$A,D152))</f>
         <v/>
@@ -30860,7 +30887,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="153" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E153" s="11" t="str">
         <f>IF(D153="","",COUNTIF('Loot History'!$A:$A,D153))</f>
         <v/>
@@ -30894,7 +30921,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="154" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E154" s="11" t="str">
         <f>IF(D154="","",COUNTIF('Loot History'!$A:$A,D154))</f>
         <v/>
@@ -30928,7 +30955,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="155" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E155" s="11" t="str">
         <f>IF(D155="","",COUNTIF('Loot History'!$A:$A,D155))</f>
         <v/>
@@ -30962,7 +30989,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="156" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E156" s="11" t="str">
         <f>IF(D156="","",COUNTIF('Loot History'!$A:$A,D156))</f>
         <v/>
@@ -30996,7 +31023,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="157" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E157" s="11" t="str">
         <f>IF(D157="","",COUNTIF('Loot History'!$A:$A,D157))</f>
         <v/>
@@ -31030,7 +31057,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="158" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E158" s="11" t="str">
         <f>IF(D158="","",COUNTIF('Loot History'!$A:$A,D158))</f>
         <v/>
@@ -31064,7 +31091,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="159" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E159" s="11" t="str">
         <f>IF(D159="","",COUNTIF('Loot History'!$A:$A,D159))</f>
         <v/>
@@ -31098,7 +31125,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="160" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E160" s="11" t="str">
         <f>IF(D160="","",COUNTIF('Loot History'!$A:$A,D160))</f>
         <v/>
@@ -31132,7 +31159,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="161" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E161" s="11" t="str">
         <f>IF(D161="","",COUNTIF('Loot History'!$A:$A,D161))</f>
         <v/>
@@ -31166,7 +31193,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="162" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E162" s="11" t="str">
         <f>IF(D162="","",COUNTIF('Loot History'!$A:$A,D162))</f>
         <v/>
@@ -31200,7 +31227,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="163" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E163" s="11" t="str">
         <f>IF(D163="","",COUNTIF('Loot History'!$A:$A,D163))</f>
         <v/>
@@ -31234,7 +31261,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="164" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E164" s="11" t="str">
         <f>IF(D164="","",COUNTIF('Loot History'!$A:$A,D164))</f>
         <v/>
@@ -31268,7 +31295,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="165" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E165" s="11" t="str">
         <f>IF(D165="","",COUNTIF('Loot History'!$A:$A,D165))</f>
         <v/>
@@ -31302,7 +31329,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="166" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E166" s="11" t="str">
         <f>IF(D166="","",COUNTIF('Loot History'!$A:$A,D166))</f>
         <v/>
@@ -31336,7 +31363,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="167" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E167" s="11" t="str">
         <f>IF(D167="","",COUNTIF('Loot History'!$A:$A,D167))</f>
         <v/>
@@ -31370,7 +31397,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="168" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E168" s="11" t="str">
         <f>IF(D168="","",COUNTIF('Loot History'!$A:$A,D168))</f>
         <v/>
@@ -31404,7 +31431,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="169" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E169" s="11" t="str">
         <f>IF(D169="","",COUNTIF('Loot History'!$A:$A,D169))</f>
         <v/>
@@ -31438,7 +31465,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="170" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E170" s="11" t="str">
         <f>IF(D170="","",COUNTIF('Loot History'!$A:$A,D170))</f>
         <v/>
@@ -31472,7 +31499,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="171" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E171" s="11" t="str">
         <f>IF(D171="","",COUNTIF('Loot History'!$A:$A,D171))</f>
         <v/>
@@ -31506,7 +31533,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="172" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E172" s="11" t="str">
         <f>IF(D172="","",COUNTIF('Loot History'!$A:$A,D172))</f>
         <v/>
@@ -31540,7 +31567,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="173" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E173" s="11" t="str">
         <f>IF(D173="","",COUNTIF('Loot History'!$A:$A,D173))</f>
         <v/>
@@ -31574,7 +31601,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="174" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E174" s="11" t="str">
         <f>IF(D174="","",COUNTIF('Loot History'!$A:$A,D174))</f>
         <v/>
@@ -31608,7 +31635,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="175" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E175" s="11" t="str">
         <f>IF(D175="","",COUNTIF('Loot History'!$A:$A,D175))</f>
         <v/>
@@ -31642,7 +31669,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="176" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E176" s="11" t="str">
         <f>IF(D176="","",COUNTIF('Loot History'!$A:$A,D176))</f>
         <v/>
@@ -31676,7 +31703,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="177" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E177" s="11" t="str">
         <f>IF(D177="","",COUNTIF('Loot History'!$A:$A,D177))</f>
         <v/>
@@ -31710,7 +31737,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="178" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E178" s="11" t="str">
         <f>IF(D178="","",COUNTIF('Loot History'!$A:$A,D178))</f>
         <v/>
@@ -31744,7 +31771,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="179" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E179" s="11" t="str">
         <f>IF(D179="","",COUNTIF('Loot History'!$A:$A,D179))</f>
         <v/>
@@ -31778,7 +31805,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="180" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E180" s="11" t="str">
         <f>IF(D180="","",COUNTIF('Loot History'!$A:$A,D180))</f>
         <v/>
@@ -31812,7 +31839,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="181" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E181" s="11" t="str">
         <f>IF(D181="","",COUNTIF('Loot History'!$A:$A,D181))</f>
         <v/>
@@ -31846,7 +31873,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="182" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E182" s="11" t="str">
         <f>IF(D182="","",COUNTIF('Loot History'!$A:$A,D182))</f>
         <v/>
@@ -31880,7 +31907,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="183" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E183" s="11" t="str">
         <f>IF(D183="","",COUNTIF('Loot History'!$A:$A,D183))</f>
         <v/>
@@ -31914,7 +31941,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="184" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E184" s="11" t="str">
         <f>IF(D184="","",COUNTIF('Loot History'!$A:$A,D184))</f>
         <v/>
@@ -31948,7 +31975,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="185" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E185" s="11" t="str">
         <f>IF(D185="","",COUNTIF('Loot History'!$A:$A,D185))</f>
         <v/>
@@ -31982,7 +32009,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="186" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E186" s="11" t="str">
         <f>IF(D186="","",COUNTIF('Loot History'!$A:$A,D186))</f>
         <v/>
@@ -32016,7 +32043,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="187" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E187" s="11" t="str">
         <f>IF(D187="","",COUNTIF('Loot History'!$A:$A,D187))</f>
         <v/>
@@ -32050,7 +32077,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="188" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E188" s="11" t="str">
         <f>IF(D188="","",COUNTIF('Loot History'!$A:$A,D188))</f>
         <v/>
@@ -32084,7 +32111,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="189" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E189" s="11" t="str">
         <f>IF(D189="","",COUNTIF('Loot History'!$A:$A,D189))</f>
         <v/>
@@ -32118,7 +32145,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="190" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E190" s="11" t="str">
         <f>IF(D190="","",COUNTIF('Loot History'!$A:$A,D190))</f>
         <v/>
@@ -32152,7 +32179,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="191" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E191" s="11" t="str">
         <f>IF(D191="","",COUNTIF('Loot History'!$A:$A,D191))</f>
         <v/>
@@ -32186,7 +32213,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" spans="5:12" x14ac:dyDescent="0.25">
+    <row r="192" spans="5:12" x14ac:dyDescent="0.2">
       <c r="E192" s="11" t="str">
         <f>IF(D192="","",COUNTIF('Loot History'!$A:$A,D192))</f>
         <v/>
@@ -32220,7 +32247,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="193" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E193" s="11" t="str">
         <f>IF(D193="","",COUNTIF('Loot History'!$A:$A,D193))</f>
         <v/>
@@ -32254,7 +32281,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="194" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E194" s="11" t="str">
         <f>IF(D194="","",COUNTIF('Loot History'!$A:$A,D194))</f>
         <v/>
@@ -32288,7 +32315,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="195" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E195" s="11" t="str">
         <f>IF(D195="","",COUNTIF('Loot History'!$A:$A,D195))</f>
         <v/>
@@ -32322,7 +32349,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="196" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E196" s="11" t="str">
         <f>IF(D196="","",COUNTIF('Loot History'!$A:$A,D196))</f>
         <v/>
@@ -32356,7 +32383,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="197" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E197" s="11" t="str">
         <f>IF(D197="","",COUNTIF('Loot History'!$A:$A,D197))</f>
         <v/>
@@ -32390,7 +32417,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="198" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E198" s="11" t="str">
         <f>IF(D198="","",COUNTIF('Loot History'!$A:$A,D198))</f>
         <v/>
@@ -32424,7 +32451,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="199" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E199" s="11" t="str">
         <f>IF(D199="","",COUNTIF('Loot History'!$A:$A,D199))</f>
         <v/>
@@ -32458,7 +32485,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="200" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E200" s="11" t="str">
         <f>IF(D200="","",COUNTIF('Loot History'!$A:$A,D200))</f>
         <v/>
@@ -32492,7 +32519,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="201" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E201" s="11" t="str">
         <f>IF(D201="","",COUNTIF('Loot History'!$A:$A,D201))</f>
         <v/>
@@ -32526,7 +32553,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="202" spans="5:37" x14ac:dyDescent="0.2">
       <c r="E202" s="11" t="str">
         <f>IF(D202="","",COUNTIF('Loot History'!$A:$A,D202))</f>
         <v/>
@@ -32560,7 +32587,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="204" spans="5:37" x14ac:dyDescent="0.2">
       <c r="AA204" s="10" t="s">
         <v>228</v>
       </c>
@@ -32599,7 +32626,7 @@
       <c r="AJ204" s="10"/>
       <c r="AK204" s="12"/>
     </row>
-    <row r="207" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="207" spans="5:37" x14ac:dyDescent="0.2">
       <c r="AD207" s="15" t="s">
         <v>229</v>
       </c>
@@ -32611,7 +32638,7 @@
       <c r="AI207" s="15"/>
       <c r="AK207" s="15"/>
     </row>
-    <row r="208" spans="5:37" x14ac:dyDescent="0.25">
+    <row r="208" spans="5:37" x14ac:dyDescent="0.2">
       <c r="AD208" s="6" t="s">
         <v>210</v>
       </c>
@@ -32629,7 +32656,7 @@
       </c>
       <c r="AK208" s="6"/>
     </row>
-    <row r="209" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="209" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD209" t="s">
         <v>23</v>
       </c>
@@ -32650,7 +32677,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="210" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="210" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD210" t="s">
         <v>38</v>
       </c>
@@ -32670,7 +32697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="211" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD211" t="s">
         <v>30</v>
       </c>
@@ -32690,7 +32717,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="212" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD212" t="s">
         <v>35</v>
       </c>
@@ -32710,7 +32737,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="213" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="213" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD213" t="s">
         <v>60</v>
       </c>
@@ -32730,7 +32757,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="214" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AD214" t="s">
         <v>232</v>
       </c>
@@ -32750,7 +32777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="215" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AH215" t="str">
         <v>SHAMAN</v>
       </c>
@@ -32759,7 +32786,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="216" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="216" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AH216" t="str">
         <v>WARLOCK</v>
       </c>
@@ -32768,7 +32795,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="217" spans="30:35" x14ac:dyDescent="0.25">
+    <row r="217" spans="30:35" x14ac:dyDescent="0.2">
       <c r="AH217" t="str">
         <v>WARRIOR</v>
       </c>
@@ -32777,7 +32804,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="261" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D261" s="4"/>
       <c r="E261" s="11" t="str">
         <f>IF(D261="","",COUNTIF('Loot History'!$B:$B,D261))</f>
@@ -32788,7 +32815,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D262" s="4"/>
       <c r="E262" s="11" t="str">
         <f>IF(D262="","",COUNTIF('Loot History'!$B:$B,D262))</f>
@@ -32799,7 +32826,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D263" s="4"/>
       <c r="E263" s="11" t="str">
         <f>IF(D263="","",COUNTIF('Loot History'!$B:$B,D263))</f>
@@ -32810,7 +32837,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D264" s="4"/>
       <c r="E264" s="11" t="str">
         <f>IF(D264="","",COUNTIF('Loot History'!$B:$B,D264))</f>
@@ -32821,7 +32848,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D265" s="4"/>
       <c r="E265" s="11" t="str">
         <f>IF(D265="","",COUNTIF('Loot History'!$B:$B,D265))</f>
@@ -32832,7 +32859,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D266" s="4"/>
       <c r="E266" s="11" t="str">
         <f>IF(D266="","",COUNTIF('Loot History'!$B:$B,D266))</f>
@@ -32843,7 +32870,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D267" s="4"/>
       <c r="E267" s="11" t="str">
         <f>IF(D267="","",COUNTIF('Loot History'!$B:$B,D267))</f>
@@ -32854,7 +32881,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D268" s="4"/>
       <c r="E268" s="11" t="str">
         <f>IF(D268="","",COUNTIF('Loot History'!$B:$B,D268))</f>
@@ -32865,7 +32892,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D269" s="4"/>
       <c r="E269" s="11" t="str">
         <f>IF(D269="","",COUNTIF('Loot History'!$B:$B,D269))</f>
@@ -32876,7 +32903,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D270" s="4"/>
       <c r="E270" s="11" t="str">
         <f>IF(D270="","",COUNTIF('Loot History'!$B:$B,D270))</f>
@@ -32887,7 +32914,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D271" s="4"/>
       <c r="E271" s="11" t="str">
         <f>IF(D271="","",COUNTIF('Loot History'!$B:$B,D271))</f>
@@ -32898,7 +32925,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D272" s="4"/>
       <c r="E272" s="11" t="str">
         <f>IF(D272="","",COUNTIF('Loot History'!$B:$B,D272))</f>
@@ -32909,7 +32936,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D273" s="4"/>
       <c r="E273" s="11" t="str">
         <f>IF(D273="","",COUNTIF('Loot History'!$B:$B,D273))</f>
@@ -32920,7 +32947,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D274" s="4"/>
       <c r="E274" s="11" t="str">
         <f>IF(D274="","",COUNTIF('Loot History'!$B:$B,D274))</f>
@@ -32931,7 +32958,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D275" s="4"/>
       <c r="E275" s="11" t="str">
         <f>IF(D275="","",COUNTIF('Loot History'!$B:$B,D275))</f>
@@ -32942,7 +32969,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D276" s="4"/>
       <c r="E276" s="11" t="str">
         <f>IF(D276="","",COUNTIF('Loot History'!$B:$B,D276))</f>
@@ -32953,7 +32980,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D277" s="4"/>
       <c r="E277" s="11" t="str">
         <f>IF(D277="","",COUNTIF('Loot History'!$B:$B,D277))</f>
@@ -32964,7 +32991,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D278" s="4"/>
       <c r="E278" s="11" t="str">
         <f>IF(D278="","",COUNTIF('Loot History'!$B:$B,D278))</f>
@@ -32975,7 +33002,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D279" s="4"/>
       <c r="E279" s="11" t="str">
         <f>IF(D279="","",COUNTIF('Loot History'!$B:$B,D279))</f>
@@ -32986,7 +33013,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D280" s="4"/>
       <c r="E280" s="11" t="str">
         <f>IF(D280="","",COUNTIF('Loot History'!$B:$B,D280))</f>
@@ -32997,7 +33024,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D281" s="4"/>
       <c r="E281" s="11" t="str">
         <f>IF(D281="","",COUNTIF('Loot History'!$B:$B,D281))</f>
@@ -33008,7 +33035,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D282" s="4"/>
       <c r="E282" s="11" t="str">
         <f>IF(D282="","",COUNTIF('Loot History'!$B:$B,D282))</f>
@@ -33019,7 +33046,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D283" s="4"/>
       <c r="E283" s="11" t="str">
         <f>IF(D283="","",COUNTIF('Loot History'!$B:$B,D283))</f>
